--- a/5PT-Master-Prospecting-Workbook.xlsx
+++ b/5PT-Master-Prospecting-Workbook.xlsx
@@ -788,10 +788,14 @@
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Bruno Bonifacini (Software Developer &amp; Security Integrations Specialist)</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n"/>
+          <t>Bruno Bonifacini</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Software Developer &amp; Security Integrations Specialist</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
@@ -890,10 +894,14 @@
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Gare Reid (Manager, Systems Integration)</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n"/>
+          <t>Gare Reid</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Systems Integration</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
@@ -992,10 +1000,14 @@
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Adam Houghton (Director, System Planning)</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n"/>
+          <t>Adam Houghton</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Director, System Planning</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1200,14 @@
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Richard Feldman (Vice President, Trade Product Security &amp; Done)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n"/>
+          <t>Richard Feldman</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Trade Product Security &amp; Done</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="inlineStr">
@@ -1290,10 +1306,14 @@
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Leanda Karunia (Manager, Process &amp; System Cum PA)</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n"/>
+          <t>Leanda Karunia</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Process &amp; System Cum PA</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
@@ -1396,10 +1416,14 @@
       <c r="J9" s="2" t="n"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Mark Federico (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n"/>
+          <t>Mark Federico</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -1498,10 +1522,14 @@
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Darrell Van Meter (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n"/>
+          <t>Darrell Van Meter</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="n"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
@@ -1600,10 +1628,14 @@
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Ashwani Sharma (System Engineer)</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n"/>
+          <t>Ashwani Sharma</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -2282,10 +2314,14 @@
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>John Connelly (IT Specialist)</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n"/>
+          <t>John Connelly</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>IT Specialist</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="n"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -2384,10 +2420,14 @@
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Dave Marsh (Interim Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n"/>
+          <t>Dave Marsh</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Interim Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="n"/>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="inlineStr">
@@ -2976,10 +3016,14 @@
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>James Clifford (Senior Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n"/>
+          <t>James Clifford</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Senior Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="n"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -3078,10 +3122,14 @@
       <c r="J26" s="2" t="n"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Jake Gent (IT Support Specialist)</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n"/>
+          <t>Jake Gent</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Specialist</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -3180,10 +3228,14 @@
       <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Samuel Lutz (It Help Desk Technician)</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n"/>
+          <t>Samuel Lutz</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>It Help Desk Technician</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="n"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -3282,10 +3334,14 @@
       <c r="J28" s="2" t="n"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Haile Mitiku (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n"/>
+          <t>Haile Mitiku</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="n"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -3384,10 +3440,14 @@
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Wayne Brantley (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n"/>
+          <t>Wayne Brantley</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -3874,10 +3934,14 @@
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Matthew Dalton (Lead System Engineer)</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n"/>
+          <t>Matthew Dalton</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Lead System Engineer</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -4270,10 +4334,14 @@
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Caroline Johal (Group Manager, Information Technology Enterprise Solution)</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n"/>
+          <t>Caroline Johal</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Group Manager, Information Technology Enterprise Solution</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="n"/>
       <c r="N38" s="2" t="n"/>
       <c r="O38" s="2" t="inlineStr">
@@ -4372,10 +4440,14 @@
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Joshua Sweeney (Supervisor, Application &amp; Systems Development)</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n"/>
+          <t>Joshua Sweeney</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Supervisor, Application &amp; Systems Development</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="n"/>
       <c r="N39" s="2" t="n"/>
       <c r="O39" s="2" t="inlineStr">
@@ -4470,10 +4542,14 @@
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>William Ainslie (Healthcare Systems Engineer)</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n"/>
+          <t>William Ainslie</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Healthcare Systems Engineer</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="n"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -5058,10 +5134,14 @@
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Randy Toscano (Director, System and Business Partner)</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n"/>
+          <t>Randy Toscano</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Director, System and Business Partner</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="n"/>
       <c r="N46" s="2" t="n"/>
       <c r="O46" s="2" t="inlineStr">
@@ -5254,10 +5334,14 @@
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Jose Torres (IT Specialist &amp; IT Engineer &amp; Senior Manager &amp; Director, ...)</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n"/>
+          <t>Jose Torres</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>IT Specialist &amp; IT Engineer &amp; Senior Manager &amp; Director, ...</t>
+        </is>
+      </c>
       <c r="M48" s="2" t="n"/>
       <c r="N48" s="2" t="n"/>
       <c r="O48" s="2" t="inlineStr">
@@ -5642,10 +5726,14 @@
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Evan Moniz (Manager, Network)</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n"/>
+          <t>Evan Moniz</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Network</t>
+        </is>
+      </c>
       <c r="M52" s="2" t="n"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -6426,10 +6514,14 @@
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Anthony Emma (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n"/>
+          <t>Anthony Emma</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="n"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -6528,10 +6620,14 @@
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Devin Melo (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n"/>
+          <t>Devin Melo</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="n"/>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -6630,10 +6726,14 @@
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Lisa Raasch (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n"/>
+          <t>Lisa Raasch</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M62" s="2" t="n"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -6732,10 +6832,14 @@
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Daniel McClelland (System Administrator)</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n"/>
+          <t>Daniel McClelland</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -6834,10 +6938,14 @@
       <c r="J64" s="2" t="n"/>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Matt Phung (IT Administrator)</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n"/>
+          <t>Matt Phung</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>IT Administrator</t>
+        </is>
+      </c>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -6936,10 +7044,14 @@
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Richard Park (Manager, Business Systems)</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n"/>
+          <t>Richard Park</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Business Systems</t>
+        </is>
+      </c>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="n"/>
       <c r="O65" s="2" t="inlineStr">
@@ -7704,10 +7816,14 @@
       <c r="J73" s="2" t="n"/>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Jimmy Noel (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n"/>
+          <t>Jimmy Noel</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M73" s="2" t="n"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -7900,10 +8016,14 @@
       <c r="J75" s="2" t="n"/>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Chris Geer (Information Technology Consultant)</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n"/>
+          <t>Chris Geer</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Information Technology Consultant</t>
+        </is>
+      </c>
       <c r="M75" s="2" t="n"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -8002,10 +8122,14 @@
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Patrick Wong (Director, Information Technology &amp; Materials)</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n"/>
+          <t>Patrick Wong</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology &amp; Materials</t>
+        </is>
+      </c>
       <c r="M76" s="2" t="n"/>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -8104,10 +8228,14 @@
       <c r="J77" s="2" t="n"/>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Tim McKinney (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n"/>
+          <t>Tim McKinney</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M77" s="2" t="n"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -8304,10 +8432,14 @@
       <c r="J79" s="2" t="n"/>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Peter Ockerbloom (Telecom Systems Technician)</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n"/>
+          <t>Peter Ockerbloom</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Telecom Systems Technician</t>
+        </is>
+      </c>
       <c r="M79" s="2" t="n"/>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -8406,10 +8538,14 @@
       <c r="J80" s="2" t="n"/>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Jonathan Epstein (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n"/>
+          <t>Jonathan Epstein</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M80" s="2" t="n"/>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -8704,10 +8840,14 @@
       <c r="J83" s="2" t="n"/>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Michael Hall (System Engineer)</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n"/>
+          <t>Michael Hall</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
@@ -10848,10 +10988,14 @@
       <c r="J105" s="2" t="n"/>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Lynn Tempesta (Vice President and Information Technology Operations Ma...)</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n"/>
+          <t>Lynn Tempesta</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Vice President and Information Technology Operations Ma...</t>
+        </is>
+      </c>
       <c r="M105" s="2" t="n"/>
       <c r="N105" s="2" t="inlineStr">
         <is>
@@ -10954,10 +11098,14 @@
       <c r="J106" s="2" t="n"/>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Karen Roche (Manager, Corporate Information Systems)</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n"/>
+          <t>Karen Roche</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Corporate Information Systems</t>
+        </is>
+      </c>
       <c r="M106" s="2" t="n"/>
       <c r="N106" s="2" t="n"/>
       <c r="O106" s="2" t="inlineStr">
@@ -11052,10 +11200,14 @@
       <c r="J107" s="2" t="n"/>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Margaret Ruuska (Vice President, Information Technology &amp; Officer)</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n"/>
+          <t>Margaret Ruuska</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Information Technology &amp; Officer</t>
+        </is>
+      </c>
       <c r="M107" s="2" t="n"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
@@ -11158,10 +11310,14 @@
       <c r="J108" s="2" t="n"/>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Phillip Joy (Director, Information Technology Operations &amp; Infrastru...)</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n"/>
+          <t>Phillip Joy</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology Operations &amp; Infrastru...</t>
+        </is>
+      </c>
       <c r="M108" s="2" t="n"/>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="inlineStr">
@@ -11256,10 +11412,14 @@
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>James Hall (Senior Software Systems Engineer &amp; Director &amp; Electrica...)</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n"/>
+          <t>James Hall</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Senior Software Systems Engineer &amp; Director &amp; Electrica...</t>
+        </is>
+      </c>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="inlineStr">
         <is>
@@ -11358,10 +11518,14 @@
       <c r="J110" s="2" t="n"/>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Daniel Bagley (Vice President, Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="n"/>
+          <t>Daniel Bagley</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M110" s="2" t="n"/>
       <c r="N110" s="2" t="inlineStr">
         <is>
@@ -11754,10 +11918,14 @@
       <c r="J114" s="2" t="n"/>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Lin Sandar (System Engineer)</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n"/>
+          <t>Lin Sandar</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>System Engineer</t>
+        </is>
+      </c>
       <c r="M114" s="2" t="n"/>
       <c r="N114" s="2" t="inlineStr">
         <is>
@@ -11856,10 +12024,14 @@
       <c r="J115" s="2" t="n"/>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Bryce Bailey (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n"/>
+          <t>Bryce Bailey</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M115" s="2" t="n"/>
       <c r="N115" s="2" t="inlineStr">
         <is>
@@ -11958,10 +12130,14 @@
       <c r="J116" s="2" t="n"/>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Briyanna Arklein (IT Specialist)</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n"/>
+          <t>Briyanna Arklein</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>IT Specialist</t>
+        </is>
+      </c>
       <c r="M116" s="2" t="n"/>
       <c r="N116" s="2" t="inlineStr">
         <is>
@@ -12256,10 +12432,14 @@
       <c r="J119" s="2" t="n"/>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Tait Hoglund (Senior Infrastructure Engineer)</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n"/>
+          <t>Tait Hoglund</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Senior Infrastructure Engineer</t>
+        </is>
+      </c>
       <c r="M119" s="2" t="n"/>
       <c r="N119" s="2" t="inlineStr">
         <is>
@@ -12938,10 +13118,14 @@
       <c r="J126" s="2" t="n"/>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Phillip Murphy (Director, Information Technology &amp; Development)</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n"/>
+          <t>Phillip Murphy</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology &amp; Development</t>
+        </is>
+      </c>
       <c r="M126" s="2" t="n"/>
       <c r="N126" s="2" t="inlineStr">
         <is>
@@ -13040,10 +13224,14 @@
       <c r="J127" s="2" t="n"/>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Kim Shaw (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n"/>
+          <t>Kim Shaw</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M127" s="2" t="n"/>
       <c r="N127" s="2" t="inlineStr">
         <is>
@@ -13142,10 +13330,14 @@
       <c r="J128" s="2" t="n"/>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Michael Andrade (Manager, Information Systems)</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n"/>
+          <t>Michael Andrade</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Systems</t>
+        </is>
+      </c>
       <c r="M128" s="2" t="n"/>
       <c r="N128" s="2" t="inlineStr">
         <is>
@@ -13240,10 +13432,14 @@
       <c r="J129" s="2" t="n"/>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Jason Brudnick (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n"/>
+          <t>Jason Brudnick</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M129" s="2" t="n"/>
       <c r="N129" s="2" t="inlineStr">
         <is>
@@ -13342,10 +13538,14 @@
       <c r="J130" s="2" t="n"/>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>John Piasecki (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n"/>
+          <t>John Piasecki</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M130" s="2" t="n"/>
       <c r="N130" s="2" t="inlineStr">
         <is>
@@ -13448,10 +13648,14 @@
       <c r="J131" s="2" t="n"/>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Louis Pappa (Information Security Officer)</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n"/>
+          <t>Louis Pappa</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Information Security Officer</t>
+        </is>
+      </c>
       <c r="M131" s="2" t="n"/>
       <c r="N131" s="2" t="inlineStr">
         <is>
@@ -13550,10 +13754,14 @@
       <c r="J132" s="2" t="n"/>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Lawrence Levesque (Senior Business Systems Analyst)</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n"/>
+          <t>Lawrence Levesque</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Systems Analyst</t>
+        </is>
+      </c>
       <c r="M132" s="2" t="n"/>
       <c r="N132" s="2" t="inlineStr">
         <is>
@@ -13652,10 +13860,14 @@
       <c r="J133" s="2" t="n"/>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Mahmoud Yassine (Director, Management Information Systems)</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n"/>
+          <t>Mahmoud Yassine</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Director, Management Information Systems</t>
+        </is>
+      </c>
       <c r="M133" s="2" t="n"/>
       <c r="N133" s="2" t="inlineStr">
         <is>
@@ -14146,10 +14358,14 @@
       <c r="J138" s="2" t="n"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Corren Collura (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n"/>
+          <t>Corren Collura</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M138" s="2" t="n"/>
       <c r="N138" s="2" t="inlineStr">
         <is>
@@ -14248,10 +14464,14 @@
       <c r="J139" s="2" t="n"/>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Ian Wall (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n"/>
+          <t>Ian Wall</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="n"/>
       <c r="O139" s="2" t="inlineStr">
@@ -14444,10 +14664,14 @@
       <c r="J141" s="2" t="n"/>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Michael Vinacco (IT Systems Administrator)</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n"/>
+          <t>Michael Vinacco</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>IT Systems Administrator</t>
+        </is>
+      </c>
       <c r="M141" s="2" t="n"/>
       <c r="N141" s="2" t="inlineStr">
         <is>
@@ -14644,10 +14868,14 @@
       <c r="J143" s="2" t="n"/>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Matthew Postulka (Chief Information Officer &amp; Vice President, Information...)</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n"/>
+          <t>Matthew Postulka</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer &amp; Vice President, Information...</t>
+        </is>
+      </c>
       <c r="M143" s="2" t="n"/>
       <c r="N143" s="2" t="n"/>
       <c r="O143" s="2" t="inlineStr">
@@ -14742,10 +14970,14 @@
       <c r="J144" s="2" t="n"/>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Deborah Cafarella (Senior Director, Information Technology Security &amp; Infr...)</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="n"/>
+          <t>Deborah Cafarella</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>Senior Director, Information Technology Security &amp; Infr...</t>
+        </is>
+      </c>
       <c r="M144" s="2" t="n"/>
       <c r="N144" s="2" t="inlineStr">
         <is>
@@ -14844,10 +15076,14 @@
       <c r="J145" s="2" t="n"/>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Alex Ivkovic (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n"/>
+          <t>Alex Ivkovic</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M145" s="2" t="n"/>
       <c r="N145" s="2" t="inlineStr">
         <is>
@@ -15232,10 +15468,14 @@
       <c r="J149" s="2" t="n"/>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Tim Stevenson (Systems Technician)</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n"/>
+          <t>Tim Stevenson</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Systems Technician</t>
+        </is>
+      </c>
       <c r="M149" s="2" t="n"/>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="2" t="inlineStr">
@@ -15526,10 +15766,14 @@
       <c r="J152" s="2" t="n"/>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Jon Pinault (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="n"/>
+          <t>Jon Pinault</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M152" s="2" t="n"/>
       <c r="N152" s="2" t="inlineStr">
         <is>
@@ -15628,10 +15872,14 @@
       <c r="J153" s="2" t="n"/>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Hossainnuzzaman Shekhon (Management Information Systems Officer)</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n"/>
+          <t>Hossainnuzzaman Shekhon</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>Management Information Systems Officer</t>
+        </is>
+      </c>
       <c r="M153" s="2" t="n"/>
       <c r="N153" s="2" t="inlineStr">
         <is>
@@ -15730,10 +15978,14 @@
       <c r="J154" s="2" t="n"/>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Matthew Wilson (Systems Consultant)</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n"/>
+          <t>Matthew Wilson</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>Systems Consultant</t>
+        </is>
+      </c>
       <c r="M154" s="2" t="n"/>
       <c r="N154" s="2" t="inlineStr">
         <is>
@@ -15832,10 +16084,14 @@
       <c r="J155" s="2" t="n"/>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Jing Wan (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n"/>
+          <t>Jing Wan</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M155" s="2" t="n"/>
       <c r="N155" s="2" t="inlineStr">
         <is>
@@ -16220,10 +16476,14 @@
       <c r="J159" s="2" t="n"/>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Ed Monahan (Infrastructure Manager)</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n"/>
+          <t>Ed Monahan</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>Infrastructure Manager</t>
+        </is>
+      </c>
       <c r="M159" s="2" t="n"/>
       <c r="N159" s="2" t="inlineStr">
         <is>
@@ -16322,10 +16582,14 @@
       <c r="J160" s="2" t="n"/>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Joe Cugini (Systems Administrator)</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n"/>
+          <t>Joe Cugini</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
       <c r="M160" s="2" t="n"/>
       <c r="N160" s="2" t="n"/>
       <c r="O160" s="2" t="inlineStr">
@@ -16420,10 +16684,14 @@
       <c r="J161" s="2" t="n"/>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Kim Pierce (IT Project Facilitator)</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n"/>
+          <t>Kim Pierce</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>IT Project Facilitator</t>
+        </is>
+      </c>
       <c r="M161" s="2" t="n"/>
       <c r="N161" s="2" t="inlineStr">
         <is>
@@ -16624,10 +16892,14 @@
       <c r="J163" s="2" t="n"/>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Wayne Arensman (IT Support Technician)</t>
-        </is>
-      </c>
-      <c r="L163" s="2" t="n"/>
+          <t>Wayne Arensman</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>IT Support Technician</t>
+        </is>
+      </c>
       <c r="M163" s="2" t="n"/>
       <c r="N163" s="2" t="inlineStr">
         <is>
@@ -16726,10 +16998,14 @@
       <c r="J164" s="2" t="n"/>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Elaina Gordon (Director, Information Technology Operations)</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n"/>
+          <t>Elaina Gordon</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology Operations</t>
+        </is>
+      </c>
       <c r="M164" s="2" t="n"/>
       <c r="N164" s="2" t="inlineStr">
         <is>
@@ -16828,10 +17104,14 @@
       <c r="J165" s="2" t="n"/>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>Maureen McLaughlin (System Support)</t>
-        </is>
-      </c>
-      <c r="L165" s="2" t="n"/>
+          <t>Maureen McLaughlin</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>System Support</t>
+        </is>
+      </c>
       <c r="M165" s="2" t="n"/>
       <c r="N165" s="2" t="inlineStr">
         <is>
@@ -16934,10 +17214,14 @@
       <c r="J166" s="2" t="n"/>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Lynne Gray (IT Specialist)</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n"/>
+          <t>Lynne Gray</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>IT Specialist</t>
+        </is>
+      </c>
       <c r="M166" s="2" t="n"/>
       <c r="N166" s="2" t="n"/>
       <c r="O166" s="2" t="inlineStr">
@@ -17032,10 +17316,14 @@
       <c r="J167" s="2" t="n"/>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Mark Badilla (Manager, Management Information Systems)</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n"/>
+          <t>Mark Badilla</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Management Information Systems</t>
+        </is>
+      </c>
       <c r="M167" s="2" t="n"/>
       <c r="N167" s="2" t="inlineStr">
         <is>
@@ -17134,10 +17422,14 @@
       <c r="J168" s="2" t="n"/>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Paul Pijanowski (Senior VP, Information Security)</t>
-        </is>
-      </c>
-      <c r="L168" s="2" t="n"/>
+          <t>Paul Pijanowski</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>Senior VP, Information Security</t>
+        </is>
+      </c>
       <c r="M168" s="2" t="n"/>
       <c r="N168" s="2" t="inlineStr">
         <is>
@@ -17334,10 +17626,14 @@
       <c r="J170" s="2" t="n"/>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>George Wyner (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L170" s="2" t="n"/>
+          <t>George Wyner</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M170" s="2" t="n"/>
       <c r="N170" s="2" t="n"/>
       <c r="O170" s="2" t="inlineStr">
@@ -17432,10 +17728,14 @@
       <c r="J171" s="2" t="n"/>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Jason Savery (Global Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n"/>
+          <t>Jason Savery</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>Global Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M171" s="2" t="n"/>
       <c r="N171" s="2" t="inlineStr">
         <is>
@@ -17534,10 +17834,14 @@
       <c r="J172" s="2" t="n"/>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>David Anderson (Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L172" s="2" t="n"/>
+          <t>David Anderson</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M172" s="2" t="n"/>
       <c r="N172" s="2" t="inlineStr">
         <is>
@@ -17820,10 +18124,14 @@
       <c r="J175" s="2" t="n"/>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Jeff Ryan (Director, Information Technology &amp; Analytics)</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="n"/>
+          <t>Jeff Ryan</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology &amp; Analytics</t>
+        </is>
+      </c>
       <c r="M175" s="2" t="n"/>
       <c r="N175" s="2" t="inlineStr">
         <is>
@@ -18396,10 +18704,14 @@
       <c r="J181" s="2" t="n"/>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>Matthew Acord (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L181" s="2" t="n"/>
+          <t>Matthew Acord</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M181" s="2" t="n"/>
       <c r="N181" s="2" t="inlineStr">
         <is>
@@ -18694,10 +19006,14 @@
       <c r="J184" s="2" t="n"/>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>Wayne McKinnon (Desktop Support Technician)</t>
-        </is>
-      </c>
-      <c r="L184" s="2" t="n"/>
+          <t>Wayne McKinnon</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>Desktop Support Technician</t>
+        </is>
+      </c>
       <c r="M184" s="2" t="n"/>
       <c r="N184" s="2" t="inlineStr">
         <is>
@@ -18796,10 +19112,14 @@
       <c r="J185" s="2" t="n"/>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Wayne Kritzman (Computer Help Desk)</t>
-        </is>
-      </c>
-      <c r="L185" s="2" t="n"/>
+          <t>Wayne Kritzman</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="inlineStr">
+        <is>
+          <t>Computer Help Desk</t>
+        </is>
+      </c>
       <c r="M185" s="2" t="n"/>
       <c r="N185" s="2" t="inlineStr">
         <is>
@@ -18898,10 +19218,14 @@
       <c r="J186" s="2" t="n"/>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Jace Swenson (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L186" s="2" t="n"/>
+          <t>Jace Swenson</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M186" s="2" t="n"/>
       <c r="N186" s="2" t="n"/>
       <c r="O186" s="2" t="inlineStr">
@@ -18992,10 +19316,14 @@
       <c r="J187" s="2" t="n"/>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Kevin Hamel (Senior Vice President Chief Information Officer)</t>
-        </is>
-      </c>
-      <c r="L187" s="2" t="n"/>
+          <t>Kevin Hamel</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>Senior Vice President Chief Information Officer</t>
+        </is>
+      </c>
       <c r="M187" s="2" t="n"/>
       <c r="N187" s="2" t="n"/>
       <c r="O187" s="2" t="inlineStr">
@@ -19196,10 +19524,14 @@
       <c r="J189" s="2" t="n"/>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Tom Kane (CISO &amp; Director, Infrastructure)</t>
-        </is>
-      </c>
-      <c r="L189" s="2" t="n"/>
+          <t>Tom Kane</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="inlineStr">
+        <is>
+          <t>CISO &amp; Director, Infrastructure</t>
+        </is>
+      </c>
       <c r="M189" s="2" t="n"/>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="2" t="inlineStr">
@@ -19286,10 +19618,14 @@
       <c r="J190" s="2" t="n"/>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Michael Fitzgerald (VP, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L190" s="2" t="n"/>
+          <t>Michael Fitzgerald</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="inlineStr">
+        <is>
+          <t>VP, Information Technology</t>
+        </is>
+      </c>
       <c r="M190" s="2" t="n"/>
       <c r="N190" s="2" t="n"/>
       <c r="O190" s="2" t="inlineStr">
@@ -19466,10 +19802,14 @@
       <c r="J192" s="2" t="n"/>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Greg Snow (IT Director, sits in Lincoln RI office)</t>
-        </is>
-      </c>
-      <c r="L192" s="2" t="n"/>
+          <t>Greg Snow</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="inlineStr">
+        <is>
+          <t>IT Director, sits in Lincoln RI office</t>
+        </is>
+      </c>
       <c r="M192" s="2" t="n"/>
       <c r="N192" s="2" t="inlineStr">
         <is>
@@ -19732,10 +20072,14 @@
       <c r="J195" s="2" t="n"/>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Vincent Camillo (Manager, System Support)</t>
-        </is>
-      </c>
-      <c r="L195" s="2" t="n"/>
+          <t>Vincent Camillo</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="inlineStr">
+        <is>
+          <t>Manager, System Support</t>
+        </is>
+      </c>
       <c r="M195" s="2" t="n"/>
       <c r="N195" s="2" t="n"/>
       <c r="O195" s="2" t="inlineStr">
@@ -19822,10 +20166,14 @@
       <c r="J196" s="2" t="n"/>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Regis Kouatcho (Business &amp; IT Systems Analyst)</t>
-        </is>
-      </c>
-      <c r="L196" s="2" t="n"/>
+          <t>Regis Kouatcho</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="inlineStr">
+        <is>
+          <t>Business &amp; IT Systems Analyst</t>
+        </is>
+      </c>
       <c r="M196" s="2" t="n"/>
       <c r="N196" s="2" t="inlineStr">
         <is>
@@ -19924,10 +20272,14 @@
       <c r="J197" s="2" t="n"/>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Bill Gabriel (Manager, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L197" s="2" t="n"/>
+          <t>Bill Gabriel</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="inlineStr">
+        <is>
+          <t>Manager, Information Technology</t>
+        </is>
+      </c>
       <c r="M197" s="2" t="n"/>
       <c r="N197" s="2" t="n"/>
       <c r="O197" s="2" t="inlineStr">
@@ -20022,10 +20374,14 @@
       <c r="J198" s="2" t="n"/>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Reema Shetye (IT Agile Project Manager)</t>
-        </is>
-      </c>
-      <c r="L198" s="2" t="n"/>
+          <t>Reema Shetye</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="inlineStr">
+        <is>
+          <t>IT Agile Project Manager</t>
+        </is>
+      </c>
       <c r="M198" s="2" t="n"/>
       <c r="N198" s="2" t="inlineStr">
         <is>
@@ -20124,10 +20480,14 @@
       <c r="J199" s="2" t="n"/>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Yashvant Patel (Desktop Support Hardware Networking Engineer)</t>
-        </is>
-      </c>
-      <c r="L199" s="2" t="n"/>
+          <t>Yashvant Patel</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="inlineStr">
+        <is>
+          <t>Desktop Support Hardware Networking Engineer</t>
+        </is>
+      </c>
       <c r="M199" s="2" t="n"/>
       <c r="N199" s="2" t="inlineStr">
         <is>
@@ -20328,10 +20688,14 @@
       <c r="J201" s="2" t="n"/>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>Debra King (Vice President, Compliance &amp; Business Systems)</t>
-        </is>
-      </c>
-      <c r="L201" s="2" t="n"/>
+          <t>Debra King</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Compliance &amp; Business Systems</t>
+        </is>
+      </c>
       <c r="M201" s="2" t="n"/>
       <c r="N201" s="2" t="inlineStr">
         <is>
@@ -20528,10 +20892,14 @@
       <c r="J203" s="2" t="n"/>
       <c r="K203" s="2" t="inlineStr">
         <is>
-          <t>Octavio Bizarro (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L203" s="2" t="n"/>
+          <t>Octavio Bizarro</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M203" s="2" t="n"/>
       <c r="N203" s="2" t="inlineStr">
         <is>
@@ -21018,10 +21386,14 @@
       <c r="J208" s="2" t="n"/>
       <c r="K208" s="2" t="inlineStr">
         <is>
-          <t>Ed Murphy (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L208" s="2" t="n"/>
+          <t>Ed Murphy</t>
+        </is>
+      </c>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M208" s="2" t="n"/>
       <c r="N208" s="2" t="n"/>
       <c r="O208" s="2" t="inlineStr">
@@ -21116,10 +21488,14 @@
       <c r="J209" s="2" t="n"/>
       <c r="K209" s="2" t="inlineStr">
         <is>
-          <t>Renato Paiva (Director, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L209" s="2" t="n"/>
+          <t>Renato Paiva</t>
+        </is>
+      </c>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>Director, Information Technology</t>
+        </is>
+      </c>
       <c r="M209" s="2" t="n"/>
       <c r="N209" s="2" t="inlineStr">
         <is>
@@ -21704,10 +22080,14 @@
       <c r="J215" s="2" t="n"/>
       <c r="K215" s="2" t="inlineStr">
         <is>
-          <t>Scott Thursby (Vice President, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L215" s="2" t="n"/>
+          <t>Scott Thursby</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Information Technology</t>
+        </is>
+      </c>
       <c r="M215" s="2" t="n"/>
       <c r="N215" s="2" t="n"/>
       <c r="O215" s="2" t="inlineStr">
@@ -21998,10 +22378,14 @@
       <c r="J218" s="2" t="n"/>
       <c r="K218" s="2" t="inlineStr">
         <is>
-          <t>Jon Dibiasio (Vice President, Information Technology)</t>
-        </is>
-      </c>
-      <c r="L218" s="2" t="n"/>
+          <t>Jon Dibiasio</t>
+        </is>
+      </c>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Information Technology</t>
+        </is>
+      </c>
       <c r="M218" s="2" t="n"/>
       <c r="N218" s="2" t="inlineStr">
         <is>
@@ -43011,7 +43395,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -43019,11 +43403,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>cutterassociates.com</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -43082,11 +43462,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>fintrx.com</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -43145,11 +43521,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>thecateredaffair.com</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -43208,11 +43580,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>cpteng.com</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -43256,14 +43624,10 @@
           <t>(781) 741-8887</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -43271,11 +43635,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>burkeandassoc.com</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -43334,11 +43694,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>emdserono.com</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -43397,11 +43753,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>foodtech.com</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -43460,11 +43812,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>rfcu.com</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -43523,11 +43871,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>uppababy.com</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -43586,11 +43930,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>polymercorporation.com</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -43641,7 +43981,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Testing Services President &amp; Director)  (ask who runs IT if unavailable</t>
+          <t>Testing Services President &amp; Director -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -43649,11 +43989,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>briggsengineering.com</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -43697,14 +44033,10 @@
           <t>(800) 979-9332</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -43712,11 +44044,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>natcoat.com</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
@@ -43763,7 +44091,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -43771,11 +44099,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>k5corporation.com</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
@@ -43826,7 +44150,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -43834,11 +44158,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>gtwilkinson.com</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -43878,14 +44198,10 @@
           <t>(781) 792-0032</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -43893,11 +44209,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>commonwealthbuildingsystems.com</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -43948,7 +44260,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Founder and Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Founder and Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -43956,11 +44268,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>bendongear.com</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
@@ -44019,11 +44327,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>foodallergy.com</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -44078,11 +44382,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>rocklandtrust.com</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
@@ -44133,7 +44433,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -44141,11 +44441,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>united-hvac.com</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
@@ -44196,7 +44492,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -44204,11 +44500,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>greenenvironmental.com</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
@@ -44248,14 +44540,10 @@
           <t>(508) 930-1270</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -44263,11 +44551,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>onescience.com</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -44314,7 +44598,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -44322,11 +44606,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>mija.com</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
@@ -44377,7 +44657,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -44385,11 +44665,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>ruggedmade.com</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
@@ -44444,11 +44720,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>zildjian.com</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="n"/>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -44507,11 +44779,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>radiusgrp.com</t>
-        </is>
-      </c>
+      <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="inlineStr">
         <is>
@@ -44570,11 +44838,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>nvna.org</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -44633,11 +44897,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>dih.com</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="inlineStr">
         <is>
@@ -44696,11 +44956,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>miniter.com</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -44751,7 +45007,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -44759,11 +45015,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>snowandjones.com</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -44814,7 +45066,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -44822,11 +45074,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>airxchange.com</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -44870,14 +45118,10 @@
           <t>(781) 923-0900</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -44885,11 +45129,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>alternativesaba.com</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -44940,7 +45180,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -44948,11 +45188,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>northriverhc.com</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -45007,11 +45243,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>radiosolutionsinc.com</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="inlineStr">
         <is>
@@ -45062,7 +45294,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Founder)  (ask who runs IT if unavailable</t>
+          <t>Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -45070,11 +45302,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>tryanglefoods.com</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="n"/>
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
@@ -45121,7 +45349,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -45129,11 +45357,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>bluebearplumbing.com</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -45184,7 +45408,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -45192,11 +45416,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>driscollagency.com</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -45251,11 +45471,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>safety-kleen.com</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
@@ -45314,11 +45530,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>sullivantire.com</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
@@ -45377,11 +45589,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>signetgroup.net</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="inlineStr">
         <is>
@@ -45425,14 +45633,10 @@
           <t>(781) 878-6495</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -45440,11 +45644,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>southshoreskincenter.com</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="inlineStr">
         <is>
@@ -45495,7 +45695,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Real Estate President &amp; Chief Operating Officer &amp; Agent)  (ask who runs IT if unavailable</t>
+          <t>Real Estate President &amp; Chief Operating Officer &amp; Agent -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -45503,11 +45703,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>jackconway.com</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -45551,14 +45747,10 @@
           <t>(781) 982-7450</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -45566,11 +45758,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>southwoodatnorwell.com</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="n"/>
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
@@ -45621,7 +45809,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Operating Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Operating Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -45629,11 +45817,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>provenaba.com</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
@@ -45684,7 +45868,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -45692,11 +45876,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>ssautismcenter.com</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -45751,11 +45931,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>lmhspc.com</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -45806,7 +45982,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Partner)  (ask who runs IT if unavailable</t>
+          <t>Partner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -45814,11 +45990,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>oralsurgerysouth.com</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -45877,11 +46049,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>arbourhealth.com</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
@@ -45932,7 +46100,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder)  (ask who runs IT if unavailable</t>
+          <t>Co-Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -45940,11 +46108,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>friendshiphome.net</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="n"/>
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -45984,14 +46148,10 @@
           <t>+44 1763 252149</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -45999,11 +46159,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>dolomite-bio.com</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
@@ -46047,14 +46203,10 @@
           <t>(617) 855-5378</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -46062,11 +46214,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>ajaxjets.com</t>
-        </is>
-      </c>
+      <c r="G51" s="2" t="n"/>
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
@@ -46121,11 +46269,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>cushingcenters.org</t>
-        </is>
-      </c>
+      <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -46176,7 +46320,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -46184,11 +46328,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>myhomesteadmortgage.com</t>
-        </is>
-      </c>
+      <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
@@ -46239,7 +46379,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -46247,11 +46387,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>firstresourcecompanies.com</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
@@ -46302,7 +46438,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -46310,11 +46446,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>wbaengineers.com</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="n"/>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -46361,7 +46493,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -46369,11 +46501,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>merrillinc.com</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -46417,14 +46545,10 @@
           <t>(781) 829-0343</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -46432,11 +46556,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>mcgeetoyota.com</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="n"/>
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
@@ -46487,7 +46607,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>General Manager, Fixed Operations)  (ask who runs IT if unavailable</t>
+          <t>General Manager, Fixed Operations -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -46495,11 +46615,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>planetsubaru.com</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="2" t="inlineStr">
         <is>
@@ -46550,7 +46666,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -46558,11 +46674,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>jannellford.com</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
@@ -46621,11 +46733,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>palanders.com</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -46684,11 +46792,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>buckleyonline.com</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="n"/>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -46747,11 +46851,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>srcmedical.com</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -46810,11 +46910,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>hapcoincorporated.com</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="n"/>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -46873,11 +46969,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>gemgravure.com</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -46936,11 +47028,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>critechinc.com</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="n"/>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
@@ -46991,7 +47079,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Owner and Operator)  (ask who runs IT if unavailable</t>
+          <t>Owner and Operator -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -46999,11 +47087,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>amurphy.com</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -47050,7 +47134,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -47058,11 +47142,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>eyesaverinternational.com</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="n"/>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -47113,7 +47193,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -47121,11 +47201,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>sturtevantinc.com</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -47169,14 +47245,10 @@
           <t>(781) 871-1420</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -47184,11 +47256,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>lubritetechnologies.com</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="n"/>
       <c r="H69" s="2" t="n"/>
       <c r="I69" s="2" t="inlineStr">
         <is>
@@ -47228,14 +47296,10 @@
           <t>(781) 829-8585</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -47243,11 +47307,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>ssymca.org</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
@@ -47291,14 +47351,10 @@
           <t>(617) 319-7027</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -47306,11 +47362,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>hinghammoving.com</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="n"/>
       <c r="H71" s="2" t="n"/>
       <c r="I71" s="2" t="inlineStr">
         <is>
@@ -47350,14 +47402,10 @@
           <t>+44 20 7089 1950</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -47365,11 +47413,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>burgopak.com</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
@@ -47428,11 +47472,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>royalhealthgroup.com</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -47476,14 +47516,10 @@
           <t>(888) 747-5283</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -47491,11 +47527,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>fmcicesports.com</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
       <c r="I74" s="2" t="inlineStr">
         <is>
@@ -47554,11 +47586,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>thayerscale.com</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="n"/>
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
@@ -47617,11 +47645,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>nelcoproducts.com</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
       <c r="I76" s="2" t="inlineStr">
         <is>
@@ -47676,11 +47700,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>newenglandvillage.org</t>
-        </is>
-      </c>
+      <c r="G77" s="2" t="n"/>
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -47727,7 +47747,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Founder)  (ask who runs IT if unavailable</t>
+          <t>Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -47735,11 +47755,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>preferredmechanicalservices.com</t>
-        </is>
-      </c>
+      <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
@@ -47794,11 +47810,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
-        <is>
-          <t>yourelectricalsolutions.com</t>
-        </is>
-      </c>
+      <c r="G79" s="2" t="n"/>
       <c r="H79" s="2" t="n"/>
       <c r="I79" s="2" t="inlineStr">
         <is>
@@ -47853,11 +47865,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>rsidelivers.com</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
       <c r="I80" s="2" t="inlineStr">
         <is>
@@ -47908,7 +47916,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -47916,11 +47924,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>acellaconstruction.com</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="n"/>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
@@ -47971,7 +47975,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -47979,11 +47983,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>ritchienavigation.com</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -48042,11 +48042,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>protectowire.com</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="n"/>
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -48086,14 +48082,10 @@
           <t>(800) 932-4202</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -48101,11 +48093,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>fci-ophthalmics.com</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
       <c r="I84" s="2" t="inlineStr">
         <is>
@@ -48145,14 +48133,10 @@
           <t>(877) 606-8765</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -48160,11 +48144,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>entegee.com</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="n"/>
       <c r="H85" s="2" t="n"/>
       <c r="I85" s="2" t="inlineStr">
         <is>
@@ -48208,14 +48188,10 @@
           <t>(781) 826-7770</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -48223,11 +48199,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>hornermillwork.com</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
       <c r="I86" s="2" t="inlineStr">
         <is>
@@ -48278,7 +48250,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -48286,11 +48258,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>markingsinc.com</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="n"/>
       <c r="H87" s="2" t="n"/>
       <c r="I87" s="2" t="inlineStr">
         <is>
@@ -48337,7 +48305,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -48345,11 +48313,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>peakmechanicalservices.com</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
       <c r="I88" s="2" t="inlineStr">
         <is>
@@ -48396,7 +48360,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Chief Financial Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Financial Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -48404,11 +48368,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>charmmedical.com</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="n"/>
       <c r="H89" s="2" t="n"/>
       <c r="I89" s="2" t="inlineStr">
         <is>
@@ -48459,7 +48419,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -48467,11 +48427,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>cadeteenterprises.com</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
       <c r="I90" s="2" t="inlineStr">
         <is>
@@ -48522,7 +48478,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Principal Partner - Chief Financial Officer)  (ask who runs IT if unavailable</t>
+          <t>Principal Partner - Chief Financial Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -48530,11 +48486,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>jlc-tech.com</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="n"/>
       <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
@@ -48581,7 +48533,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Chief Financial Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Financial Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -48589,11 +48541,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>tkasphalt.com</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -48644,7 +48592,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -48652,11 +48600,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>capecodlumber.com</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="n"/>
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -48700,14 +48644,10 @@
           <t>(781) 924-1408</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -48715,11 +48655,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>southeasternaba.com</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
       <c r="I94" s="2" t="inlineStr">
         <is>
@@ -48766,7 +48702,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Owner and Operator)  (ask who runs IT if unavailable</t>
+          <t>Owner and Operator -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -48774,11 +48710,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>sullivansusa.com</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="n"/>
       <c r="H95" s="2" t="n"/>
       <c r="I95" s="2" t="inlineStr">
         <is>
@@ -48829,7 +48761,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>President, Operations &amp; Sales)  (ask who runs IT if unavailable</t>
+          <t>President, Operations &amp; Sales -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -48837,11 +48769,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>seoanelandscape.com</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -48888,7 +48816,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -48896,11 +48824,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>whitman-company.com</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="n"/>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
@@ -48951,7 +48875,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -48959,11 +48883,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>defenseinvestigatorsgroup.com</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
@@ -49007,14 +48927,10 @@
           <t>(781) 871-7496</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -49022,11 +48938,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>walshmechanical.com</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="n"/>
       <c r="H99" s="2" t="n"/>
       <c r="I99" s="2" t="inlineStr">
         <is>
@@ -49073,7 +48985,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -49081,11 +48993,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>websterprinting.com</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -49132,7 +49040,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Buyer &amp; Owner)  (ask who runs IT if unavailable</t>
+          <t>Buyer &amp; Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -49140,11 +49048,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>whitmantoolanddie.com</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="n"/>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -49191,7 +49095,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -49199,11 +49103,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>presidenttitanium.com</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -49254,7 +49154,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -49262,11 +49162,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>clean-systems.com</t>
-        </is>
-      </c>
+      <c r="G103" s="2" t="n"/>
       <c r="H103" s="2" t="n"/>
       <c r="I103" s="2" t="inlineStr">
         <is>
@@ -49317,7 +49213,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -49325,11 +49221,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
-        <is>
-          <t>angelshealthcare.com</t>
-        </is>
-      </c>
+      <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="n"/>
       <c r="I104" s="2" t="inlineStr">
         <is>
@@ -49384,11 +49276,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
-        <is>
-          <t>southshorebank.com</t>
-        </is>
-      </c>
+      <c r="G105" s="2" t="n"/>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
@@ -49447,11 +49335,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>electroswitch.com</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="n"/>
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -49510,11 +49394,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>coastalheritagebank.com</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="n"/>
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -49573,11 +49453,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>healthcaresouth.com</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -49636,11 +49512,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>massa.com</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="n"/>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -49699,11 +49571,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>hinghamsavings.com</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -49750,7 +49618,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Founder)  (ask who runs IT if unavailable</t>
+          <t>Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -49758,11 +49626,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>hinghamlumber.com</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="n"/>
       <c r="H111" s="2" t="n"/>
       <c r="I111" s="2" t="inlineStr">
         <is>
@@ -49813,7 +49677,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Vice President and General Manager)  (ask who runs IT if unavailable</t>
+          <t>Vice President and General Manager -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -49821,11 +49685,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>dynavac.com</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
       <c r="I112" s="2" t="inlineStr">
         <is>
@@ -49869,14 +49729,10 @@
           <t>(781) 337-5555</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -49884,11 +49740,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>southshoreorthopedics.com</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="n"/>
       <c r="H113" s="2" t="n"/>
       <c r="I113" s="2" t="inlineStr">
         <is>
@@ -49943,11 +49795,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>ajaint.com</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
       <c r="I114" s="2" t="inlineStr">
         <is>
@@ -50006,11 +49854,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>egsawyer.com</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="n"/>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
@@ -50069,11 +49913,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>haroldbros.com</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="n"/>
       <c r="H116" s="2" t="n"/>
       <c r="I116" s="2" t="inlineStr">
         <is>
@@ -50120,7 +49960,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -50128,11 +49968,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>harborclinical.com</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="n"/>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -50183,7 +50019,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Founder)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer &amp; Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -50191,11 +50027,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>wellnessworkdays.com</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="n"/>
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -50250,11 +50082,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>o2x.com</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="n"/>
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -50298,14 +50126,10 @@
           <t>(781) 749-4982</t>
         </is>
       </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -50313,11 +50137,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>queenannenh.com</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="n"/>
       <c r="H120" s="2" t="n"/>
       <c r="I120" s="2" t="inlineStr">
         <is>
@@ -50364,7 +50184,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Chief Operating Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Operating Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -50372,11 +50192,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>mcdonaldcorp.com</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="n"/>
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="inlineStr">
         <is>
@@ -50423,7 +50239,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Owner and Administrator)  (ask who runs IT if unavailable</t>
+          <t>Owner and Administrator -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -50431,11 +50247,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>newenglandhospice.com</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="n"/>
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
@@ -50475,14 +50287,10 @@
           <t>(781) 749-0220</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -50490,11 +50298,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>henniganengineering.com</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="n"/>
       <c r="H123" s="2" t="n"/>
       <c r="I123" s="2" t="inlineStr">
         <is>
@@ -50545,7 +50349,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -50553,11 +50357,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>hartsupply.com</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="n"/>
       <c r="H124" s="2" t="n"/>
       <c r="I124" s="2" t="inlineStr">
         <is>
@@ -50608,7 +50408,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Plant Manager)  (ask who runs IT if unavailable</t>
+          <t>Plant Manager -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -50616,11 +50416,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>boxerbrand.com</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="n"/>
       <c r="H125" s="2" t="n"/>
       <c r="I125" s="2" t="inlineStr">
         <is>
@@ -50679,11 +50475,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>baystatemilling.com</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="n"/>
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -50742,11 +50534,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>manetchc.org</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="n"/>
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -50805,11 +50593,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>newenglandmutual.com</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="n"/>
       <c r="H128" s="2" t="n"/>
       <c r="I128" s="2" t="inlineStr">
         <is>
@@ -50864,11 +50648,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>xsbrokers.com</t>
-        </is>
-      </c>
+      <c r="G129" s="2" t="n"/>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="inlineStr">
         <is>
@@ -50923,11 +50703,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>twinriverstechnologies.com</t>
-        </is>
-      </c>
+      <c r="G130" s="2" t="n"/>
       <c r="H130" s="2" t="n"/>
       <c r="I130" s="2" t="inlineStr">
         <is>
@@ -50986,11 +50762,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>mcmcllc.com</t>
-        </is>
-      </c>
+      <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="inlineStr">
         <is>
@@ -51049,11 +50821,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>granitecityelectric.com</t>
-        </is>
-      </c>
+      <c r="G132" s="2" t="n"/>
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -51108,11 +50876,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>leekennedy.com</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="n"/>
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -51159,7 +50923,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -51167,11 +50931,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>baystatecs.org</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="n"/>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -51218,7 +50978,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Owner and President)  (ask who runs IT if unavailable</t>
+          <t>Owner and President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -51226,11 +50986,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>bestofcareinc.com</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="n"/>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -51281,7 +51037,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Founder and President Emeritus)  (ask who runs IT if unavailable</t>
+          <t>Founder and President Emeritus -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -51289,11 +51045,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>hmrproperties.com</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="n"/>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
@@ -51344,7 +51096,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -51352,11 +51104,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>southcovemanor.org</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="n"/>
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="inlineStr">
         <is>
@@ -51411,11 +51159,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>dellbrookjks.com</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="n"/>
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="inlineStr">
         <is>
@@ -51470,11 +51214,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>stran.com</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="n"/>
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
@@ -51525,7 +51265,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -51533,11 +51273,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>jcalnan.com</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="n"/>
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="inlineStr">
         <is>
@@ -51592,11 +51328,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>magellanjets.com</t>
-        </is>
-      </c>
+      <c r="G141" s="2" t="n"/>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
@@ -51643,7 +51375,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -51651,11 +51383,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>envpartners.com</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="n"/>
       <c r="H142" s="2" t="n"/>
       <c r="I142" s="2" t="inlineStr">
         <is>
@@ -51714,11 +51442,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>arbella.com</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="n"/>
       <c r="H143" s="2" t="n"/>
       <c r="I143" s="2" t="inlineStr">
         <is>
@@ -51777,11 +51501,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>shields.com</t>
-        </is>
-      </c>
+      <c r="G144" s="2" t="n"/>
       <c r="H144" s="2" t="n"/>
       <c r="I144" s="2" t="inlineStr">
         <is>
@@ -51840,11 +51560,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>cdf1.com</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="n"/>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
@@ -51888,14 +51604,10 @@
           <t>(781) 585-7136</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -51903,11 +51615,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>welchhrg.com</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="n"/>
       <c r="H146" s="2" t="n"/>
       <c r="I146" s="2" t="inlineStr">
         <is>
@@ -51951,14 +51659,10 @@
           <t>(508) 732-9191</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D147" s="2" t="n"/>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -51966,11 +51670,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>suncorstainless.com</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="n"/>
       <c r="H147" s="2" t="n"/>
       <c r="I147" s="2" t="inlineStr">
         <is>
@@ -52021,7 +51721,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Founder)  (ask who runs IT if unavailable</t>
+          <t>Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -52029,11 +51729,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>ksp.com</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="n"/>
       <c r="H148" s="2" t="n"/>
       <c r="I148" s="2" t="inlineStr">
         <is>
@@ -52092,11 +51788,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>vptec.com</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="n"/>
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
@@ -52147,7 +51839,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Founder)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -52155,11 +51847,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>pbortho.com</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="n"/>
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
@@ -52199,14 +51887,10 @@
           <t>(508) 747-0300</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -52214,11 +51898,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>techetch.com</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
       <c r="I151" s="2" t="inlineStr">
         <is>
@@ -52277,11 +51957,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>learnwell.com</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="n"/>
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
@@ -52340,11 +52016,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>vercenterprises.com</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="n"/>
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
@@ -52403,11 +52075,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>keville.com</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="n"/>
       <c r="H154" s="2" t="n"/>
       <c r="I154" s="2" t="inlineStr">
         <is>
@@ -52462,11 +52130,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>roadtoresponsibility.org</t>
-        </is>
-      </c>
+      <c r="G155" s="2" t="n"/>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
@@ -52506,14 +52170,10 @@
           <t>(508) 746-7433</t>
         </is>
       </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -52521,11 +52181,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
-        <is>
-          <t>hac.center</t>
-        </is>
-      </c>
+      <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="inlineStr">
         <is>
@@ -52572,7 +52228,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -52580,11 +52236,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
-        <is>
-          <t>unitedelevatorcorp.com</t>
-        </is>
-      </c>
+      <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
@@ -52631,7 +52283,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Senior Vice President - General Manager)  (ask who runs IT if unavailable</t>
+          <t>Senior Vice President - General Manager -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -52639,11 +52291,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>coolgearinc.com</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="n"/>
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
@@ -52698,11 +52346,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>induscom.com</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="n"/>
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
@@ -52761,11 +52405,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>sheehanfamilycompanies.com</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="n"/>
       <c r="H160" s="2" t="n"/>
       <c r="I160" s="2" t="inlineStr">
         <is>
@@ -52824,11 +52464,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>smartpakequine.com</t>
-        </is>
-      </c>
+      <c r="G161" s="2" t="n"/>
       <c r="H161" s="2" t="n"/>
       <c r="I161" s="2" t="inlineStr">
         <is>
@@ -52872,14 +52508,10 @@
           <t>(508) 830-1722</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -52887,11 +52519,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>elfc.com</t>
-        </is>
-      </c>
+      <c r="G162" s="2" t="n"/>
       <c r="H162" s="2" t="n"/>
       <c r="I162" s="2" t="inlineStr">
         <is>
@@ -52950,11 +52578,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>ee-co.com</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="n"/>
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
@@ -53013,11 +52637,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>northeastonsavingsbank.com</t>
-        </is>
-      </c>
+      <c r="G164" s="2" t="n"/>
       <c r="H164" s="2" t="n"/>
       <c r="I164" s="2" t="inlineStr">
         <is>
@@ -53072,11 +52692,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>concordfoods.com</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="n"/>
       <c r="H165" s="2" t="n"/>
       <c r="I165" s="2" t="inlineStr">
         <is>
@@ -53135,11 +52751,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>rexa.com</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="n"/>
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="inlineStr">
         <is>
@@ -53198,11 +52810,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>pharmasol.com</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="n"/>
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="inlineStr">
         <is>
@@ -53261,11 +52869,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>scucu.com</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="n"/>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="inlineStr">
         <is>
@@ -53312,7 +52916,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer &amp; Director)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer &amp; Director -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F169" s="2" t="inlineStr">
@@ -53320,11 +52924,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>lyne.com</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="n"/>
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="inlineStr">
         <is>
@@ -53383,11 +52983,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>shawmutcorporation.com</t>
-        </is>
-      </c>
+      <c r="G170" s="2" t="n"/>
       <c r="H170" s="2" t="n"/>
       <c r="I170" s="2" t="inlineStr">
         <is>
@@ -53446,11 +53042,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>jonesandvining.com</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="n"/>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="inlineStr">
         <is>
@@ -53505,11 +53097,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>bnhc.org</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="n"/>
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="inlineStr">
         <is>
@@ -53560,7 +53148,7 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
@@ -53568,11 +53156,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>cheerpack.com</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="n"/>
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="inlineStr">
         <is>
@@ -53627,11 +53211,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>burkedist.com</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="n"/>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="inlineStr">
         <is>
@@ -53678,7 +53258,7 @@
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Chief Commercial Officer)  (ask who runs IT if unavailable</t>
+          <t>Chief Commercial Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr">
@@ -53686,11 +53266,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>cervos.com</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="n"/>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="inlineStr">
         <is>
@@ -53741,7 +53317,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -53749,11 +53325,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>gtrmfg.com</t>
-        </is>
-      </c>
+      <c r="G176" s="2" t="n"/>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="inlineStr">
         <is>
@@ -53804,7 +53376,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -53812,11 +53384,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>frankirounds.com</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="n"/>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="inlineStr">
         <is>
@@ -53856,14 +53424,10 @@
           <t>(508) 230-3170</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
@@ -53871,11 +53435,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>willworkinc.com</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="n"/>
       <c r="H178" s="2" t="n"/>
       <c r="I178" s="2" t="inlineStr">
         <is>
@@ -53915,14 +53475,10 @@
           <t>(508) 230-8001</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr">
@@ -53930,11 +53486,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>gorelco.com</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="n"/>
       <c r="H179" s="2" t="n"/>
       <c r="I179" s="2" t="inlineStr">
         <is>
@@ -53989,11 +53541,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>rubywines.com</t>
-        </is>
-      </c>
+      <c r="G180" s="2" t="n"/>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="inlineStr">
         <is>
@@ -54044,7 +53592,7 @@
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>General Manager)  (ask who runs IT if unavailable</t>
+          <t>General Manager -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F181" s="2" t="inlineStr">
@@ -54052,11 +53600,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>weiss-sheetmetal.com</t>
-        </is>
-      </c>
+      <c r="G181" s="2" t="n"/>
       <c r="H181" s="2" t="n"/>
       <c r="I181" s="2" t="inlineStr">
         <is>
@@ -54103,7 +53647,7 @@
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
@@ -54111,11 +53655,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
-        <is>
-          <t>centralceilings.com</t>
-        </is>
-      </c>
+      <c r="G182" s="2" t="n"/>
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="inlineStr">
         <is>
@@ -54170,11 +53710,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
-        <is>
-          <t>aqualeisure.com</t>
-        </is>
-      </c>
+      <c r="G183" s="2" t="n"/>
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="inlineStr">
         <is>
@@ -54229,11 +53765,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>equalexchange.coop</t>
-        </is>
-      </c>
+      <c r="G184" s="2" t="n"/>
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="inlineStr">
         <is>
@@ -54292,11 +53824,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>mayinstitute.org</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="n"/>
       <c r="H185" s="2" t="n"/>
       <c r="I185" s="2" t="inlineStr">
         <is>
@@ -54347,7 +53875,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>President &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>President &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr">
@@ -54355,11 +53883,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>ipclydon.com</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="n"/>
       <c r="H186" s="2" t="n"/>
       <c r="I186" s="2" t="inlineStr">
         <is>
@@ -54418,11 +53942,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>bostonmutual.com</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="n"/>
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="inlineStr">
         <is>
@@ -54466,14 +53986,10 @@
           <t>(781) 344-1111</t>
         </is>
       </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
@@ -54481,11 +53997,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>franklinsports.com</t>
-        </is>
-      </c>
+      <c r="G188" s="2" t="n"/>
       <c r="H188" s="2" t="n"/>
       <c r="I188" s="2" t="inlineStr">
         <is>
@@ -54544,11 +54056,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>beta-inc.com</t>
-        </is>
-      </c>
+      <c r="G189" s="2" t="n"/>
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
@@ -54592,14 +54100,10 @@
           <t>(781) 828-6900</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D190" s="2" t="n"/>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
@@ -54607,11 +54111,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>aefireinc.com</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="n"/>
       <c r="H190" s="2" t="n"/>
       <c r="I190" s="2" t="inlineStr">
         <is>
@@ -54655,14 +54155,10 @@
           <t>(617) 464-3366</t>
         </is>
       </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D191" s="2" t="n"/>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F191" s="2" t="inlineStr">
@@ -54670,11 +54166,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>channelfish.com</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="n"/>
       <c r="H191" s="2" t="n"/>
       <c r="I191" s="2" t="inlineStr">
         <is>
@@ -54733,11 +54225,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>enesystems.com</t>
-        </is>
-      </c>
+      <c r="G192" s="2" t="n"/>
       <c r="H192" s="2" t="n"/>
       <c r="I192" s="2" t="inlineStr">
         <is>
@@ -54796,11 +54284,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>lacerta.com</t>
-        </is>
-      </c>
+      <c r="G193" s="2" t="n"/>
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
@@ -54859,11 +54343,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>metalbellows.com</t>
-        </is>
-      </c>
+      <c r="G194" s="2" t="n"/>
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="inlineStr">
         <is>
@@ -54922,11 +54402,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>connectpayusa.com</t>
-        </is>
-      </c>
+      <c r="G195" s="2" t="n"/>
       <c r="H195" s="2" t="n"/>
       <c r="I195" s="2" t="inlineStr">
         <is>
@@ -54985,11 +54461,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>cpstechnologysolutions.com</t>
-        </is>
-      </c>
+      <c r="G196" s="2" t="n"/>
       <c r="H196" s="2" t="n"/>
       <c r="I196" s="2" t="inlineStr">
         <is>
@@ -55040,7 +54512,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Business Owner)  (ask who runs IT if unavailable</t>
+          <t>Business Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -55048,11 +54520,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>provenprocess.com</t>
-        </is>
-      </c>
+      <c r="G197" s="2" t="n"/>
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -55111,11 +54579,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>acumentrics.com</t>
-        </is>
-      </c>
+      <c r="G198" s="2" t="n"/>
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="inlineStr">
         <is>
@@ -55166,7 +54630,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Chief Financial Officer &amp; Controller)  (ask who runs IT if unavailable</t>
+          <t>Chief Financial Officer &amp; Controller -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
@@ -55174,11 +54638,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>clinicalsciencelab.com</t>
-        </is>
-      </c>
+      <c r="G199" s="2" t="n"/>
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="inlineStr">
         <is>
@@ -55237,11 +54697,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>newenglandicecream.com</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="n"/>
       <c r="H200" s="2" t="n"/>
       <c r="I200" s="2" t="inlineStr">
         <is>
@@ -55285,14 +54741,10 @@
           <t>(888) 498-0476</t>
         </is>
       </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D201" s="2" t="n"/>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
@@ -55300,11 +54752,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>aerogloballogistics.com</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="n"/>
       <c r="H201" s="2" t="n"/>
       <c r="I201" s="2" t="inlineStr">
         <is>
@@ -55344,14 +54792,10 @@
           <t>(508) 772-1200</t>
         </is>
       </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D202" s="2" t="n"/>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
@@ -55359,11 +54803,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>kdc.org</t>
-        </is>
-      </c>
+      <c r="G202" s="2" t="n"/>
       <c r="H202" s="2" t="n"/>
       <c r="I202" s="2" t="inlineStr">
         <is>
@@ -55410,7 +54850,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Chief Executive Officer)  (ask who runs IT if unavailable</t>
+          <t>Co-Founder &amp; Chief Executive Officer -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
@@ -55418,11 +54858,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>nexdine.com</t>
-        </is>
-      </c>
+      <c r="G203" s="2" t="n"/>
       <c r="H203" s="2" t="n"/>
       <c r="I203" s="2" t="inlineStr">
         <is>
@@ -55473,7 +54909,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>President)  (ask who runs IT if unavailable</t>
+          <t>President -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F204" s="2" t="inlineStr">
@@ -55481,11 +54917,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>islandoasis.com</t>
-        </is>
-      </c>
+      <c r="G204" s="2" t="n"/>
       <c r="H204" s="2" t="n"/>
       <c r="I204" s="2" t="inlineStr">
         <is>
@@ -55544,11 +54976,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>belknapwhite.com</t>
-        </is>
-      </c>
+      <c r="G205" s="2" t="n"/>
       <c r="H205" s="2" t="n"/>
       <c r="I205" s="2" t="inlineStr">
         <is>
@@ -55603,11 +55031,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>charlesriverapparel.com</t>
-        </is>
-      </c>
+      <c r="G206" s="2" t="n"/>
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="inlineStr">
         <is>
@@ -55658,7 +55082,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Owner)  (ask who runs IT if unavailable</t>
+          <t>Owner -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F207" s="2" t="inlineStr">
@@ -55666,11 +55090,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>accutechpkg.com</t>
-        </is>
-      </c>
+      <c r="G207" s="2" t="n"/>
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="inlineStr">
         <is>
@@ -55710,14 +55130,10 @@
           <t>(781) 447-0393</t>
         </is>
       </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D208" s="2" t="n"/>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F208" s="2" t="inlineStr">
@@ -55725,11 +55141,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
-        <is>
-          <t>payton-construction.com</t>
-        </is>
-      </c>
+      <c r="G208" s="2" t="n"/>
       <c r="H208" s="2" t="n"/>
       <c r="I208" s="2" t="inlineStr">
         <is>
@@ -55776,7 +55188,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>General Manager)  (ask who runs IT if unavailable</t>
+          <t>General Manager -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
@@ -55784,11 +55196,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
-        <is>
-          <t>southshoremillwork.com</t>
-        </is>
-      </c>
+      <c r="G209" s="2" t="n"/>
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="inlineStr">
         <is>
@@ -55839,7 +55247,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Founder)  (ask who runs IT if unavailable</t>
+          <t>Founder -- no dedicated IT contact on file, ask who runs IT</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
@@ -55847,11 +55255,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
-        <is>
-          <t>chexfoods.com</t>
-        </is>
-      </c>
+      <c r="G210" s="2" t="n"/>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="inlineStr">
         <is>
@@ -55891,14 +55295,10 @@
           <t>(508) 339-1300</t>
         </is>
       </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D211" s="2" t="n"/>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
@@ -55906,11 +55306,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
-        <is>
-          <t>hrknowledge.com</t>
-        </is>
-      </c>
+      <c r="G211" s="2" t="n"/>
       <c r="H211" s="2" t="n"/>
       <c r="I211" s="2" t="inlineStr">
         <is>
@@ -55969,11 +55365,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>eclinicalsol.com</t>
-        </is>
-      </c>
+      <c r="G212" s="2" t="n"/>
       <c r="H212" s="2" t="n"/>
       <c r="I212" s="2" t="inlineStr">
         <is>
@@ -56017,14 +55409,10 @@
           <t>(508) 928-4769</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D213" s="2" t="n"/>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
@@ -56032,11 +55420,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>ferrymorse.com</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="n"/>
       <c r="H213" s="2" t="n"/>
       <c r="I213" s="2" t="inlineStr">
         <is>
@@ -56080,14 +55464,10 @@
           <t>(781) 821-0121</t>
         </is>
       </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>ask who runs IT if unavailable</t>
+          <t>No IT contact on file -- ask who runs IT</t>
         </is>
       </c>
       <c r="F214" s="2" t="inlineStr">
@@ -56095,11 +55475,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>aetco.us</t>
-        </is>
-      </c>
+      <c r="G214" s="2" t="n"/>
       <c r="H214" s="2" t="n"/>
       <c r="I214" s="2" t="inlineStr">
         <is>
@@ -56158,11 +55534,7 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>baystatept.com</t>
-        </is>
-      </c>
+      <c r="G215" s="2" t="n"/>
       <c r="H215" s="2" t="n"/>
       <c r="I215" s="2" t="inlineStr">
         <is>

--- a/5PT-Master-Prospecting-Workbook.xlsx
+++ b/5PT-Master-Prospecting-Workbook.xlsx
@@ -683,7 +683,11 @@
           <t>(339) 469-0600</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>(785) 845-8526</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
@@ -732,116 +736,124 @@
           <t>cutterassociates.com</t>
         </is>
       </c>
-      <c r="W2" s="2" t="n"/>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>Owned by Nomura Research Institute since 2022. Local office still runs day to day here. Hybrid workforce. [ZoomInfo ID 19993081]</t>
+          <t>Owned by Nomura Research Institute since 2022. Local office still runs day to day here. Hybrid workforce. [ZoomInfo ID 19993081]  |  ZoomInfo confirmed mobile (785) 845-8526 for Cindy Castellano, callable (not flagged Do Not Call).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>FINTRX</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>40 Reservoir Park Dr, Ste A</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>(617) 517-0789</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Bruno Bonifacini</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Software Developer &amp; Security Integrations Specialist</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Dennis Caulfield (Chief Product &amp; Data Officer)</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>Family office and RIA data platform (SaaS)</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>Growing fintech with SOC 2 expectations from clients. Lead with co-managed security and compliance.</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>17855000</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="U3" s="4" t="n"/>
+      <c r="V3" s="4" t="inlineStr">
         <is>
           <t>fintrx.com</t>
         </is>
       </c>
-      <c r="W3" s="2" t="n"/>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>Has developers but likely thin IT ops. Good co-managed fit. Fast growth company. [ZoomInfo ID 461888001]</t>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X3" s="5" t="inlineStr">
+        <is>
+          <t>Has developers but likely thin IT ops. Good co-managed fit. Fast growth company. [ZoomInfo ID 461888001]  |  ZoomInfo matched Bruno Bonifacini but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1425,11 @@
           <t>(781) 878-0232</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>(781) 681-4808</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
           <t>Mark Federico</t>
@@ -1466,10 +1482,14 @@
           <t>rfcu.com</t>
         </is>
       </c>
-      <c r="W9" s="2" t="n"/>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>Has internal IT led by a senior VP. Co-managed and security services angle, not full outsource. [ZoomInfo ID 59785848]</t>
+          <t>Has internal IT led by a senior VP. Co-managed and security services angle, not full outsource. [ZoomInfo ID 59785848]  |  ZoomInfo confirmed both direct (781) 681-4808 and mobile (774) 249-2492 for Mark Federico, callable.</t>
         </is>
       </c>
     </row>
@@ -1519,7 +1539,11 @@
           <t>(781) 413-3000</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>(781) 413-3008</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Darrell Van Meter</t>
@@ -1572,116 +1596,124 @@
           <t>uppababy.com</t>
         </is>
       </c>
-      <c r="W10" s="2" t="n"/>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>Flagship local HQ. CPSC regulated products mean documentation and systems matter. Also on the 2026 Targets Master. Merge outreach history before visiting. [ZoomInfo ID 353910475]</t>
+          <t>Flagship local HQ. CPSC regulated products mean documentation and systems matter. Also on the 2026 Targets Master. Merge outreach history before visiting. [ZoomInfo ID 353910475]  |  ZoomInfo confirmed direct (781) 413-3008 and mobile (781) 243-9205 for Darrell Van Meter, callable.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Polymer Corporation</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>180 Pleasant St</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>(781) 871-4606</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Ashwani Sharma</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>System Engineer</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>Jim Ryan (President)</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>Custom plastics and thermoforming manufacturer</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>100 person manufacturer, likely 0 to 2 IT staff. Lead with co-managed support and plant uptime.</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>26997000</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>1979</t>
         </is>
       </c>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U11" s="4" t="n"/>
+      <c r="V11" s="4" t="inlineStr">
         <is>
           <t>polymercorporation.com</t>
         </is>
       </c>
-      <c r="W11" s="2" t="n"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>Classic ICP manufacturer. Strong first stop. [ZoomInfo ID 343688307]</t>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X11" s="5" t="inlineStr">
+        <is>
+          <t>Classic ICP manufacturer. Strong first stop. [ZoomInfo ID 343688307]  |  ZoomInfo matched Ashwani Sharma but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1763,11 @@
           <t>(781) 871-6040</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>(781) 871-6040 ext. 204</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
@@ -1776,104 +1812,112 @@
           <t>briggsengineering.com</t>
         </is>
       </c>
-      <c r="W12" s="2" t="n"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>Same complex as Bendon Gear. Two stops, one lot. [ZoomInfo ID 17159799]</t>
+          <t>Same complex as Bendon Gear. Two stops, one lot. [ZoomInfo ID 17159799]  |  ZoomInfo confirmed direct dial (781) 871-6040 ext. 204 for Sean Skorohod, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>National Coating</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>105 Industrial Way</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>(800) 979-9332</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Coated fabrics and technical textiles manufacturer</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Production scheduling and quality systems on aging infrastructure is common here. Ask about uptime.</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>13780000</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U13" s="4" t="n"/>
+      <c r="V13" s="4" t="inlineStr">
         <is>
           <t>natcoat.com</t>
         </is>
       </c>
-      <c r="W13" s="2" t="n"/>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 353777346]</t>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X13" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 353777346]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3057,11 @@
           <t>(781) 871-2200</t>
         </is>
       </c>
-      <c r="J25" s="2" t="n"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>(781) 607-2482</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
           <t>James Clifford</t>
@@ -3066,10 +3114,14 @@
           <t>zildjian.com</t>
         </is>
       </c>
-      <c r="W25" s="2" t="n"/>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>Vic Firth is part of Zildjian, same campus. Iconic account for local proof. [ZoomInfo ID 8996860]</t>
+          <t>Vic Firth is part of Zildjian, same campus. Iconic account for local proof. [ZoomInfo ID 8996860]  |  ZoomInfo confirmed mobile (781) 607-2482 for James Clifford, callable.</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3171,11 @@
           <t>(877) 223-4800</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>(781) 882-8921</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Jake Gent</t>
@@ -3172,222 +3228,234 @@
           <t>radiusgrp.com</t>
         </is>
       </c>
-      <c r="W26" s="2" t="n"/>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>Same building as Miniter Group, different suite. Pair the stops. [ZoomInfo ID 371618282]</t>
+          <t>Same building as Miniter Group, different suite. Pair the stops. [ZoomInfo ID 371618282]  |  ZoomInfo confirmed direct dial (781) 882-8921 for Jake Gent, callable.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>NVNA and Hospice (Norwell VNA)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>120 Longwater Dr, Ste 104</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>(781) 659-2342</t>
         </is>
       </c>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Samuel Lutz</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>It Help Desk Technician</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Bj Snow (Chief Human Resources Officer)</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>Visiting nurse association and hospice, nonprofit</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>Clinicians in the field on mobile devices with PHI. Lead with HIPAA, device management and help desk.</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R27" s="2" t="inlineStr">
+      <c r="R27" s="4" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="S27" s="4" t="inlineStr">
         <is>
           <t>22797000</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>1920</t>
         </is>
       </c>
-      <c r="U27" s="2" t="n"/>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="U27" s="4" t="n"/>
+      <c r="V27" s="4" t="inlineStr">
         <is>
           <t>nvna.org</t>
         </is>
       </c>
-      <c r="W27" s="2" t="n"/>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>Nonprofit budget cycle. EHR uptime and clinician onboarding speed are real pains. [ZoomInfo ID 82658395]</t>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X27" s="5" t="inlineStr">
+        <is>
+          <t>Nonprofit budget cycle. EHR uptime and clinician onboarding speed are real pains. [ZoomInfo ID 82658395]  |  ZoomInfo matched Samuel Lutz but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>DIH Holding US (Hocoma)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>77 Accord Park Dr, Ste D1</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>(617) 871-2101</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Haile Mitiku</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>Jason Chen (Chief Executive Officer &amp; Chairman)</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>Rehab robotics and medtech, US HQ</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>Public medtech company with FDA documentation needs. Lead with compliance ready IT and security.</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S28" s="4" t="inlineStr">
         <is>
           <t>69573000</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr">
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="U28" s="2" t="n"/>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="U28" s="4" t="n"/>
+      <c r="V28" s="4" t="inlineStr">
         <is>
           <t>dih.com</t>
         </is>
       </c>
-      <c r="W28" s="2" t="n"/>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ listed. Hocoma brand runs from same office. [ZoomInfo ID 481121880]</t>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X28" s="5" t="inlineStr">
+        <is>
+          <t>NASDAQ listed. Hocoma brand runs from same office. [ZoomInfo ID 481121880]  |  ZoomInfo matched Haile Mitiku but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3505,11 @@
           <t>(800) 646-4837</t>
         </is>
       </c>
-      <c r="J29" s="2" t="n"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>(781) 982-3100</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
           <t>Wayne Brantley</t>
@@ -3490,108 +3562,116 @@
           <t>miniter.com</t>
         </is>
       </c>
-      <c r="W29" s="2" t="n"/>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>Same building as Radius. Two ICP financial accounts in one stop. [ZoomInfo ID 25117527]</t>
+          <t>Same building as Radius. Two ICP financial accounts in one stop. [ZoomInfo ID 25117527]  |  ZoomInfo confirmed direct dial (781) 982-3100 for Wayne Brantley, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Snow &amp; Jones</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>85 Accord Park Dr</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>(781) 878-3312</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>Danielle Jones (President)</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>Plumbing and HVAC wholesale distributor, HQ</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>Multi branch distributor on one ERP. Lead with branch connectivity, uptime and ransomware defense.</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr">
         <is>
           <t>14844000</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr">
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>1952</t>
         </is>
       </c>
-      <c r="U30" s="2" t="n"/>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U30" s="4" t="n"/>
+      <c r="V30" s="4" t="inlineStr">
         <is>
           <t>snowandjones.com</t>
         </is>
       </c>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t>7 locations run from here. [ZoomInfo ID 93767622]</t>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X30" s="5" t="inlineStr">
+        <is>
+          <t>7 locations run from here. [ZoomInfo ID 93767622]  |  ZoomInfo: both direct (508) 394-0911 ext. 223 and mobile for Danielle Jones are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3721,11 @@
           <t>(781) 871-4816</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>(617) 871-4816</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
@@ -3686,10 +3770,14 @@
           <t>airxchange.com</t>
         </is>
       </c>
-      <c r="W31" s="2" t="n"/>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>Rockland address but sits in the Accord Park corridor. Route with Norwell stops. [ZoomInfo ID 2935868]</t>
+          <t>Rockland address but sits in the Accord Park corridor. Route with Norwell stops. [ZoomInfo ID 2935868]  |  ZoomInfo confirmed both direct (617) 871-4816 and mobile (617) 974-6115 for Randall Steele, callable.</t>
         </is>
       </c>
     </row>
@@ -4604,96 +4692,100 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>South Shore Skin Center</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>75 Washington St, Ste 1</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>(781) 878-6495</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="inlineStr">
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n"/>
+      <c r="N41" s="4" t="n"/>
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>Dermatology practice and med spa</t>
         </is>
       </c>
-      <c r="P41" s="2" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>EHR uptime and HIPAA. Lead with a HIPAA security risk assessment, which insurers now expect.</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="S41" s="4" t="inlineStr">
         <is>
           <t>3100000</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="4" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="U41" s="2" t="n"/>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="U41" s="4" t="n"/>
+      <c r="V41" s="4" t="inlineStr">
         <is>
           <t>southshoreskincenter.com</t>
         </is>
       </c>
-      <c r="W41" s="2" t="n"/>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>Multi provider practice. Visit mid afternoon, never during morning patient rush. [ZoomInfo ID 227410374]</t>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X41" s="5" t="inlineStr">
+        <is>
+          <t>Multi provider practice. Visit mid afternoon, never during morning patient rush. [ZoomInfo ID 227410374]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -5723,7 +5815,11 @@
           <t>(781) 826-6371</t>
         </is>
       </c>
-      <c r="J52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>(781) 829-4609</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
           <t>Evan Moniz</t>
@@ -5776,108 +5872,116 @@
           <t>cushingcenters.org</t>
         </is>
       </c>
-      <c r="W52" s="2" t="n"/>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>Large campus on Rt 53. Ask for the business office. [ZoomInfo ID 30739950]</t>
+          <t>Large campus on Rt 53. Ask for the business office. [ZoomInfo ID 30739950]  |  ZoomInfo confirmed direct dial (781) 829-4609 for Evan Moniz, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Homestead Mortgage</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>427 Columbia Rd, Ste 114</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>(781) 924-5482</t>
         </is>
       </c>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+      <c r="M53" s="4" t="n"/>
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>Kimmie Miller (Owner)</t>
         </is>
       </c>
-      <c r="O53" s="2" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Mortgage lender</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>GLBA safeguards and loan officer laptops everywhere. Lead with compliance and device management.</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
+      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R53" s="4" t="inlineStr">
         <is>
           <t>82</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
+      <c r="S53" s="4" t="inlineStr">
         <is>
           <t>5328000</t>
         </is>
       </c>
-      <c r="T53" s="2" t="inlineStr">
+      <c r="T53" s="4" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U53" s="2" t="n"/>
-      <c r="V53" s="2" t="inlineStr">
+      <c r="U53" s="4" t="n"/>
+      <c r="V53" s="4" t="inlineStr">
         <is>
           <t>myhomesteadmortgage.com</t>
         </is>
       </c>
-      <c r="W53" s="2" t="n"/>
-      <c r="X53" s="3" t="inlineStr">
-        <is>
-          <t>Same building as Merrill Associates. [ZoomInfo ID 344599909]</t>
+      <c r="W53" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X53" s="5" t="inlineStr">
+        <is>
+          <t>Same building as Merrill Associates. [ZoomInfo ID 344599909]  |  ZoomInfo: mobile (801) 718-5467 for Kimmie Miller is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -6466,108 +6570,112 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>P.A. Landers</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>351 Winter St</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>(781) 826-8818</t>
         </is>
       </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="inlineStr">
         <is>
           <t>Anthony Emma</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="L60" s="4" t="inlineStr">
         <is>
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="M60" s="4" t="n"/>
+      <c r="N60" s="4" t="inlineStr">
         <is>
           <t>Joseph Durant (Chief Operating Officer)</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>Site development and paving contractor, HQ</t>
         </is>
       </c>
-      <c r="P60" s="2" t="inlineStr">
+      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>Big contractor, prime wire fraud target. Lead with email security and estimating uptime.</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="inlineStr">
+      <c r="Q60" s="4" t="inlineStr">
         <is>
           <t>ACTIVE ACCOUNT</t>
         </is>
       </c>
-      <c r="R60" s="2" t="inlineStr">
+      <c r="R60" s="4" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
+      <c r="S60" s="4" t="inlineStr">
         <is>
           <t>66695000</t>
         </is>
       </c>
-      <c r="T60" s="2" t="inlineStr">
+      <c r="T60" s="4" t="inlineStr">
         <is>
           <t>1978</t>
         </is>
       </c>
-      <c r="U60" s="2" t="n"/>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="U60" s="4" t="n"/>
+      <c r="V60" s="4" t="inlineStr">
         <is>
           <t>palanders.com</t>
         </is>
       </c>
-      <c r="W60" s="2" t="n"/>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>One of the biggest private employers based in Hanover. Active 5PT account. Do not cold pitch. Relationship and expansion visit only. [ZoomInfo ID 80937600]</t>
+      <c r="W60" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X60" s="5" t="inlineStr">
+        <is>
+          <t>One of the biggest private employers based in Hanover. Active 5PT account. Do not cold pitch. Relationship and expansion visit only. [ZoomInfo ID 80937600]  |  ZoomInfo: mobile (781) 385-1348 for Anthony Emma is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -6617,7 +6725,11 @@
           <t>(781) 878-5000</t>
         </is>
       </c>
-      <c r="J61" s="2" t="n"/>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>(781) 681-3289</t>
+        </is>
+      </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
           <t>Devin Melo</t>
@@ -6670,10 +6782,14 @@
           <t>buckleyonline.com</t>
         </is>
       </c>
-      <c r="W61" s="2" t="n"/>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>Biggest revenue target in Hanover on this list. [ZoomInfo ID 16239075]</t>
+          <t>Biggest revenue target in Hanover on this list. [ZoomInfo ID 16239075]  |  ZoomInfo confirmed direct dial (781) 681-3289 for Devin Melo, callable.</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6839,11 @@
           <t>(781) 826-9100</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>(781) 826-7833</t>
+        </is>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
           <t>Lisa Raasch</t>
@@ -6776,10 +6896,14 @@
           <t>srcmedical.com</t>
         </is>
       </c>
-      <c r="W62" s="2" t="n"/>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>Medical manufacturing is a priority vertical. [ZoomInfo ID 193593434]</t>
+          <t>Medical manufacturing is a priority vertical. [ZoomInfo ID 193593434]  |  ZoomInfo confirmed direct dial (781) 826-7833 for Lisa Raasch, callable.</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6953,11 @@
           <t>(781) 826-8801</t>
         </is>
       </c>
-      <c r="J63" s="2" t="n"/>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>(781) 826-8801</t>
+        </is>
+      </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
           <t>Daniel McClelland</t>
@@ -6882,222 +7010,234 @@
           <t>hapcoincorporated.com</t>
         </is>
       </c>
-      <c r="W63" s="2" t="n"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>Phone corrected from web. ZoomInfo listed an out of state number. [ZoomInfo ID 50678002]</t>
+          <t>Phone corrected from web. ZoomInfo listed an out of state number. [ZoomInfo ID 50678002]  |  ZoomInfo confirmed direct dial (781) 826-8801 for Daniel McClelland, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Gem Gravure</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>112 School St</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>(781) 878-0456</t>
         </is>
       </c>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>Matt Phung</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="4" t="inlineStr">
         <is>
           <t>IT Administrator</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="M64" s="4" t="n"/>
+      <c r="N64" s="4" t="inlineStr">
         <is>
           <t>Joseph Gemelli (Founder)</t>
         </is>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Wire marking inks and printing systems, HQ</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>Third generation manufacturer with global customers. Lead with security and production uptime.</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="inlineStr">
+      <c r="Q64" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="R64" s="4" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
+      <c r="S64" s="4" t="inlineStr">
         <is>
           <t>18507000</t>
         </is>
       </c>
-      <c r="T64" s="2" t="inlineStr">
+      <c r="T64" s="4" t="inlineStr">
         <is>
           <t>1952</t>
         </is>
       </c>
-      <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="inlineStr">
+      <c r="U64" s="4" t="n"/>
+      <c r="V64" s="4" t="inlineStr">
         <is>
           <t>gemgravure.com</t>
         </is>
       </c>
-      <c r="W64" s="2" t="n"/>
-      <c r="X64" s="3" t="inlineStr">
-        <is>
-          <t>West Hanover village, near Circuit St loop. [ZoomInfo ID 352771180]</t>
+      <c r="W64" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X64" s="5" t="inlineStr">
+        <is>
+          <t>West Hanover village, near Circuit St loop. [ZoomInfo ID 352771180]  |  ZoomInfo: mobile (617) 697-8970 for Matt Phung is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Cri-Tech (Daikin)</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>85 Winter St</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>(781) 826-5600</t>
         </is>
       </c>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="inlineStr">
         <is>
           <t>Richard Park</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="L65" s="4" t="inlineStr">
         <is>
           <t>Manager, Business Systems</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="inlineStr">
+      <c r="M65" s="4" t="n"/>
+      <c r="N65" s="4" t="n"/>
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>Specialty rubber compounds manufacturer</t>
         </is>
       </c>
-      <c r="P65" s="2" t="inlineStr">
+      <c r="P65" s="4" t="inlineStr">
         <is>
           <t>Daikin owned but locally run plant. Lead with co-managed support for site systems.</t>
         </is>
       </c>
-      <c r="Q65" s="2" t="inlineStr">
+      <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R65" s="2" t="inlineStr">
+      <c r="R65" s="4" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr">
+      <c r="S65" s="4" t="inlineStr">
         <is>
           <t>6341000</t>
         </is>
       </c>
-      <c r="T65" s="2" t="inlineStr">
+      <c r="T65" s="4" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr">
+      <c r="U65" s="4" t="inlineStr">
         <is>
           <t>Daikin Industries</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="V65" s="4" t="inlineStr">
         <is>
           <t>critechinc.com</t>
         </is>
       </c>
-      <c r="W65" s="2" t="n"/>
-      <c r="X65" s="3" t="inlineStr">
-        <is>
-          <t>Corporate IT may exist at Daikin America. Local plant manager still feels the pain. [ZoomInfo ID 32690370]</t>
+      <c r="W65" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X65" s="5" t="inlineStr">
+        <is>
+          <t>Corporate IT may exist at Daikin America. Local plant manager still feels the pain. [ZoomInfo ID 32690370]  |  ZoomInfo: both direct and mobile for Richard Park are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7953,11 @@
           <t>(781) 826-2393</t>
         </is>
       </c>
-      <c r="J73" s="2" t="n"/>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>(781) 924-3167</t>
+        </is>
+      </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
           <t>Jimmy Noel</t>
@@ -7866,104 +8010,112 @@
           <t>royalhealthgroup.com</t>
         </is>
       </c>
-      <c r="W73" s="2" t="n"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
-          <t>HQ decides for all facilities. Employee count spans the group. [ZoomInfo ID 44024049]</t>
+          <t>HQ decides for all facilities. Employee count spans the group. [ZoomInfo ID 44024049]  |  ZoomInfo confirmed direct dial (781) 924-3167 for Jimmy Noel, callable.</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>FMC Ice Sports</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>100 Schoosett St, Bldg 3</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>(888) 747-5283</t>
         </is>
       </c>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="J74" s="4" t="n"/>
+      <c r="K74" s="4" t="n"/>
+      <c r="L74" s="4" t="n"/>
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>Ice rink management company, HQ</t>
         </is>
       </c>
-      <c r="P74" s="2" t="inlineStr">
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>25 rinks on POS, scheduling and payment systems. Lead with multi site support and uptime.</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="inlineStr">
+      <c r="Q74" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R74" s="2" t="inlineStr">
+      <c r="R74" s="4" t="inlineStr">
         <is>
           <t>226</t>
         </is>
       </c>
-      <c r="S74" s="2" t="inlineStr">
+      <c r="S74" s="4" t="inlineStr">
         <is>
           <t>54426000</t>
         </is>
       </c>
-      <c r="T74" s="2" t="inlineStr">
+      <c r="T74" s="4" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
       </c>
-      <c r="U74" s="2" t="n"/>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="U74" s="4" t="n"/>
+      <c r="V74" s="4" t="inlineStr">
         <is>
           <t>fmcicesports.com</t>
         </is>
       </c>
-      <c r="W74" s="2" t="n"/>
-      <c r="X74" s="3" t="inlineStr">
-        <is>
-          <t>HQ office decides for all sites. Strong multi site play. [ZoomInfo ID 40865749]</t>
+      <c r="W74" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X74" s="5" t="inlineStr">
+        <is>
+          <t>HQ office decides for all sites. Strong multi site play. [ZoomInfo ID 40865749]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -8013,7 +8165,11 @@
           <t>(855) 784-2937</t>
         </is>
       </c>
-      <c r="J75" s="2" t="n"/>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>(781) 341-2222</t>
+        </is>
+      </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
           <t>Chris Geer</t>
@@ -8066,116 +8222,124 @@
           <t>thayerscale.com</t>
         </is>
       </c>
-      <c r="W75" s="2" t="n"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>Classic ICP manufacturer. [ZoomInfo ID 38076611]</t>
+          <t>Classic ICP manufacturer. [ZoomInfo ID 38076611]  |  ZoomInfo confirmed direct dial (781) 341-2222 for Chris Geer, callable.</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Nelco Products</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>22 Riverside Dr</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>(800) 346-3526</t>
         </is>
       </c>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="J76" s="4" t="n"/>
+      <c r="K76" s="4" t="inlineStr">
         <is>
           <t>Patrick Wong</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="4" t="inlineStr">
         <is>
           <t>Director, Information Technology &amp; Materials</t>
         </is>
       </c>
-      <c r="M76" s="2" t="n"/>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="inlineStr">
         <is>
           <t>Miriam Nelson (Owner)</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" s="4" t="inlineStr">
         <is>
           <t>Cable ties and wire management, distribution HQ</t>
         </is>
       </c>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="P76" s="4" t="inlineStr">
         <is>
           <t>E-commerce and warehouse ops. Lead with uptime, EDI reliability and security.</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="inlineStr">
+      <c r="Q76" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="R76" s="4" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr">
+      <c r="S76" s="4" t="inlineStr">
         <is>
           <t>37741000</t>
         </is>
       </c>
-      <c r="T76" s="2" t="inlineStr">
+      <c r="T76" s="4" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="U76" s="2" t="n"/>
-      <c r="V76" s="2" t="inlineStr">
+      <c r="U76" s="4" t="n"/>
+      <c r="V76" s="4" t="inlineStr">
         <is>
           <t>nelcoproducts.com</t>
         </is>
       </c>
-      <c r="W76" s="2" t="n"/>
-      <c r="X76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 71779517]</t>
+      <c r="W76" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X76" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 71779517]  |  ZoomInfo returned an email on the flextronics.com domain for Patrick Wong (no phone). VERIFY: he may have moved to Flextronics/Flex, or Nelco may now sit under that parent. Confirm before outreach.</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9891,11 @@
           <t>(781) 826-3138</t>
         </is>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>(781) 523-3213</t>
+        </is>
+      </c>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
       <c r="M92" s="2" t="n"/>
@@ -9772,108 +9940,116 @@
           <t>tkasphalt.com</t>
         </is>
       </c>
-      <c r="W92" s="2" t="n"/>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X92" s="3" t="inlineStr">
         <is>
-          <t>One of the largest paving firms in New England. [ZoomInfo ID 184991889]</t>
+          <t>One of the largest paving firms in New England. [ZoomInfo ID 184991889]  |  ZoomInfo confirmed direct dial (781) 523-3213 for Peter Cleary, callable.</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Cape Cod Lumber</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>Abington</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>225 Groveland St</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>02351</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t>(781) 878-0715</t>
         </is>
       </c>
-      <c r="J93" s="2" t="n"/>
-      <c r="K93" s="2" t="n"/>
-      <c r="L93" s="2" t="n"/>
-      <c r="M93" s="2" t="n"/>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
+      <c r="L93" s="4" t="n"/>
+      <c r="M93" s="4" t="n"/>
+      <c r="N93" s="4" t="inlineStr">
         <is>
           <t>Thomas McManus (President)</t>
         </is>
       </c>
-      <c r="O93" s="2" t="inlineStr">
+      <c r="O93" s="4" t="inlineStr">
         <is>
           <t>Independent lumber yard and building products</t>
         </is>
       </c>
-      <c r="P93" s="2" t="inlineStr">
+      <c r="P93" s="4" t="inlineStr">
         <is>
           <t>POS, inventory and delivery ops on one system. Lead with uptime and ransomware defense.</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr">
+      <c r="Q93" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R93" s="2" t="inlineStr">
+      <c r="R93" s="4" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="S93" s="2" t="inlineStr">
+      <c r="S93" s="4" t="inlineStr">
         <is>
           <t>27457000</t>
         </is>
       </c>
-      <c r="T93" s="2" t="inlineStr">
+      <c r="T93" s="4" t="inlineStr">
         <is>
           <t>1958</t>
         </is>
       </c>
-      <c r="U93" s="2" t="n"/>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="U93" s="4" t="n"/>
+      <c r="V93" s="4" t="inlineStr">
         <is>
           <t>capecodlumber.com</t>
         </is>
       </c>
-      <c r="W93" s="2" t="n"/>
-      <c r="X93" s="3" t="inlineStr">
-        <is>
-          <t>Family owned. Decision makers on site. [ZoomInfo ID 20517658]</t>
+      <c r="W93" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X93" s="5" t="inlineStr">
+        <is>
+          <t>Family owned. Decision makers on site. [ZoomInfo ID 20517658]  |  ZoomInfo: mobile (508) 847-4666 for Thomas McManus is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -10940,112 +11116,116 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>South Shore Bank</t>
         </is>
       </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Weymouth</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>1530 Main St</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>02190</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>(800) 419-1700</t>
         </is>
       </c>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="J105" s="4" t="n"/>
+      <c r="K105" s="4" t="inlineStr">
         <is>
           <t>Lynn Tempesta</t>
         </is>
       </c>
-      <c r="L105" s="2" t="inlineStr">
+      <c r="L105" s="4" t="inlineStr">
         <is>
           <t>Vice President and Information Technology Operations Ma...</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="2" t="inlineStr">
+      <c r="M105" s="4" t="n"/>
+      <c r="N105" s="4" t="inlineStr">
         <is>
           <t>James Dunphy (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O105" s="2" t="inlineStr">
+      <c r="O105" s="4" t="inlineStr">
         <is>
           <t>Community bank, main office</t>
         </is>
       </c>
-      <c r="P105" s="2" t="inlineStr">
+      <c r="P105" s="4" t="inlineStr">
         <is>
           <t>Exam and vendor management pressure with lean internal IT. Lead with vCISO, compliance alignment and MDR.</t>
         </is>
       </c>
-      <c r="Q105" s="2" t="inlineStr">
+      <c r="Q105" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R105" s="2" t="inlineStr">
+      <c r="R105" s="4" t="inlineStr">
         <is>
           <t>221</t>
         </is>
       </c>
-      <c r="S105" s="2" t="inlineStr">
+      <c r="S105" s="4" t="inlineStr">
         <is>
           <t>110640000</t>
         </is>
       </c>
-      <c r="T105" s="2" t="inlineStr">
+      <c r="T105" s="4" t="inlineStr">
         <is>
           <t>1889</t>
         </is>
       </c>
-      <c r="U105" s="2" t="inlineStr">
+      <c r="U105" s="4" t="inlineStr">
         <is>
           <t>Merging with Dedham Savings</t>
         </is>
       </c>
-      <c r="V105" s="2" t="inlineStr">
+      <c r="V105" s="4" t="inlineStr">
         <is>
           <t>southshorebank.com</t>
         </is>
       </c>
-      <c r="W105" s="2" t="n"/>
-      <c r="X105" s="3" t="inlineStr">
-        <is>
-          <t>Merger integration is an IT trigger. Bank flagged as Dedham Savings affiliate. [ZoomInfo ID 35750110]</t>
+      <c r="W105" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X105" s="5" t="inlineStr">
+        <is>
+          <t>Merger integration is an IT trigger. Bank flagged as Dedham Savings affiliate. [ZoomInfo ID 35750110]  |  ZoomInfo weak match (company only, no personal data confirmed) for Lynn Tempesta this pass. Prior intel stands: desk line (781) 682-3269, mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11275,11 @@
           <t>(781) 335-5200</t>
         </is>
       </c>
-      <c r="J106" s="2" t="n"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>(781) 607-3366</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
           <t>Karen Roche</t>
@@ -11144,10 +11328,14 @@
           <t>electroswitch.com</t>
         </is>
       </c>
-      <c r="W106" s="2" t="n"/>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X106" s="3" t="inlineStr">
         <is>
-          <t>Defense customers mean a CMMC door opener. [ZoomInfo ID 12681815]</t>
+          <t>Defense customers mean a CMMC door opener. [ZoomInfo ID 12681815]  |  ZoomInfo confirmed direct dial (781) 607-3366 for Karen Roche, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -11197,7 +11385,11 @@
           <t>(781) 796-6050</t>
         </is>
       </c>
-      <c r="J107" s="2" t="n"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>(781) 682-4438</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
           <t>Margaret Ruuska</t>
@@ -11254,10 +11446,14 @@
           <t>coastalheritagebank.com</t>
         </is>
       </c>
-      <c r="W107" s="2" t="n"/>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X107" s="3" t="inlineStr">
         <is>
-          <t>Listed as merged into MountainOne. Verify branding before visiting. [ZoomInfo ID 375237867]</t>
+          <t>Listed as merged into MountainOne. Verify branding before visiting. [ZoomInfo ID 375237867]  |  ZoomInfo confirmed direct dial (781) 682-4438 and mobile (781) 796-6009 for Margaret Ruuska, both callable.</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11503,11 @@
           <t>(781) 383-6800</t>
         </is>
       </c>
-      <c r="J108" s="2" t="n"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>(781) 803-2786 ext. 223</t>
+        </is>
+      </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
           <t>Phillip Joy</t>
@@ -11356,622 +11556,650 @@
           <t>healthcaresouth.com</t>
         </is>
       </c>
-      <c r="W108" s="2" t="n"/>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X108" s="3" t="inlineStr">
         <is>
-          <t>Multi practice group. HIPAA and EHR uptime. [ZoomInfo ID 54415058]</t>
+          <t>Multi practice group. HIPAA and EHR uptime. [ZoomInfo ID 54415058]  |  ZoomInfo confirmed direct dial (781) 803-2786 ext. 223 for Phillip Joy, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Massa Products</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F109" s="4" t="inlineStr">
         <is>
           <t>280 Lincoln St</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>(781) 749-4800</t>
         </is>
       </c>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="J109" s="4" t="n"/>
+      <c r="K109" s="4" t="inlineStr">
         <is>
           <t>James Hall</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="L109" s="4" t="inlineStr">
         <is>
           <t>Senior Software Systems Engineer &amp; Director &amp; Electrica...</t>
         </is>
       </c>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="M109" s="4" t="n"/>
+      <c r="N109" s="4" t="inlineStr">
         <is>
           <t>Donald Massa (Chief Technical Officer &amp; Chairman)</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr">
+      <c r="O109" s="4" t="inlineStr">
         <is>
           <t>Sonar and ultrasonic transducer manufacturer</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
+      <c r="P109" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="Q109" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="R109" s="4" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="S109" s="2" t="inlineStr">
+      <c r="S109" s="4" t="inlineStr">
         <is>
           <t>19426000</t>
         </is>
       </c>
-      <c r="T109" s="2" t="inlineStr">
+      <c r="T109" s="4" t="inlineStr">
         <is>
           <t>1945</t>
         </is>
       </c>
-      <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="inlineStr">
+      <c r="U109" s="4" t="n"/>
+      <c r="V109" s="4" t="inlineStr">
         <is>
           <t>massa.com</t>
         </is>
       </c>
-      <c r="W109" s="2" t="n"/>
-      <c r="X109" s="3" t="inlineStr">
-        <is>
-          <t>Defense supplier. Ask about CMMC prep. [ZoomInfo ID 46614387]</t>
+      <c r="W109" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X109" s="5" t="inlineStr">
+        <is>
+          <t>Defense supplier. Ask about CMMC prep. [ZoomInfo ID 46614387]  |  ZoomInfo matched James Hall but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>Hingham Institution for Savings</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F110" s="4" t="inlineStr">
         <is>
           <t>55 Main St</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>(781) 783-1798</t>
         </is>
       </c>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="J110" s="4" t="n"/>
+      <c r="K110" s="4" t="inlineStr">
         <is>
           <t>Daniel Bagley</t>
         </is>
       </c>
-      <c r="L110" s="2" t="inlineStr">
+      <c r="L110" s="4" t="inlineStr">
         <is>
           <t>Vice President, Chief Information Officer</t>
         </is>
       </c>
-      <c r="M110" s="2" t="n"/>
-      <c r="N110" s="2" t="inlineStr">
+      <c r="M110" s="4" t="n"/>
+      <c r="N110" s="4" t="inlineStr">
         <is>
           <t>Patrick Gaughen (President &amp; Chief Operating Officer)</t>
         </is>
       </c>
-      <c r="O110" s="2" t="inlineStr">
+      <c r="O110" s="4" t="inlineStr">
         <is>
           <t>Independent bank, HQ</t>
         </is>
       </c>
-      <c r="P110" s="2" t="inlineStr">
+      <c r="P110" s="4" t="inlineStr">
         <is>
           <t>Exam and vendor management pressure with lean internal IT. Lead with vCISO, compliance alignment and MDR.</t>
         </is>
       </c>
-      <c r="Q110" s="2" t="inlineStr">
+      <c r="Q110" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
+      <c r="R110" s="4" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="S110" s="2" t="inlineStr">
+      <c r="S110" s="4" t="inlineStr">
         <is>
           <t>54947000</t>
         </is>
       </c>
-      <c r="T110" s="2" t="inlineStr">
+      <c r="T110" s="4" t="inlineStr">
         <is>
           <t>1834</t>
         </is>
       </c>
-      <c r="U110" s="2" t="n"/>
-      <c r="V110" s="2" t="inlineStr">
+      <c r="U110" s="4" t="n"/>
+      <c r="V110" s="4" t="inlineStr">
         <is>
           <t>hinghamsavings.com</t>
         </is>
       </c>
-      <c r="W110" s="2" t="n"/>
-      <c r="X110" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 31361066]</t>
+      <c r="W110" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 31361066]  |  ZoomInfo: mobile (617) 240-5885 for Daniel Bagley is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Hingham Lumber</t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>Cohasset</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" s="4" t="inlineStr">
         <is>
           <t>165 Chief Justice Cushing Hwy</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G111" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>02025</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>(781) 749-4200</t>
         </is>
       </c>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="inlineStr">
+      <c r="J111" s="4" t="n"/>
+      <c r="K111" s="4" t="n"/>
+      <c r="L111" s="4" t="n"/>
+      <c r="M111" s="4" t="n"/>
+      <c r="N111" s="4" t="inlineStr">
         <is>
           <t>William McNulty (Founder)</t>
         </is>
       </c>
-      <c r="O111" s="2" t="inlineStr">
+      <c r="O111" s="4" t="inlineStr">
         <is>
           <t>Independent lumber yard</t>
         </is>
       </c>
-      <c r="P111" s="2" t="inlineStr">
+      <c r="P111" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q111" s="2" t="inlineStr">
+      <c r="Q111" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R111" s="2" t="inlineStr">
+      <c r="R111" s="4" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="S111" s="2" t="inlineStr">
+      <c r="S111" s="4" t="inlineStr">
         <is>
           <t>19898000</t>
         </is>
       </c>
-      <c r="T111" s="2" t="inlineStr">
+      <c r="T111" s="4" t="inlineStr">
         <is>
           <t>1947</t>
         </is>
       </c>
-      <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="inlineStr">
+      <c r="U111" s="4" t="n"/>
+      <c r="V111" s="4" t="inlineStr">
         <is>
           <t>hinghamlumber.com</t>
         </is>
       </c>
-      <c r="W111" s="2" t="n"/>
-      <c r="X111" s="3" t="inlineStr">
-        <is>
-          <t>Family owned. Same 3A run as Healthcare South. [ZoomInfo ID 31361067]</t>
+      <c r="W111" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X111" s="5" t="inlineStr">
+        <is>
+          <t>Family owned. Same 3A run as Healthcare South. [ZoomInfo ID 31361067]  |  ZoomInfo matched William McNulty but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>Dynavac</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" s="4" t="inlineStr">
         <is>
           <t>110 Industrial Park Rd</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="I112" s="4" t="inlineStr">
         <is>
           <t>(781) 740-8600</t>
         </is>
       </c>
-      <c r="J112" s="2" t="n"/>
-      <c r="K112" s="2" t="n"/>
-      <c r="L112" s="2" t="n"/>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="2" t="inlineStr">
+      <c r="J112" s="4" t="n"/>
+      <c r="K112" s="4" t="n"/>
+      <c r="L112" s="4" t="n"/>
+      <c r="M112" s="4" t="n"/>
+      <c r="N112" s="4" t="inlineStr">
         <is>
           <t>Joel Smolka (Vice President and General Manager)</t>
         </is>
       </c>
-      <c r="O112" s="2" t="inlineStr">
+      <c r="O112" s="4" t="inlineStr">
         <is>
           <t>Vacuum chamber systems manufacturer</t>
         </is>
       </c>
-      <c r="P112" s="2" t="inlineStr">
+      <c r="P112" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q112" s="2" t="inlineStr">
+      <c r="Q112" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R112" s="2" t="inlineStr">
+      <c r="R112" s="4" t="inlineStr">
         <is>
           <t>81</t>
         </is>
       </c>
-      <c r="S112" s="2" t="inlineStr">
+      <c r="S112" s="4" t="inlineStr">
         <is>
           <t>22657000</t>
         </is>
       </c>
-      <c r="T112" s="2" t="inlineStr">
+      <c r="T112" s="4" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="U112" s="2" t="inlineStr">
+      <c r="U112" s="4" t="inlineStr">
         <is>
           <t>Schunk GmbH</t>
         </is>
       </c>
-      <c r="V112" s="2" t="inlineStr">
+      <c r="V112" s="4" t="inlineStr">
         <is>
           <t>dynavac.com</t>
         </is>
       </c>
-      <c r="W112" s="2" t="n"/>
-      <c r="X112" s="3" t="inlineStr">
-        <is>
-          <t>German parent, locally run plant. [ZoomInfo ID 25103548]</t>
+      <c r="W112" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X112" s="5" t="inlineStr">
+        <is>
+          <t>German parent, locally run plant. [ZoomInfo ID 25103548]  |  ZoomInfo: mobile (339) 788-0470 for Joel Smolka is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>South Shore Orthopedics</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F113" s="4" t="inlineStr">
         <is>
           <t>2 Pond Park Rd Ste 102</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>(781) 337-5555</t>
         </is>
       </c>
-      <c r="J113" s="2" t="n"/>
-      <c r="K113" s="2" t="n"/>
-      <c r="L113" s="2" t="n"/>
-      <c r="M113" s="2" t="n"/>
-      <c r="N113" s="2" t="n"/>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="J113" s="4" t="n"/>
+      <c r="K113" s="4" t="n"/>
+      <c r="L113" s="4" t="n"/>
+      <c r="M113" s="4" t="n"/>
+      <c r="N113" s="4" t="n"/>
+      <c r="O113" s="4" t="inlineStr">
         <is>
           <t>Orthopedic practice</t>
         </is>
       </c>
-      <c r="P113" s="2" t="inlineStr">
+      <c r="P113" s="4" t="inlineStr">
         <is>
           <t>PHI and EHR uptime on a lean team. Lead with a HIPAA security risk assessment.</t>
         </is>
       </c>
-      <c r="Q113" s="2" t="inlineStr">
+      <c r="Q113" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R113" s="2" t="inlineStr">
+      <c r="R113" s="4" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="S113" s="2" t="inlineStr">
+      <c r="S113" s="4" t="inlineStr">
         <is>
           <t>3176000</t>
         </is>
       </c>
-      <c r="T113" s="2" t="inlineStr">
+      <c r="T113" s="4" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U113" s="2" t="n"/>
-      <c r="V113" s="2" t="inlineStr">
+      <c r="U113" s="4" t="n"/>
+      <c r="V113" s="4" t="inlineStr">
         <is>
           <t>southshoreorthopedics.com</t>
         </is>
       </c>
-      <c r="W113" s="2" t="n"/>
-      <c r="X113" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 73893756]</t>
+      <c r="W113" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X113" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 73893756]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>AJA International</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>Scituate</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F114" s="4" t="inlineStr">
         <is>
           <t>809 Country Way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>02066</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="I114" s="4" t="inlineStr">
         <is>
           <t>(781) 545-7365</t>
         </is>
       </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="J114" s="4" t="n"/>
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Lin Sandar</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr">
+      <c r="L114" s="4" t="inlineStr">
         <is>
           <t>System Engineer</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
-      <c r="N114" s="2" t="inlineStr">
+      <c r="M114" s="4" t="n"/>
+      <c r="N114" s="4" t="inlineStr">
         <is>
           <t>William Hale (Founder)</t>
         </is>
       </c>
-      <c r="O114" s="2" t="inlineStr">
+      <c r="O114" s="4" t="inlineStr">
         <is>
           <t>Thin film deposition systems manufacturer</t>
         </is>
       </c>
-      <c r="P114" s="2" t="inlineStr">
+      <c r="P114" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q114" s="2" t="inlineStr">
+      <c r="Q114" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R114" s="2" t="inlineStr">
+      <c r="R114" s="4" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr">
+      <c r="S114" s="4" t="inlineStr">
         <is>
           <t>17109000</t>
         </is>
       </c>
-      <c r="T114" s="2" t="inlineStr">
+      <c r="T114" s="4" t="inlineStr">
         <is>
           <t>1989</t>
         </is>
       </c>
-      <c r="U114" s="2" t="n"/>
-      <c r="V114" s="2" t="inlineStr">
+      <c r="U114" s="4" t="n"/>
+      <c r="V114" s="4" t="inlineStr">
         <is>
           <t>ajaint.com</t>
         </is>
       </c>
-      <c r="W114" s="2" t="n"/>
-      <c r="X114" s="3" t="inlineStr">
-        <is>
-          <t>World class instrument maker in your home town. [ZoomInfo ID 2379476]</t>
+      <c r="W114" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X114" s="5" t="inlineStr">
+        <is>
+          <t>World class instrument maker in your home town. [ZoomInfo ID 2379476]  |  ZoomInfo matched Lin Sandar but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -13070,108 +13298,112 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>Bay State Milling</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" s="4" t="inlineStr">
         <is>
           <t>100 Congress St Ste 2</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H126" s="4" t="inlineStr">
         <is>
           <t>02169</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="I126" s="4" t="inlineStr">
         <is>
           <t>(800) 553-5687</t>
         </is>
       </c>
-      <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="J126" s="4" t="n"/>
+      <c r="K126" s="4" t="inlineStr">
         <is>
           <t>Phillip Murphy</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="L126" s="4" t="inlineStr">
         <is>
           <t>Director, Information Technology &amp; Development</t>
         </is>
       </c>
-      <c r="M126" s="2" t="n"/>
-      <c r="N126" s="2" t="inlineStr">
+      <c r="M126" s="4" t="n"/>
+      <c r="N126" s="4" t="inlineStr">
         <is>
           <t>Alain Hanna (Chief Financial Officer)</t>
         </is>
       </c>
-      <c r="O126" s="2" t="inlineStr">
+      <c r="O126" s="4" t="inlineStr">
         <is>
           <t>Flour and grain milling, HQ since 1899</t>
         </is>
       </c>
-      <c r="P126" s="2" t="inlineStr">
+      <c r="P126" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="inlineStr">
+      <c r="Q126" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R126" s="2" t="inlineStr">
+      <c r="R126" s="4" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="S126" s="2" t="inlineStr">
+      <c r="S126" s="4" t="inlineStr">
         <is>
           <t>143434000</t>
         </is>
       </c>
-      <c r="T126" s="2" t="inlineStr">
+      <c r="T126" s="4" t="inlineStr">
         <is>
           <t>1899</t>
         </is>
       </c>
-      <c r="U126" s="2" t="n"/>
-      <c r="V126" s="2" t="inlineStr">
+      <c r="U126" s="4" t="n"/>
+      <c r="V126" s="4" t="inlineStr">
         <is>
           <t>baystatemilling.com</t>
         </is>
       </c>
-      <c r="W126" s="2" t="n"/>
-      <c r="X126" s="3" t="inlineStr">
-        <is>
-          <t>HQ office decides for plants nationwide. [ZoomInfo ID 8587966]</t>
+      <c r="W126" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X126" s="5" t="inlineStr">
+        <is>
+          <t>HQ office decides for plants nationwide. [ZoomInfo ID 8587966]  |  ZoomInfo: mobile (270) 222-0317 for Phillip Murphy is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -13221,7 +13453,11 @@
           <t>(617) 376-3000</t>
         </is>
       </c>
-      <c r="J127" s="2" t="n"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>(503) 691-4139</t>
+        </is>
+      </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
           <t>Kim Shaw</t>
@@ -13274,10 +13510,14 @@
           <t>manetchc.org</t>
         </is>
       </c>
-      <c r="W127" s="2" t="n"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X127" s="3" t="inlineStr">
         <is>
-          <t>Was on your 2026 target list. Admin office visit, afternoons. [ZoomInfo ID 52348112]</t>
+          <t>Was on your 2026 target list. Admin office visit, afternoons. [ZoomInfo ID 52348112]  |  ZoomInfo: direct line for Kim Shaw is flagged Do Not Call; mobile (503) 691-4139 is callable.</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13567,11 @@
           <t>(617) 770-5100</t>
         </is>
       </c>
-      <c r="J128" s="2" t="n"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>(617) 472-8770</t>
+        </is>
+      </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
           <t>Michael Andrade</t>
@@ -13376,10 +13620,14 @@
           <t>newenglandmutual.com</t>
         </is>
       </c>
-      <c r="W128" s="2" t="n"/>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X128" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 57574629]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 57574629]  |  ZoomInfo confirmed both direct (617) 472-8770 and mobile (617) 770-5127 for Michael Andrade, callable.</t>
         </is>
       </c>
     </row>
@@ -13429,7 +13677,11 @@
           <t>(617) 471-7171</t>
         </is>
       </c>
-      <c r="J129" s="2" t="n"/>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>(617) 330-5702</t>
+        </is>
+      </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
           <t>Jason Brudnick</t>
@@ -13482,10 +13734,14 @@
           <t>xsbrokers.com</t>
         </is>
       </c>
-      <c r="W129" s="2" t="n"/>
+      <c r="W129" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 43008409]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 43008409]  |  ZoomInfo confirmed direct dial (617) 330-5702 for Jason Brudnick, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13791,11 @@
           <t>(617) 472-9200</t>
         </is>
       </c>
-      <c r="J130" s="2" t="n"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>(617) 845-1126</t>
+        </is>
+      </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
           <t>John Piasecki</t>
@@ -13592,10 +13852,14 @@
           <t>twinriverstechnologies.com</t>
         </is>
       </c>
-      <c r="W130" s="2" t="n"/>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X130" s="3" t="inlineStr">
         <is>
-          <t>Named IT director on file. Parent overseas, plant IT local. [ZoomInfo ID 39175210]</t>
+          <t>Named IT director on file. Parent overseas, plant IT local. [ZoomInfo ID 39175210]  |  ZoomInfo confirmed direct dial (617) 845-1126 for John Piasecki, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -15028,394 +15292,410 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>CDF Corporation</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" s="4" t="inlineStr">
         <is>
           <t>Plymouth</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" s="4" t="inlineStr">
         <is>
           <t>77 Industrial Park Rd</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>02360</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="I145" s="4" t="inlineStr">
         <is>
           <t>(800) 443-1920</t>
         </is>
       </c>
-      <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="J145" s="4" t="n"/>
+      <c r="K145" s="4" t="inlineStr">
         <is>
           <t>Alex Ivkovic</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
+      <c r="L145" s="4" t="inlineStr">
         <is>
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M145" s="2" t="n"/>
-      <c r="N145" s="2" t="inlineStr">
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="inlineStr">
         <is>
           <t>Joseph Sullivan (President)</t>
         </is>
       </c>
-      <c r="O145" s="2" t="inlineStr">
+      <c r="O145" s="4" t="inlineStr">
         <is>
           <t>Industrial packaging and liners manufacturer</t>
         </is>
       </c>
-      <c r="P145" s="2" t="inlineStr">
+      <c r="P145" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q145" s="2" t="inlineStr">
+      <c r="Q145" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R145" s="2" t="inlineStr">
+      <c r="R145" s="4" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="S145" s="2" t="inlineStr">
+      <c r="S145" s="4" t="inlineStr">
         <is>
           <t>33885000</t>
         </is>
       </c>
-      <c r="T145" s="2" t="inlineStr">
+      <c r="T145" s="4" t="inlineStr">
         <is>
           <t>1971</t>
         </is>
       </c>
-      <c r="U145" s="2" t="n"/>
-      <c r="V145" s="2" t="inlineStr">
+      <c r="U145" s="4" t="n"/>
+      <c r="V145" s="4" t="inlineStr">
         <is>
           <t>cdf1.com</t>
         </is>
       </c>
-      <c r="W145" s="2" t="n"/>
-      <c r="X145" s="3" t="inlineStr">
-        <is>
-          <t>Plymouth Industrial Park anchor. [ZoomInfo ID 22089378]</t>
+      <c r="W145" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X145" s="5" t="inlineStr">
+        <is>
+          <t>Plymouth Industrial Park anchor. [ZoomInfo ID 22089378]  |  ZoomInfo: mobile (508) 667-6556 for Alex Ivkovic is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>Welch Healthcare &amp; Retirement Group</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E146" s="4" t="inlineStr">
         <is>
           <t>Duxbury</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F146" s="4" t="inlineStr">
         <is>
           <t>290 Kingstown Way</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G146" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H146" s="4" t="inlineStr">
         <is>
           <t>02332</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="I146" s="4" t="inlineStr">
         <is>
           <t>(781) 585-7136</t>
         </is>
       </c>
-      <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="n"/>
-      <c r="L146" s="2" t="n"/>
-      <c r="M146" s="2" t="n"/>
-      <c r="N146" s="2" t="n"/>
-      <c r="O146" s="2" t="inlineStr">
+      <c r="J146" s="4" t="n"/>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="inlineStr">
         <is>
           <t>Family owned senior living group, HQ</t>
         </is>
       </c>
-      <c r="P146" s="2" t="inlineStr">
+      <c r="P146" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q146" s="2" t="inlineStr">
+      <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R146" s="2" t="inlineStr">
+      <c r="R146" s="4" t="inlineStr">
         <is>
           <t>502</t>
         </is>
       </c>
-      <c r="S146" s="2" t="inlineStr">
+      <c r="S146" s="4" t="inlineStr">
         <is>
           <t>33533000</t>
         </is>
       </c>
-      <c r="T146" s="2" t="inlineStr">
+      <c r="T146" s="4" t="inlineStr">
         <is>
           <t>1949</t>
         </is>
       </c>
-      <c r="U146" s="2" t="n"/>
-      <c r="V146" s="2" t="inlineStr">
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="inlineStr">
         <is>
           <t>welchhrg.com</t>
         </is>
       </c>
-      <c r="W146" s="2" t="n"/>
-      <c r="X146" s="3" t="inlineStr">
-        <is>
-          <t>HQ decides for all communities. HIPAA and nurse call uptime. [ZoomInfo ID 43045537]</t>
+      <c r="W146" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X146" s="5" t="inlineStr">
+        <is>
+          <t>HQ decides for all communities. HIPAA and nurse call uptime. [ZoomInfo ID 43045537]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
         <is>
           <t>Suncor Stainless / Atlantis Rail</t>
         </is>
       </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="D147" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E147" s="4" t="inlineStr">
         <is>
           <t>Plymouth</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F147" s="4" t="inlineStr">
         <is>
           <t>70 Armstrong Rd</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G147" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>02360</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>(508) 732-9191</t>
         </is>
       </c>
-      <c r="J147" s="2" t="n"/>
-      <c r="K147" s="2" t="n"/>
-      <c r="L147" s="2" t="n"/>
-      <c r="M147" s="2" t="n"/>
-      <c r="N147" s="2" t="n"/>
-      <c r="O147" s="2" t="inlineStr">
+      <c r="J147" s="4" t="n"/>
+      <c r="K147" s="4" t="n"/>
+      <c r="L147" s="4" t="n"/>
+      <c r="M147" s="4" t="n"/>
+      <c r="N147" s="4" t="n"/>
+      <c r="O147" s="4" t="inlineStr">
         <is>
           <t>Stainless hardware and railing manufacturer</t>
         </is>
       </c>
-      <c r="P147" s="2" t="inlineStr">
+      <c r="P147" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q147" s="2" t="inlineStr">
+      <c r="Q147" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R147" s="2" t="inlineStr">
+      <c r="R147" s="4" t="inlineStr">
         <is>
           <t>171</t>
         </is>
       </c>
-      <c r="S147" s="2" t="inlineStr">
+      <c r="S147" s="4" t="inlineStr">
         <is>
           <t>48765000</t>
         </is>
       </c>
-      <c r="T147" s="2" t="inlineStr">
+      <c r="T147" s="4" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="U147" s="2" t="n"/>
-      <c r="V147" s="2" t="inlineStr">
+      <c r="U147" s="4" t="n"/>
+      <c r="V147" s="4" t="inlineStr">
         <is>
           <t>suncorstainless.com</t>
         </is>
       </c>
-      <c r="W147" s="2" t="n"/>
-      <c r="X147" s="3" t="inlineStr">
-        <is>
-          <t>Two brands, one building. One stop covers both. [ZoomInfo ID 11442642]</t>
+      <c r="W147" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X147" s="5" t="inlineStr">
+        <is>
+          <t>Two brands, one building. One stop covers both. [ZoomInfo ID 11442642]  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Kirwan Surgical Products</t>
         </is>
       </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="D148" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E148" s="4" t="inlineStr">
         <is>
           <t>Marshfield</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F148" s="4" t="inlineStr">
         <is>
           <t>180 Enterprise Dr</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G148" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H148" s="4" t="inlineStr">
         <is>
           <t>02050</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>(781) 834-9500</t>
         </is>
       </c>
-      <c r="J148" s="2" t="n"/>
-      <c r="K148" s="2" t="n"/>
-      <c r="L148" s="2" t="n"/>
-      <c r="M148" s="2" t="n"/>
-      <c r="N148" s="2" t="inlineStr">
+      <c r="J148" s="4" t="n"/>
+      <c r="K148" s="4" t="n"/>
+      <c r="L148" s="4" t="n"/>
+      <c r="M148" s="4" t="n"/>
+      <c r="N148" s="4" t="inlineStr">
         <is>
           <t>Jean Kirwan (Founder)</t>
         </is>
       </c>
-      <c r="O148" s="2" t="inlineStr">
+      <c r="O148" s="4" t="inlineStr">
         <is>
           <t>Surgical instruments manufacturer</t>
         </is>
       </c>
-      <c r="P148" s="2" t="inlineStr">
+      <c r="P148" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q148" s="2" t="inlineStr">
+      <c r="Q148" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R148" s="2" t="inlineStr">
+      <c r="R148" s="4" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="S148" s="2" t="inlineStr">
+      <c r="S148" s="4" t="inlineStr">
         <is>
           <t>26238000</t>
         </is>
       </c>
-      <c r="T148" s="2" t="inlineStr">
+      <c r="T148" s="4" t="inlineStr">
         <is>
           <t>1979</t>
         </is>
       </c>
-      <c r="U148" s="2" t="n"/>
-      <c r="V148" s="2" t="inlineStr">
+      <c r="U148" s="4" t="n"/>
+      <c r="V148" s="4" t="inlineStr">
         <is>
           <t>ksp.com</t>
         </is>
       </c>
-      <c r="W148" s="2" t="n"/>
-      <c r="X148" s="3" t="inlineStr">
-        <is>
-          <t>FDA quality system. Enterprise Dr pairs with United Elevator. [ZoomInfo ID 67520122]</t>
+      <c r="W148" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X148" s="5" t="inlineStr">
+        <is>
+          <t>FDA quality system. Enterprise Dr pairs with United Elevator. [ZoomInfo ID 67520122]  |  ZoomInfo matched Jean Kirwan but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -15465,7 +15745,11 @@
           <t>(508) 732-7200</t>
         </is>
       </c>
-      <c r="J149" s="2" t="n"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>(781) 724-0677</t>
+        </is>
+      </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
           <t>Tim Stevenson</t>
@@ -15518,10 +15802,14 @@
           <t>vptec.com</t>
         </is>
       </c>
-      <c r="W149" s="2" t="n"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X149" s="3" t="inlineStr">
         <is>
-          <t>PE owned, locally run. [ZoomInfo ID 126091458]</t>
+          <t>PE owned, locally run. [ZoomInfo ID 126091458]  |  ZoomInfo confirmed mobile (781) 724-0677 for Tim Stevenson, callable.</t>
         </is>
       </c>
     </row>
@@ -15571,7 +15859,11 @@
           <t>(781) 934-2400</t>
         </is>
       </c>
-      <c r="J150" s="2" t="n"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>(508) 298-6785</t>
+        </is>
+      </c>
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
       <c r="M150" s="2" t="n"/>
@@ -15616,10 +15908,14 @@
           <t>pbortho.com</t>
         </is>
       </c>
-      <c r="W150" s="2" t="n"/>
+      <c r="W150" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X150" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 353633068]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 353633068]  |  ZoomInfo confirmed direct dial (508) 298-6785 for Scott Oliver, callable.</t>
         </is>
       </c>
     </row>
@@ -16844,108 +17140,112 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>Double E Group</t>
         </is>
       </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
         <is>
           <t>West Bridgewater</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>319 Manley St</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>02379</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="I163" s="4" t="inlineStr">
         <is>
           <t>(508) 588-8099</t>
         </is>
       </c>
-      <c r="J163" s="2" t="n"/>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="J163" s="4" t="n"/>
+      <c r="K163" s="4" t="inlineStr">
         <is>
           <t>Wayne Arensman</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="L163" s="4" t="inlineStr">
         <is>
           <t>IT Support Technician</t>
         </is>
       </c>
-      <c r="M163" s="2" t="n"/>
-      <c r="N163" s="2" t="inlineStr">
+      <c r="M163" s="4" t="n"/>
+      <c r="N163" s="4" t="inlineStr">
         <is>
           <t>Kyle Willis (President &amp; Chief Operating Officer)</t>
         </is>
       </c>
-      <c r="O163" s="2" t="inlineStr">
+      <c r="O163" s="4" t="inlineStr">
         <is>
           <t>Web handling equipment manufacturer, HQ</t>
         </is>
       </c>
-      <c r="P163" s="2" t="inlineStr">
+      <c r="P163" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q163" s="2" t="inlineStr">
+      <c r="Q163" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R163" s="2" t="inlineStr">
+      <c r="R163" s="4" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S163" s="2" t="inlineStr">
+      <c r="S163" s="4" t="inlineStr">
         <is>
           <t>54315000</t>
         </is>
       </c>
-      <c r="T163" s="2" t="inlineStr">
+      <c r="T163" s="4" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U163" s="2" t="n"/>
-      <c r="V163" s="2" t="inlineStr">
+      <c r="U163" s="4" t="n"/>
+      <c r="V163" s="4" t="inlineStr">
         <is>
           <t>ee-co.com</t>
         </is>
       </c>
-      <c r="W163" s="2" t="n"/>
-      <c r="X163" s="3" t="inlineStr">
-        <is>
-          <t>Manley St industrial corridor anchor. [ZoomInfo ID 18859551]</t>
+      <c r="W163" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X163" s="5" t="inlineStr">
+        <is>
+          <t>Manley St industrial corridor anchor. [ZoomInfo ID 18859551]  |  ZoomInfo matched Wayne Arensman but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -16995,7 +17295,11 @@
           <t>(508) 238-2007</t>
         </is>
       </c>
-      <c r="J164" s="2" t="n"/>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>(508) 297-8062</t>
+        </is>
+      </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
           <t>Elaina Gordon</t>
@@ -17048,10 +17352,14 @@
           <t>northeastonsavingsbank.com</t>
         </is>
       </c>
-      <c r="W164" s="2" t="n"/>
+      <c r="W164" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X164" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 82150842]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 82150842]  |  ZoomInfo confirmed direct dial (508) 297-8062 for Elaina Gordon, callable.</t>
         </is>
       </c>
     </row>
@@ -17101,7 +17409,11 @@
           <t>(508) 580-1700</t>
         </is>
       </c>
-      <c r="J165" s="2" t="n"/>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>(508) 930-2768</t>
+        </is>
+      </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
           <t>Maureen McLaughlin</t>
@@ -17158,218 +17470,230 @@
           <t>concordfoods.com</t>
         </is>
       </c>
-      <c r="W165" s="2" t="n"/>
+      <c r="W165" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X165" s="3" t="inlineStr">
         <is>
-          <t>Parented but plant run locally. [ZoomInfo ID 25808706]</t>
+          <t>Parented but plant run locally. [ZoomInfo ID 25808706]  |  ZoomInfo confirmed mobile (508) 930-2768 for Maureen McLaughlin, callable.</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>REXA</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D166" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
         <is>
           <t>West Bridgewater</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F166" s="4" t="inlineStr">
         <is>
           <t>4 Manley St</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t>02379</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="I166" s="4" t="inlineStr">
         <is>
           <t>(508) 584-1199</t>
         </is>
       </c>
-      <c r="J166" s="2" t="n"/>
-      <c r="K166" s="2" t="inlineStr">
+      <c r="J166" s="4" t="n"/>
+      <c r="K166" s="4" t="inlineStr">
         <is>
           <t>Lynne Gray</t>
         </is>
       </c>
-      <c r="L166" s="2" t="inlineStr">
+      <c r="L166" s="4" t="inlineStr">
         <is>
           <t>IT Specialist</t>
         </is>
       </c>
-      <c r="M166" s="2" t="n"/>
-      <c r="N166" s="2" t="n"/>
-      <c r="O166" s="2" t="inlineStr">
+      <c r="M166" s="4" t="n"/>
+      <c r="N166" s="4" t="n"/>
+      <c r="O166" s="4" t="inlineStr">
         <is>
           <t>Electraulic actuator manufacturer</t>
         </is>
       </c>
-      <c r="P166" s="2" t="inlineStr">
+      <c r="P166" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q166" s="2" t="inlineStr">
+      <c r="Q166" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R166" s="2" t="inlineStr">
+      <c r="R166" s="4" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="S166" s="2" t="inlineStr">
+      <c r="S166" s="4" t="inlineStr">
         <is>
           <t>29369000</t>
         </is>
       </c>
-      <c r="T166" s="2" t="inlineStr">
+      <c r="T166" s="4" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="U166" s="2" t="n"/>
-      <c r="V166" s="2" t="inlineStr">
+      <c r="U166" s="4" t="n"/>
+      <c r="V166" s="4" t="inlineStr">
         <is>
           <t>rexa.com</t>
         </is>
       </c>
-      <c r="W166" s="2" t="n"/>
-      <c r="X166" s="3" t="inlineStr">
-        <is>
-          <t>Same street as Double E and Shawmut. [ZoomInfo ID 86705017]</t>
+      <c r="W166" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X166" s="5" t="inlineStr">
+        <is>
+          <t>Same street as Double E and Shawmut. [ZoomInfo ID 86705017]  |  ZoomInfo: both direct and mobile for Lynne Gray are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>Pharmasol</t>
         </is>
       </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
         <is>
           <t>South Easton</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>1 Norfolk Ave Ste 1</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t>02375</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="I167" s="4" t="inlineStr">
         <is>
           <t>(508) 238-8501</t>
         </is>
       </c>
-      <c r="J167" s="2" t="n"/>
-      <c r="K167" s="2" t="inlineStr">
+      <c r="J167" s="4" t="n"/>
+      <c r="K167" s="4" t="inlineStr">
         <is>
           <t>Mark Badilla</t>
         </is>
       </c>
-      <c r="L167" s="2" t="inlineStr">
+      <c r="L167" s="4" t="inlineStr">
         <is>
           <t>Manager, Management Information Systems</t>
         </is>
       </c>
-      <c r="M167" s="2" t="n"/>
-      <c r="N167" s="2" t="inlineStr">
+      <c r="M167" s="4" t="n"/>
+      <c r="N167" s="4" t="inlineStr">
         <is>
           <t>Donghwan Choi (President)</t>
         </is>
       </c>
-      <c r="O167" s="2" t="inlineStr">
+      <c r="O167" s="4" t="inlineStr">
         <is>
           <t>Contract pharma manufacturer</t>
         </is>
       </c>
-      <c r="P167" s="2" t="inlineStr">
+      <c r="P167" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q167" s="2" t="inlineStr">
+      <c r="Q167" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R167" s="2" t="inlineStr">
+      <c r="R167" s="4" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="S167" s="2" t="inlineStr">
+      <c r="S167" s="4" t="inlineStr">
         <is>
           <t>28647000</t>
         </is>
       </c>
-      <c r="T167" s="2" t="inlineStr">
+      <c r="T167" s="4" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="U167" s="2" t="n"/>
-      <c r="V167" s="2" t="inlineStr">
+      <c r="U167" s="4" t="n"/>
+      <c r="V167" s="4" t="inlineStr">
         <is>
           <t>pharmasol.com</t>
         </is>
       </c>
-      <c r="W167" s="2" t="n"/>
-      <c r="X167" s="3" t="inlineStr">
-        <is>
-          <t>Norfolk Ave cluster with Reilly, Central Ceilings, Willwork, Averill. [ZoomInfo ID 92259395]</t>
+      <c r="W167" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X167" s="5" t="inlineStr">
+        <is>
+          <t>Norfolk Ave cluster with Reilly, Central Ceilings, Willwork, Averill. [ZoomInfo ID 92259395]  |  ZoomInfo matched Mark Badilla but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -17419,7 +17743,11 @@
           <t>(781) 784-7725</t>
         </is>
       </c>
-      <c r="J168" s="2" t="n"/>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>(508) 408-6331</t>
+        </is>
+      </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
           <t>Paul Pijanowski</t>
@@ -17472,10 +17800,14 @@
           <t>scucu.com</t>
         </is>
       </c>
-      <c r="W168" s="2" t="n"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X168" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 509741446]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 509741446]  |  ZoomInfo confirmed direct dial (508) 408-6331 for Paul Pijanowski, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17857,11 @@
           <t>(508) 583-8700</t>
         </is>
       </c>
-      <c r="J169" s="2" t="n"/>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>(508) 583-0943</t>
+        </is>
+      </c>
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="2" t="n"/>
       <c r="M169" s="2" t="n"/>
@@ -17570,10 +17906,14 @@
           <t>lyne.com</t>
         </is>
       </c>
-      <c r="W169" s="2" t="n"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X169" s="3" t="inlineStr">
         <is>
-          <t>FDA site. Compliance ready IT pitch. [ZoomInfo ID 71355494]</t>
+          <t>FDA site. Compliance ready IT pitch. [ZoomInfo ID 71355494]  |  ZoomInfo confirmed direct dial (508) 583-0943 for Stephen Tarallo, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -19521,7 +19861,11 @@
           <t>(781) 828-7000</t>
         </is>
       </c>
-      <c r="J189" s="2" t="n"/>
+      <c r="J189" s="2" t="inlineStr">
+        <is>
+          <t>(781) 770-0351</t>
+        </is>
+      </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
           <t>Tom Kane</t>
@@ -19566,100 +19910,108 @@
           <t>bostonmutual.com</t>
         </is>
       </c>
-      <c r="W189" s="2" t="n"/>
+      <c r="W189" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X189" s="3" t="inlineStr">
         <is>
-          <t>From June postcard list. Email on file: tom.kane@bostonmutual.com.</t>
+          <t>From June postcard list. Email on file: tom.kane@bostonmutual.com.  |  ZoomInfo confirmed direct dial (781) 770-0351 for Tom Kane during the earlier warm-lead enrichment pass, callable.</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="4" t="inlineStr">
         <is>
           <t>Abington Bank</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="4" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="E190" s="4" t="inlineStr">
         <is>
           <t>Holbrook</t>
         </is>
       </c>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="F190" s="4" t="inlineStr">
         <is>
           <t>95 N Franklin St</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="H190" s="4" t="inlineStr">
         <is>
           <t>02343</t>
         </is>
       </c>
-      <c r="I190" s="2" t="n"/>
-      <c r="J190" s="2" t="n"/>
-      <c r="K190" s="2" t="inlineStr">
+      <c r="I190" s="4" t="n"/>
+      <c r="J190" s="4" t="n"/>
+      <c r="K190" s="4" t="inlineStr">
         <is>
           <t>Michael Fitzgerald</t>
         </is>
       </c>
-      <c r="L190" s="2" t="inlineStr">
+      <c r="L190" s="4" t="inlineStr">
         <is>
           <t>VP, Information Technology</t>
         </is>
       </c>
-      <c r="M190" s="2" t="n"/>
-      <c r="N190" s="2" t="n"/>
-      <c r="O190" s="2" t="inlineStr">
+      <c r="M190" s="4" t="n"/>
+      <c r="N190" s="4" t="n"/>
+      <c r="O190" s="4" t="inlineStr">
         <is>
           <t>Community bank</t>
         </is>
       </c>
-      <c r="P190" s="2" t="inlineStr">
+      <c r="P190" s="4" t="inlineStr">
         <is>
           <t>Community bank with one IT officer. Lead with exam prep, vCISO and layered security.</t>
         </is>
       </c>
-      <c r="Q190" s="2" t="inlineStr">
+      <c r="Q190" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R190" s="2" t="inlineStr">
+      <c r="R190" s="4" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S190" s="2" t="n"/>
-      <c r="T190" s="2" t="n"/>
-      <c r="U190" s="2" t="n"/>
-      <c r="V190" s="2" t="inlineStr">
+      <c r="S190" s="4" t="n"/>
+      <c r="T190" s="4" t="n"/>
+      <c r="U190" s="4" t="n"/>
+      <c r="V190" s="4" t="inlineStr">
         <is>
           <t>abingtonbank.com</t>
         </is>
       </c>
-      <c r="W190" s="2" t="n"/>
-      <c r="X190" s="3" t="inlineStr">
-        <is>
-          <t>From postcard list. Contact email on file had a mismatched domain, verify at the door.</t>
+      <c r="W190" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X190" s="5" t="inlineStr">
+        <is>
+          <t>From postcard list. Contact email on file had a mismatched domain, verify at the door.  |  ZoomInfo weak match (company only, no personal data confirmed) for Michael Fitzgerald. Reinforces the prior flag: this contact is unverified/likely stale.</t>
         </is>
       </c>
     </row>
@@ -20163,7 +20515,11 @@
           <t>(508) 339-3312</t>
         </is>
       </c>
-      <c r="J196" s="2" t="n"/>
+      <c r="J196" s="2" t="inlineStr">
+        <is>
+          <t>(508) 281-2193</t>
+        </is>
+      </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
           <t>Regis Kouatcho</t>
@@ -20216,10 +20572,14 @@
           <t>lacerta.com</t>
         </is>
       </c>
-      <c r="W196" s="2" t="n"/>
+      <c r="W196" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X196" s="3" t="inlineStr">
         <is>
-          <t>Forbes Blvd cluster with Proven Process. [ZoomInfo ID 45598062]</t>
+          <t>Forbes Blvd cluster with Proven Process. [ZoomInfo ID 45598062]  |  ZoomInfo confirmed direct dial (508) 281-2193 for Regis Kouatcho, callable.</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20629,11 @@
           <t>(781) 784-1400</t>
         </is>
       </c>
-      <c r="J197" s="2" t="n"/>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>(774) 217-0995</t>
+        </is>
+      </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
           <t>Bill Gabriel</t>
@@ -20318,10 +20682,14 @@
           <t>metalbellows.com</t>
         </is>
       </c>
-      <c r="W197" s="2" t="n"/>
+      <c r="W197" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X197" s="3" t="inlineStr">
         <is>
-          <t>Defense and aerospace. CMMC door opener. [ZoomInfo ID 129401436]</t>
+          <t>Defense and aerospace. CMMC door opener. [ZoomInfo ID 129401436]  |  ZoomInfo confirmed mobile (774) 217-0995 for Bill Gabriel, callable.</t>
         </is>
       </c>
     </row>
@@ -20371,7 +20739,11 @@
           <t>(877) 551-0907</t>
         </is>
       </c>
-      <c r="J198" s="2" t="n"/>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>(617) 704-2289</t>
+        </is>
+      </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
           <t>Reema Shetye</t>
@@ -20424,116 +20796,124 @@
           <t>connectpayusa.com</t>
         </is>
       </c>
-      <c r="W198" s="2" t="n"/>
+      <c r="W198" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X198" s="3" t="inlineStr">
         <is>
-          <t>Client payroll data. Security and uptime pitch. [ZoomInfo ID 371623882]</t>
+          <t>Client payroll data. Security and uptime pitch. [ZoomInfo ID 371623882]  |  ZoomInfo confirmed mobile (617) 704-2289 for Reema Shetye, callable.</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B199" s="2" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>CPS Technologies</t>
         </is>
       </c>
-      <c r="D199" s="2" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="E199" s="2" t="inlineStr">
+      <c r="E199" s="4" t="inlineStr">
         <is>
           <t>Norton</t>
         </is>
       </c>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>111 S Worcester St</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="H199" s="4" t="inlineStr">
         <is>
           <t>02766</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="I199" s="4" t="inlineStr">
         <is>
           <t>(508) 222-0614</t>
         </is>
       </c>
-      <c r="J199" s="2" t="n"/>
-      <c r="K199" s="2" t="inlineStr">
+      <c r="J199" s="4" t="n"/>
+      <c r="K199" s="4" t="inlineStr">
         <is>
           <t>Yashvant Patel</t>
         </is>
       </c>
-      <c r="L199" s="2" t="inlineStr">
+      <c r="L199" s="4" t="inlineStr">
         <is>
           <t>Desktop Support Hardware Networking Engineer</t>
         </is>
       </c>
-      <c r="M199" s="2" t="n"/>
-      <c r="N199" s="2" t="inlineStr">
+      <c r="M199" s="4" t="n"/>
+      <c r="N199" s="4" t="inlineStr">
         <is>
           <t>Ashish Desai (Founder)</t>
         </is>
       </c>
-      <c r="O199" s="2" t="inlineStr">
+      <c r="O199" s="4" t="inlineStr">
         <is>
           <t>Advanced materials manufacturer, public co</t>
         </is>
       </c>
-      <c r="P199" s="2" t="inlineStr">
+      <c r="P199" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q199" s="2" t="inlineStr">
+      <c r="Q199" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R199" s="2" t="inlineStr">
+      <c r="R199" s="4" t="inlineStr">
         <is>
           <t>117</t>
         </is>
       </c>
-      <c r="S199" s="2" t="inlineStr">
+      <c r="S199" s="4" t="inlineStr">
         <is>
           <t>32350000</t>
         </is>
       </c>
-      <c r="T199" s="2" t="inlineStr">
+      <c r="T199" s="4" t="inlineStr">
         <is>
           <t>1984</t>
         </is>
       </c>
-      <c r="U199" s="2" t="n"/>
-      <c r="V199" s="2" t="inlineStr">
+      <c r="U199" s="4" t="n"/>
+      <c r="V199" s="4" t="inlineStr">
         <is>
           <t>cpstechnologysolutions.com</t>
         </is>
       </c>
-      <c r="W199" s="2" t="n"/>
-      <c r="X199" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ listed metal matrix composites maker. [ZoomInfo ID 30296872]</t>
+      <c r="W199" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X199" s="5" t="inlineStr">
+        <is>
+          <t>NASDAQ listed metal matrix composites maker. [ZoomInfo ID 30296872]  |  ZoomInfo matched Yashvant Patel but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -20583,7 +20963,11 @@
           <t>(508) 261-0849</t>
         </is>
       </c>
-      <c r="J200" s="2" t="n"/>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>(630) 423-7688</t>
+        </is>
+      </c>
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="2" t="n"/>
       <c r="M200" s="2" t="n"/>
@@ -20632,10 +21016,14 @@
           <t>provenprocess.com</t>
         </is>
       </c>
-      <c r="W200" s="2" t="n"/>
+      <c r="W200" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X200" s="3" t="inlineStr">
         <is>
-          <t>FDA quality system. [ZoomInfo ID 114443677]</t>
+          <t>FDA quality system. [ZoomInfo ID 114443677]  |  ZoomInfo confirmed direct dial (630) 423-7688 for Anthony Roscoe, callable (out-of-state number on file, likely a personal cell).</t>
         </is>
       </c>
     </row>
@@ -20685,7 +21073,11 @@
           <t>(617) 932-7877</t>
         </is>
       </c>
-      <c r="J201" s="2" t="n"/>
+      <c r="J201" s="2" t="inlineStr">
+        <is>
+          <t>(781) 461-8251</t>
+        </is>
+      </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
           <t>Debra King</t>
@@ -20738,10 +21130,14 @@
           <t>acumentrics.com</t>
         </is>
       </c>
-      <c r="W201" s="2" t="n"/>
+      <c r="W201" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X201" s="3" t="inlineStr">
         <is>
-          <t>Military power systems. CMMC angle. [ZoomInfo ID 426173]</t>
+          <t>Military power systems. CMMC angle. [ZoomInfo ID 426173]  |  ZoomInfo confirmed direct dial (781) 461-8251 for Debra King, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -20791,7 +21187,11 @@
           <t>(800) 255-6106</t>
         </is>
       </c>
-      <c r="J202" s="2" t="n"/>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>(508) 339-6106</t>
+        </is>
+      </c>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
       <c r="M202" s="2" t="n"/>
@@ -20836,10 +21236,14 @@
           <t>clinicalsciencelab.com</t>
         </is>
       </c>
-      <c r="W202" s="2" t="n"/>
+      <c r="W202" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X202" s="3" t="inlineStr">
         <is>
-          <t>CLIA lab, PHI. [ZoomInfo ID 416692291]</t>
+          <t>CLIA lab, PHI. [ZoomInfo ID 416692291]  |  ZoomInfo confirmed direct dial (508) 339-6106 for Lonnie Elfbaum, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -43385,7 +43789,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>(339) 469-0600</t>
+          <t>(785) 845-8526</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -43400,7 +43804,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -43427,7 +43831,7 @@
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>Owned by Nomura Research Institute since 2022. Local office still runs day to day here. Hybrid workforce.</t>
+          <t>Owned by Nomura Research Institute since 2022. Local office still runs day to day here. Hybrid workforce.  |  ZoomInfo confirmed mobile (785) 845-8526 for Cindy Castellano, callable (not flagged Do Not Call).</t>
         </is>
       </c>
     </row>
@@ -43486,7 +43890,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Has developers but likely thin IT ops. Good co-managed fit. Fast growth company.</t>
+          <t>Has developers but likely thin IT ops. Good co-managed fit. Fast growth company.  |  ZoomInfo matched Bruno Bonifacini but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -43794,7 +44198,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>(781) 878-0232</t>
+          <t>(781) 681-4808</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -43809,7 +44213,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
@@ -43836,7 +44240,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Has internal IT led by a senior VP. Co-managed and security services angle, not full outsource.</t>
+          <t>Has internal IT led by a senior VP. Co-managed and security services angle, not full outsource.  |  ZoomInfo confirmed both direct (781) 681-4808 and mobile (774) 249-2492 for Mark Federico, callable.</t>
         </is>
       </c>
     </row>
@@ -43853,7 +44257,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>(781) 413-3000</t>
+          <t>(781) 413-3008</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -43868,7 +44272,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G10" s="2" t="n"/>
@@ -43895,7 +44299,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Flagship local HQ. CPSC regulated products mean documentation and systems matter. Also on the 2026 Targets Master. Merge outreach history before visiting.</t>
+          <t>Flagship local HQ. CPSC regulated products mean documentation and systems matter. Also on the 2026 Targets Master. Merge outreach history before visiting.  |  ZoomInfo confirmed direct (781) 413-3008 and mobile (781) 243-9205 for Darrell Van Meter, callable.</t>
         </is>
       </c>
     </row>
@@ -43954,7 +44358,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Classic ICP manufacturer. Strong first stop.</t>
+          <t>Classic ICP manufacturer. Strong first stop.  |  ZoomInfo matched Ashwani Sharma but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -43971,7 +44375,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>(781) 871-6040</t>
+          <t>(781) 871-6040 ext. 204</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -43986,7 +44390,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G12" s="2" t="n"/>
@@ -44013,7 +44417,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Same complex as Bendon Gear. Two stops, one lot.</t>
+          <t>Same complex as Bendon Gear. Two stops, one lot.  |  ZoomInfo confirmed direct dial (781) 871-6040 ext. 204 for Sean Skorohod, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -44066,7 +44470,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M13" s="3" t="n"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -44702,7 +45110,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>(781) 871-2200</t>
+          <t>(781) 607-2482</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -44717,7 +45125,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G25" s="2" t="n"/>
@@ -44744,7 +45152,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Vic Firth is part of Zildjian, same campus. Iconic account for local proof.</t>
+          <t>Vic Firth is part of Zildjian, same campus. Iconic account for local proof.  |  ZoomInfo confirmed mobile (781) 607-2482 for James Clifford, callable.</t>
         </is>
       </c>
     </row>
@@ -44761,7 +45169,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>(877) 223-4800</t>
+          <t>(781) 882-8921</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -44776,7 +45184,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G26" s="2" t="n"/>
@@ -44803,7 +45211,7 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Same building as Miniter Group, different suite. Pair the stops.</t>
+          <t>Same building as Miniter Group, different suite. Pair the stops.  |  ZoomInfo confirmed direct dial (781) 882-8921 for Jake Gent, callable.</t>
         </is>
       </c>
     </row>
@@ -44862,7 +45270,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Nonprofit budget cycle. EHR uptime and clinician onboarding speed are real pains.</t>
+          <t>Nonprofit budget cycle. EHR uptime and clinician onboarding speed are real pains.  |  ZoomInfo matched Samuel Lutz but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -44921,7 +45329,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ listed. Hocoma brand runs from same office.</t>
+          <t>NASDAQ listed. Hocoma brand runs from same office.  |  ZoomInfo matched Haile Mitiku but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -44938,7 +45346,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>(800) 646-4837</t>
+          <t>(781) 982-3100</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -44953,7 +45361,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
@@ -44980,7 +45388,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>Same building as Radius. Two ICP financial accounts in one stop.</t>
+          <t>Same building as Radius. Two ICP financial accounts in one stop.  |  ZoomInfo confirmed direct dial (781) 982-3100 for Wayne Brantley, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -45039,7 +45447,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>7 locations run from here.</t>
+          <t>7 locations run from here.  |  ZoomInfo: both direct (508) 394-0911 ext. 223 and mobile for Danielle Jones are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
@@ -45056,7 +45464,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>(781) 871-4816</t>
+          <t>(617) 871-4816</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -45071,7 +45479,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G31" s="2" t="n"/>
@@ -45098,7 +45506,7 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Rockland address but sits in the Accord Park corridor. Route with Norwell stops.</t>
+          <t>Rockland address but sits in the Accord Park corridor. Route with Norwell stops.  |  ZoomInfo confirmed both direct (617) 871-4816 and mobile (617) 974-6115 for Randall Steele, callable.</t>
         </is>
       </c>
     </row>
@@ -45668,7 +46076,7 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>Multi provider practice. Visit mid afternoon, never during morning patient rush.</t>
+          <t>Multi provider practice. Visit mid afternoon, never during morning patient rush.  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -46251,7 +46659,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>(781) 826-6371</t>
+          <t>(781) 829-4609</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -46266,7 +46674,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
@@ -46293,7 +46701,7 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>Large campus on Rt 53. Ask for the business office.</t>
+          <t>Large campus on Rt 53. Ask for the business office.  |  ZoomInfo confirmed direct dial (781) 829-4609 for Evan Moniz, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -46352,7 +46760,7 @@
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>Same building as Merrill Associates.</t>
+          <t>Same building as Merrill Associates.  |  ZoomInfo: mobile (801) 718-5467 for Kimmie Miller is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -46757,7 +47165,7 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>One of the biggest private employers based in Hanover. Active 5PT account. Do not cold pitch. Relationship and expansion visit only.</t>
+          <t>One of the biggest private employers based in Hanover. Active 5PT account. Do not cold pitch. Relationship and expansion visit only.  |  ZoomInfo: mobile (781) 385-1348 for Anthony Emma is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -46774,7 +47182,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>(781) 878-5000</t>
+          <t>(781) 681-3289</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -46789,7 +47197,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G61" s="2" t="n"/>
@@ -46816,7 +47224,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>Biggest revenue target in Hanover on this list.</t>
+          <t>Biggest revenue target in Hanover on this list.  |  ZoomInfo confirmed direct dial (781) 681-3289 for Devin Melo, callable.</t>
         </is>
       </c>
     </row>
@@ -46833,7 +47241,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>(781) 826-9100</t>
+          <t>(781) 826-7833</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -46848,7 +47256,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G62" s="2" t="n"/>
@@ -46875,7 +47283,7 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>Medical manufacturing is a priority vertical.</t>
+          <t>Medical manufacturing is a priority vertical.  |  ZoomInfo confirmed direct dial (781) 826-7833 for Lisa Raasch, callable.</t>
         </is>
       </c>
     </row>
@@ -46907,7 +47315,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G63" s="2" t="n"/>
@@ -46934,7 +47342,7 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>Phone corrected from web. ZoomInfo listed an out of state number.</t>
+          <t>Phone corrected from web. ZoomInfo listed an out of state number.  |  ZoomInfo confirmed direct dial (781) 826-8801 for Daniel McClelland, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -46993,7 +47401,7 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>West Hanover village, near Circuit St loop.</t>
+          <t>West Hanover village, near Circuit St loop.  |  ZoomInfo: mobile (617) 697-8970 for Matt Phung is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -47052,7 +47460,7 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>Corporate IT may exist at Daikin America. Local plant manager still feels the pain.</t>
+          <t>Corporate IT may exist at Daikin America. Local plant manager still feels the pain.  |  ZoomInfo: both direct and mobile for Richard Park are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
@@ -47454,7 +47862,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>(781) 826-2393</t>
+          <t>(781) 924-3167</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -47469,7 +47877,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G73" s="2" t="n"/>
@@ -47496,7 +47904,7 @@
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>HQ decides for all facilities. Employee count spans the group.</t>
+          <t>HQ decides for all facilities. Employee count spans the group.  |  ZoomInfo confirmed direct dial (781) 924-3167 for Jimmy Noel, callable.</t>
         </is>
       </c>
     </row>
@@ -47551,7 +47959,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>HQ office decides for all sites. Strong multi site play.</t>
+          <t>HQ office decides for all sites. Strong multi site play.  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -47568,7 +47976,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>(855) 784-2937</t>
+          <t>(781) 341-2222</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -47583,7 +47991,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G75" s="2" t="n"/>
@@ -47610,7 +48018,7 @@
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>Classic ICP manufacturer.</t>
+          <t>Classic ICP manufacturer.  |  ZoomInfo confirmed direct dial (781) 341-2222 for Chris Geer, callable.</t>
         </is>
       </c>
     </row>
@@ -47667,7 +48075,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M76" s="3" t="n"/>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo returned an email on the flextronics.com domain for Patrick Wong (no phone). VERIFY: he may have moved to Flextronics/Flex, or Nelco may now sit under that parent. Confirm before outreach.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -48523,7 +48935,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>(781) 826-3138</t>
+          <t>(781) 523-3213</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -48538,7 +48950,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G92" s="2" t="n"/>
@@ -48565,7 +48977,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>One of the largest paving firms in New England.</t>
+          <t>One of the largest paving firms in New England.  |  ZoomInfo confirmed direct dial (781) 523-3213 for Peter Cleary, callable.</t>
         </is>
       </c>
     </row>
@@ -48624,7 +49036,7 @@
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>Family owned. Decision makers on site.</t>
+          <t>Family owned. Decision makers on site.  |  ZoomInfo: mobile (508) 847-4666 for Thomas McManus is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -49300,7 +49712,7 @@
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
-          <t>Merger integration is an IT trigger. Bank flagged as Dedham Savings affiliate.</t>
+          <t>Merger integration is an IT trigger. Bank flagged as Dedham Savings affiliate.  |  ZoomInfo weak match (company only, no personal data confirmed) for Lynn Tempesta this pass. Prior intel stands: desk line (781) 682-3269, mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -49317,7 +49729,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>(781) 335-5200</t>
+          <t>(781) 607-3366</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -49332,7 +49744,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G106" s="2" t="n"/>
@@ -49359,7 +49771,7 @@
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
-          <t>Defense customers mean a CMMC door opener.</t>
+          <t>Defense customers mean a CMMC door opener.  |  ZoomInfo confirmed direct dial (781) 607-3366 for Karen Roche, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -49376,7 +49788,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>(781) 796-6050</t>
+          <t>(781) 682-4438</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -49391,7 +49803,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G107" s="2" t="n"/>
@@ -49418,7 +49830,7 @@
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
-          <t>Listed as merged into MountainOne. Verify branding before visiting.</t>
+          <t>Listed as merged into MountainOne. Verify branding before visiting.  |  ZoomInfo confirmed direct dial (781) 682-4438 and mobile (781) 796-6009 for Margaret Ruuska, both callable.</t>
         </is>
       </c>
     </row>
@@ -49435,7 +49847,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>(781) 383-6800</t>
+          <t>(781) 803-2786 ext. 223</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -49450,7 +49862,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G108" s="2" t="n"/>
@@ -49477,7 +49889,7 @@
       </c>
       <c r="M108" s="3" t="inlineStr">
         <is>
-          <t>Multi practice group. HIPAA and EHR uptime.</t>
+          <t>Multi practice group. HIPAA and EHR uptime.  |  ZoomInfo confirmed direct dial (781) 803-2786 ext. 223 for Phillip Joy, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -49536,7 +49948,7 @@
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
-          <t>Defense supplier. Ask about CMMC prep.</t>
+          <t>Defense supplier. Ask about CMMC prep.  |  ZoomInfo matched James Hall but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -49593,7 +50005,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M110" s="3" t="n"/>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: mobile (617) 240-5885 for Daniel Bagley is flagged Do Not Call. No alternate number found; use company main line.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -49650,7 +50066,7 @@
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>Family owned. Same 3A run as Healthcare South.</t>
+          <t>Family owned. Same 3A run as Healthcare South.  |  ZoomInfo matched William McNulty but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -49709,7 +50125,7 @@
       </c>
       <c r="M112" s="3" t="inlineStr">
         <is>
-          <t>German parent, locally run plant.</t>
+          <t>German parent, locally run plant.  |  ZoomInfo: mobile (339) 788-0470 for Joel Smolka is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -49762,7 +50178,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M113" s="3" t="n"/>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -49819,7 +50239,7 @@
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
-          <t>World class instrument maker in your home town.</t>
+          <t>World class instrument maker in your home town.  |  ZoomInfo matched Lin Sandar but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -50499,7 +50919,7 @@
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
-          <t>HQ office decides for plants nationwide.</t>
+          <t>HQ office decides for plants nationwide.  |  ZoomInfo: mobile (270) 222-0317 for Phillip Murphy is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -50516,7 +50936,7 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>(617) 376-3000</t>
+          <t>(503) 691-4139</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -50531,7 +50951,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G127" s="2" t="n"/>
@@ -50558,7 +50978,7 @@
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
-          <t>Was on your 2026 target list. Admin office visit, afternoons.</t>
+          <t>Was on your 2026 target list. Admin office visit, afternoons.  |  ZoomInfo: direct line for Kim Shaw is flagged Do Not Call; mobile (503) 691-4139 is callable.</t>
         </is>
       </c>
     </row>
@@ -50575,7 +50995,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>(617) 770-5100</t>
+          <t>(617) 472-8770</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -50590,7 +51010,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G128" s="2" t="n"/>
@@ -50615,7 +51035,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M128" s="3" t="n"/>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed both direct (617) 472-8770 and mobile (617) 770-5127 for Michael Andrade, callable.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -50630,7 +51054,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>(617) 471-7171</t>
+          <t>(617) 330-5702</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -50645,7 +51069,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G129" s="2" t="n"/>
@@ -50670,7 +51094,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M129" s="3" t="n"/>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed direct dial (617) 330-5702 for Jason Brudnick, callable. Mobile on file is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -50685,7 +51113,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>(617) 472-9200</t>
+          <t>(617) 845-1126</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -50700,7 +51128,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G130" s="2" t="n"/>
@@ -50727,7 +51155,7 @@
       </c>
       <c r="M130" s="3" t="inlineStr">
         <is>
-          <t>Named IT director on file. Parent overseas, plant IT local.</t>
+          <t>Named IT director on file. Parent overseas, plant IT local.  |  ZoomInfo confirmed direct dial (617) 845-1126 for John Piasecki, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -51584,7 +52012,7 @@
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>Plymouth Industrial Park anchor.</t>
+          <t>Plymouth Industrial Park anchor.  |  ZoomInfo: mobile (508) 667-6556 for Alex Ivkovic is flagged Do Not Call. No alternate number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -51639,7 +52067,7 @@
       </c>
       <c r="M146" s="3" t="inlineStr">
         <is>
-          <t>HQ decides for all communities. HIPAA and nurse call uptime.</t>
+          <t>HQ decides for all communities. HIPAA and nurse call uptime.  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -51694,7 +52122,7 @@
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
-          <t>Two brands, one building. One stop covers both.</t>
+          <t>Two brands, one building. One stop covers both.  |  No named IT or executive contact on file to enrich. ZoomInfo pass not run; use company main line and ask who runs IT.</t>
         </is>
       </c>
     </row>
@@ -51753,7 +52181,7 @@
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
-          <t>FDA quality system. Enterprise Dr pairs with United Elevator.</t>
+          <t>FDA quality system. Enterprise Dr pairs with United Elevator.  |  ZoomInfo matched Jean Kirwan but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -51770,7 +52198,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>(508) 732-7200</t>
+          <t>(781) 724-0677</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -51785,7 +52213,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G149" s="2" t="n"/>
@@ -51812,7 +52240,7 @@
       </c>
       <c r="M149" s="3" t="inlineStr">
         <is>
-          <t>PE owned, locally run.</t>
+          <t>PE owned, locally run.  |  ZoomInfo confirmed mobile (781) 724-0677 for Tim Stevenson, callable.</t>
         </is>
       </c>
     </row>
@@ -51829,7 +52257,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>(781) 934-2400</t>
+          <t>(508) 298-6785</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -51844,7 +52272,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -51869,7 +52297,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M150" s="3" t="n"/>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed direct dial (508) 298-6785 for Scott Oliver, callable.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -52602,7 +53034,7 @@
       </c>
       <c r="M163" s="3" t="inlineStr">
         <is>
-          <t>Manley St industrial corridor anchor.</t>
+          <t>Manley St industrial corridor anchor.  |  ZoomInfo matched Wayne Arensman but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -52619,7 +53051,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>(508) 238-2007</t>
+          <t>(508) 297-8062</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -52634,7 +53066,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G164" s="2" t="n"/>
@@ -52659,7 +53091,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M164" s="3" t="n"/>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed direct dial (508) 297-8062 for Elaina Gordon, callable.</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -52674,7 +53110,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>(508) 580-1700</t>
+          <t>(508) 930-2768</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -52689,7 +53125,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G165" s="2" t="n"/>
@@ -52716,7 +53152,7 @@
       </c>
       <c r="M165" s="3" t="inlineStr">
         <is>
-          <t>Parented but plant run locally.</t>
+          <t>Parented but plant run locally.  |  ZoomInfo confirmed mobile (508) 930-2768 for Maureen McLaughlin, callable.</t>
         </is>
       </c>
     </row>
@@ -52775,7 +53211,7 @@
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
-          <t>Same street as Double E and Shawmut.</t>
+          <t>Same street as Double E and Shawmut.  |  ZoomInfo: both direct and mobile for Lynne Gray are flagged Do Not Call. Use company main line only.</t>
         </is>
       </c>
     </row>
@@ -52834,7 +53270,7 @@
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
-          <t>Norfolk Ave cluster with Reilly, Central Ceilings, Willwork, Averill.</t>
+          <t>Norfolk Ave cluster with Reilly, Central Ceilings, Willwork, Averill.  |  ZoomInfo matched Mark Badilla but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -52851,7 +53287,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>(781) 784-7725</t>
+          <t>(508) 408-6331</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -52866,7 +53302,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G168" s="2" t="n"/>
@@ -52891,7 +53327,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M168" s="3" t="n"/>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed direct dial (508) 408-6331 for Paul Pijanowski, callable. Mobile on file is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -52906,7 +53346,7 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>(508) 583-8700</t>
+          <t>(508) 583-0943</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
@@ -52921,7 +53361,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G169" s="2" t="n"/>
@@ -52948,7 +53388,7 @@
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
-          <t>FDA site. Compliance ready IT pitch.</t>
+          <t>FDA site. Compliance ready IT pitch.  |  ZoomInfo confirmed direct dial (508) 583-0943 for Stephen Tarallo, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -53924,7 +54364,7 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>(781) 828-7000</t>
+          <t>(781) 770-0351</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
@@ -53939,7 +54379,7 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G187" s="2" t="n"/>
@@ -53966,7 +54406,7 @@
       </c>
       <c r="M187" s="3" t="inlineStr">
         <is>
-          <t>From June postcard list. Email on file: tom.kane@bostonmutual.com.</t>
+          <t>From June postcard list. Email on file: tom.kane@bostonmutual.com.  |  ZoomInfo confirmed direct dial (781) 770-0351 for Tom Kane during the earlier warm-lead enrichment pass, callable.</t>
         </is>
       </c>
     </row>
@@ -54266,7 +54706,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>(508) 339-3312</t>
+          <t>(508) 281-2193</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
@@ -54281,7 +54721,7 @@
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G193" s="2" t="n"/>
@@ -54308,7 +54748,7 @@
       </c>
       <c r="M193" s="3" t="inlineStr">
         <is>
-          <t>Forbes Blvd cluster with Proven Process.</t>
+          <t>Forbes Blvd cluster with Proven Process.  |  ZoomInfo confirmed direct dial (508) 281-2193 for Regis Kouatcho, callable.</t>
         </is>
       </c>
     </row>
@@ -54325,7 +54765,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>(781) 784-1400</t>
+          <t>(774) 217-0995</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -54340,7 +54780,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G194" s="2" t="n"/>
@@ -54367,7 +54807,7 @@
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
-          <t>Defense and aerospace. CMMC door opener.</t>
+          <t>Defense and aerospace. CMMC door opener.  |  ZoomInfo confirmed mobile (774) 217-0995 for Bill Gabriel, callable.</t>
         </is>
       </c>
     </row>
@@ -54384,7 +54824,7 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>(877) 551-0907</t>
+          <t>(617) 704-2289</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
@@ -54399,7 +54839,7 @@
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G195" s="2" t="n"/>
@@ -54426,7 +54866,7 @@
       </c>
       <c r="M195" s="3" t="inlineStr">
         <is>
-          <t>Client payroll data. Security and uptime pitch.</t>
+          <t>Client payroll data. Security and uptime pitch.  |  ZoomInfo confirmed mobile (617) 704-2289 for Reema Shetye, callable.</t>
         </is>
       </c>
     </row>
@@ -54485,7 +54925,7 @@
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ listed metal matrix composites maker.</t>
+          <t>NASDAQ listed metal matrix composites maker.  |  ZoomInfo matched Yashvant Patel but returned no phone or mobile. No personal number found; use company main line.</t>
         </is>
       </c>
     </row>
@@ -54502,7 +54942,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>(508) 261-0849</t>
+          <t>(630) 423-7688</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
@@ -54517,7 +54957,7 @@
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G197" s="2" t="n"/>
@@ -54544,7 +54984,7 @@
       </c>
       <c r="M197" s="3" t="inlineStr">
         <is>
-          <t>FDA quality system.</t>
+          <t>FDA quality system.  |  ZoomInfo confirmed direct dial (630) 423-7688 for Anthony Roscoe, callable (out-of-state number on file, likely a personal cell).</t>
         </is>
       </c>
     </row>
@@ -54561,7 +55001,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>(617) 932-7877</t>
+          <t>(781) 461-8251</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -54576,7 +55016,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G198" s="2" t="n"/>
@@ -54603,7 +55043,7 @@
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>Military power systems. CMMC angle.</t>
+          <t>Military power systems. CMMC angle.  |  ZoomInfo confirmed direct dial (781) 461-8251 for Debra King, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -54620,7 +55060,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>(800) 255-6106</t>
+          <t>(508) 339-6106</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
@@ -54635,7 +55075,7 @@
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G199" s="2" t="n"/>
@@ -54662,7 +55102,7 @@
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
-          <t>CLIA lab, PHI.</t>
+          <t>CLIA lab, PHI.  |  ZoomInfo confirmed direct dial (508) 339-6106 for Lonnie Elfbaum, callable. Mobile on file is Do Not Call.</t>
         </is>
       </c>
     </row>

--- a/5PT-Master-Prospecting-Workbook.xlsx
+++ b/5PT-Master-Prospecting-Workbook.xlsx
@@ -690,7 +690,11 @@
       </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>ccastellano@cutterassociates.com</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Cindy Castellano (Chief Executive Officer)</t>
@@ -1440,7 +1444,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>mfederico@rfcu.com</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Kristin VanBeek (Chief Executive Officer &amp; President)</t>
@@ -1554,7 +1562,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>darrell@uppababy.com</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Bob Monahan (Chief Executive Officer &amp; Co-Founder)</t>
@@ -1770,7 +1782,11 @@
       </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>sskorohod@briggsengineering.com</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Sean Skorohod (Testing Services President &amp; Director)</t>
@@ -3072,7 +3088,11 @@
           <t>Senior Director, Information Technology</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>jamesc@zildjian.com</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Thomas Young (Senior Vice President, Chief Financial Officer and Treasurer)</t>
@@ -3296,7 +3316,11 @@
           <t>It Help Desk Technician</t>
         </is>
       </c>
-      <c r="M27" s="4" t="n"/>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>slutz@nvna.org</t>
+        </is>
+      </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
           <t>Bj Snow (Chief Human Resources Officer)</t>
@@ -3520,7 +3544,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>wayne@miniter.com</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>Julianne Gilpin (President &amp; Chief Executive Officer)</t>
@@ -3622,7 +3650,11 @@
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>danielle.jones@snowandjones.com</t>
+        </is>
+      </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
           <t>Danielle Jones (President)</t>
@@ -3728,7 +3760,11 @@
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>randallsteele@airxchange.com</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>Randall Steele (President &amp; Chief Executive Officer)</t>
@@ -5830,7 +5866,11 @@
           <t>Manager, Network</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>emoniz@cushingcenters.org</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>Gina Rosas (Chief Operating Officer)</t>
@@ -6626,7 +6666,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M60" s="4" t="n"/>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>aemma@palanders.com</t>
+        </is>
+      </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
           <t>Joseph Durant (Chief Operating Officer)</t>
@@ -6740,7 +6784,11 @@
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>dmelo@buckleyonline.com</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>Robert Buckley (Founder)</t>
@@ -6854,7 +6902,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>lraasch@srcmedical.com</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>Roy Tinkham (President)</t>
@@ -6968,7 +7020,11 @@
           <t>System Administrator</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>daniel_mcclelland@hapcoincorporated.com</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>Fred DeSimone (General Manager)</t>
@@ -7078,7 +7134,11 @@
           <t>IT Administrator</t>
         </is>
       </c>
-      <c r="M64" s="4" t="n"/>
+      <c r="M64" s="4" t="inlineStr">
+        <is>
+          <t>mphung@gemgravure.com</t>
+        </is>
+      </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
           <t>Joseph Gemelli (Founder)</t>
@@ -7968,7 +8028,11 @@
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>jnoel@royalhealthgroup.com</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>Pamela Jones (Chief Financial Officer)</t>
@@ -8180,7 +8244,11 @@
           <t>Information Technology Consultant</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>cgeer@thayerscale.com</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>Frank Hyer (Chairman &amp; Chief Executive Officer)</t>
@@ -9898,7 +9966,11 @@
       </c>
       <c r="K92" s="2" t="n"/>
       <c r="L92" s="2" t="n"/>
-      <c r="M92" s="2" t="n"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>pcleary@tkasphalt.com</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>Peter Cleary (Chief Financial Officer)</t>
@@ -10000,7 +10072,11 @@
       <c r="J93" s="4" t="n"/>
       <c r="K93" s="4" t="n"/>
       <c r="L93" s="4" t="n"/>
-      <c r="M93" s="4" t="n"/>
+      <c r="M93" s="4" t="inlineStr">
+        <is>
+          <t>tmcmanus@cclco.com</t>
+        </is>
+      </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
           <t>Thomas McManus (President)</t>
@@ -11172,7 +11248,11 @@
           <t>Vice President and Information Technology Operations Ma...</t>
         </is>
       </c>
-      <c r="M105" s="4" t="n"/>
+      <c r="M105" s="4" t="inlineStr">
+        <is>
+          <t>ltempesta@southshorebank.com</t>
+        </is>
+      </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
           <t>James Dunphy (President &amp; Chief Executive Officer)</t>
@@ -11290,7 +11370,11 @@
           <t>Manager, Corporate Information Systems</t>
         </is>
       </c>
-      <c r="M106" s="2" t="n"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>kroche@electroswitch.com</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="n"/>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -11400,7 +11484,11 @@
           <t>Vice President, Information Technology &amp; Officer</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>mruuska@coastalheritagebank.com</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>Richard Rowe (Director Chief Executive Officer)</t>
@@ -11518,7 +11606,11 @@
           <t>Director, Information Technology Operations &amp; Infrastru...</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>pjoy@healthcaresouth.com</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="n"/>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -11624,7 +11716,11 @@
           <t>Senior Software Systems Engineer &amp; Director &amp; Electrica...</t>
         </is>
       </c>
-      <c r="M109" s="4" t="n"/>
+      <c r="M109" s="4" t="inlineStr">
+        <is>
+          <t>jgh@massa.com</t>
+        </is>
+      </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
           <t>Donald Massa (Chief Technical Officer &amp; Chairman)</t>
@@ -11734,7 +11830,11 @@
           <t>Vice President, Chief Information Officer</t>
         </is>
       </c>
-      <c r="M110" s="4" t="n"/>
+      <c r="M110" s="4" t="inlineStr">
+        <is>
+          <t>danielbagley@hinghamsavings.com</t>
+        </is>
+      </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
           <t>Patrick Gaughen (President &amp; Chief Operating Officer)</t>
@@ -13354,7 +13454,11 @@
           <t>Director, Information Technology &amp; Development</t>
         </is>
       </c>
-      <c r="M126" s="4" t="n"/>
+      <c r="M126" s="4" t="inlineStr">
+        <is>
+          <t>pmurphy@bsm.com</t>
+        </is>
+      </c>
       <c r="N126" s="4" t="inlineStr">
         <is>
           <t>Alain Hanna (Chief Financial Officer)</t>
@@ -13468,7 +13572,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M127" s="2" t="n"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>shawk@manetchc.org</t>
+        </is>
+      </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Marc Conroy (Chief Financial Officer)</t>
@@ -13692,7 +13800,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M129" s="2" t="n"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>jbrudnick@xsbrokers.com</t>
+        </is>
+      </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
           <t>Eric Wirkus (Chief Executive Officer)</t>
@@ -15348,7 +15460,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M145" s="4" t="n"/>
+      <c r="M145" s="4" t="inlineStr">
+        <is>
+          <t>aivkovic@cdf1.com</t>
+        </is>
+      </c>
       <c r="N145" s="4" t="inlineStr">
         <is>
           <t>Joseph Sullivan (President)</t>
@@ -15760,7 +15876,11 @@
           <t>Systems Technician</t>
         </is>
       </c>
-      <c r="M149" s="2" t="n"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>tstevenson@vptec.com</t>
+        </is>
+      </c>
       <c r="N149" s="2" t="n"/>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -15866,7 +15986,11 @@
       </c>
       <c r="K150" s="2" t="n"/>
       <c r="L150" s="2" t="n"/>
-      <c r="M150" s="2" t="n"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>soliver@pbortho.com</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="inlineStr">
         <is>
           <t>Scott Oliver (President &amp; Founder)</t>
@@ -17196,7 +17320,11 @@
           <t>IT Support Technician</t>
         </is>
       </c>
-      <c r="M163" s="4" t="n"/>
+      <c r="M163" s="4" t="inlineStr">
+        <is>
+          <t>w.arensman@ee-co.com</t>
+        </is>
+      </c>
       <c r="N163" s="4" t="inlineStr">
         <is>
           <t>Kyle Willis (President &amp; Chief Operating Officer)</t>
@@ -17538,7 +17666,11 @@
           <t>IT Specialist</t>
         </is>
       </c>
-      <c r="M166" s="4" t="n"/>
+      <c r="M166" s="4" t="inlineStr">
+        <is>
+          <t>lgray@rexa.com</t>
+        </is>
+      </c>
       <c r="N166" s="4" t="n"/>
       <c r="O166" s="4" t="inlineStr">
         <is>
@@ -17644,7 +17776,11 @@
           <t>Manager, Management Information Systems</t>
         </is>
       </c>
-      <c r="M167" s="4" t="n"/>
+      <c r="M167" s="4" t="inlineStr">
+        <is>
+          <t>mbadilla@pharmasol.com</t>
+        </is>
+      </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
           <t>Donghwan Choi (President)</t>
@@ -17758,7 +17894,11 @@
           <t>Senior VP, Information Security</t>
         </is>
       </c>
-      <c r="M168" s="2" t="n"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>ppijanowski@scucu.com</t>
+        </is>
+      </c>
       <c r="N168" s="2" t="inlineStr">
         <is>
           <t>Robert Gustafson (President &amp; Chief Executive Officer)</t>
@@ -17864,7 +18004,11 @@
       </c>
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="2" t="n"/>
-      <c r="M169" s="2" t="n"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>starallo@lyne.com</t>
+        </is>
+      </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Stephen Tarallo (President &amp; Chief Executive Officer &amp; Director)</t>
@@ -19876,7 +20020,11 @@
           <t>CISO &amp; Director, Infrastructure</t>
         </is>
       </c>
-      <c r="M189" s="2" t="n"/>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>tom_kane@bostonmutual.com</t>
+        </is>
+      </c>
       <c r="N189" s="2" t="n"/>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -20530,7 +20678,11 @@
           <t>Business &amp; IT Systems Analyst</t>
         </is>
       </c>
-      <c r="M196" s="2" t="n"/>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>rkouatcho@lacerta.com</t>
+        </is>
+      </c>
       <c r="N196" s="2" t="inlineStr">
         <is>
           <t>Ali Lotfi (President)</t>
@@ -20644,7 +20796,11 @@
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M197" s="2" t="n"/>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>bgabriel@metalbellows.com</t>
+        </is>
+      </c>
       <c r="N197" s="2" t="n"/>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -20970,7 +21126,11 @@
       </c>
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="2" t="n"/>
-      <c r="M200" s="2" t="n"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>tony@proven-process.com</t>
+        </is>
+      </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
           <t>Anthony Roscoe (Business Owner)</t>
@@ -21088,7 +21248,11 @@
           <t>Vice President, Compliance &amp; Business Systems</t>
         </is>
       </c>
-      <c r="M201" s="2" t="n"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>dking@acumentrics.com</t>
+        </is>
+      </c>
       <c r="N201" s="2" t="inlineStr">
         <is>
           <t>John Cerulli (Chief Executive Officer)</t>
@@ -21194,7 +21358,11 @@
       </c>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="2" t="n"/>
-      <c r="M202" s="2" t="n"/>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>lonnie@clinicalsciencelab.com</t>
+        </is>
+      </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
           <t>Lonnie Elfbaum (Chief Financial Officer &amp; Controller)</t>
@@ -43807,7 +43975,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ccastellano@cutterassociates.com</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -44216,7 +44388,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>mfederico@rfcu.com</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -44275,7 +44451,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>darrell@uppababy.com</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
@@ -44393,7 +44573,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>sskorohod@briggsengineering.com</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -45128,7 +45312,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G25" s="2" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>jamesc@zildjian.com</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
@@ -45246,7 +45434,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>slutz@nvna.org</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
@@ -45364,7 +45556,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G29" s="2" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>wayne@miniter.com</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
@@ -45423,7 +45619,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>danielle.jones@snowandjones.com</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="inlineStr">
         <is>
@@ -45482,7 +45682,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G31" s="2" t="n"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>randallsteele@airxchange.com</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="n"/>
       <c r="I31" s="2" t="inlineStr">
         <is>
@@ -46677,7 +46881,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G52" s="2" t="n"/>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>emoniz@cushingcenters.org</t>
+        </is>
+      </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
@@ -47141,7 +47349,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G60" s="2" t="n"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>aemma@palanders.com</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
@@ -47200,7 +47412,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G61" s="2" t="n"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>dmelo@buckleyonline.com</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
@@ -47259,7 +47475,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G62" s="2" t="n"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>lraasch@srcmedical.com</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
@@ -47318,7 +47538,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G63" s="2" t="n"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>daniel_mcclelland@hapcoincorporated.com</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
@@ -47377,7 +47601,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G64" s="2" t="n"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>mphung@gemgravure.com</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
@@ -47880,7 +48108,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G73" s="2" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>jnoel@royalhealthgroup.com</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
@@ -47994,7 +48226,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G75" s="2" t="n"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>cgeer@thayerscale.com</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="n"/>
       <c r="I75" s="2" t="inlineStr">
         <is>
@@ -48953,7 +49189,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G92" s="2" t="n"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>pcleary@tkasphalt.com</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="n"/>
       <c r="I92" s="2" t="inlineStr">
         <is>
@@ -49012,7 +49252,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G93" s="2" t="n"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>tmcmanus@cclco.com</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="n"/>
       <c r="I93" s="2" t="inlineStr">
         <is>
@@ -49688,7 +49932,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G105" s="2" t="n"/>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>ltempesta@southshorebank.com</t>
+        </is>
+      </c>
       <c r="H105" s="2" t="n"/>
       <c r="I105" s="2" t="inlineStr">
         <is>
@@ -49747,7 +49995,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G106" s="2" t="n"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>kroche@electroswitch.com</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="n"/>
       <c r="I106" s="2" t="inlineStr">
         <is>
@@ -49806,7 +50058,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G107" s="2" t="n"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>mruuska@coastalheritagebank.com</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="n"/>
       <c r="I107" s="2" t="inlineStr">
         <is>
@@ -49865,7 +50121,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G108" s="2" t="n"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>pjoy@healthcaresouth.com</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="n"/>
       <c r="I108" s="2" t="inlineStr">
         <is>
@@ -49924,7 +50184,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G109" s="2" t="n"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>jgh@massa.com</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="inlineStr">
         <is>
@@ -49983,7 +50247,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G110" s="2" t="n"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>danielbagley@hinghamsavings.com</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="n"/>
       <c r="I110" s="2" t="inlineStr">
         <is>
@@ -50895,7 +51163,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G126" s="2" t="n"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>pmurphy@bsm.com</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="n"/>
       <c r="I126" s="2" t="inlineStr">
         <is>
@@ -50954,7 +51226,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G127" s="2" t="n"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>shawk@manetchc.org</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="n"/>
       <c r="I127" s="2" t="inlineStr">
         <is>
@@ -51072,7 +51348,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G129" s="2" t="n"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>jbrudnick@xsbrokers.com</t>
+        </is>
+      </c>
       <c r="H129" s="2" t="n"/>
       <c r="I129" s="2" t="inlineStr">
         <is>
@@ -51988,7 +52268,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G145" s="2" t="n"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>aivkovic@cdf1.com</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="n"/>
       <c r="I145" s="2" t="inlineStr">
         <is>
@@ -52216,7 +52500,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G149" s="2" t="n"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>tstevenson@vptec.com</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="n"/>
       <c r="I149" s="2" t="inlineStr">
         <is>
@@ -52275,7 +52563,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G150" s="2" t="n"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>soliver@pbortho.com</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="inlineStr">
         <is>
@@ -53010,7 +53302,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G163" s="2" t="n"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>w.arensman@ee-co.com</t>
+        </is>
+      </c>
       <c r="H163" s="2" t="n"/>
       <c r="I163" s="2" t="inlineStr">
         <is>
@@ -53187,7 +53483,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G166" s="2" t="n"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>lgray@rexa.com</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="n"/>
       <c r="I166" s="2" t="inlineStr">
         <is>
@@ -53246,7 +53546,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G167" s="2" t="n"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>mbadilla@pharmasol.com</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="n"/>
       <c r="I167" s="2" t="inlineStr">
         <is>
@@ -53305,7 +53609,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G168" s="2" t="n"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>ppijanowski@scucu.com</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="n"/>
       <c r="I168" s="2" t="inlineStr">
         <is>
@@ -53364,7 +53672,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G169" s="2" t="n"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>starallo@lyne.com</t>
+        </is>
+      </c>
       <c r="H169" s="2" t="n"/>
       <c r="I169" s="2" t="inlineStr">
         <is>
@@ -54382,7 +54694,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G187" s="2" t="n"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>tom_kane@bostonmutual.com</t>
+        </is>
+      </c>
       <c r="H187" s="2" t="n"/>
       <c r="I187" s="2" t="inlineStr">
         <is>
@@ -54724,7 +55040,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G193" s="2" t="n"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>rkouatcho@lacerta.com</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="n"/>
       <c r="I193" s="2" t="inlineStr">
         <is>
@@ -54783,7 +55103,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G194" s="2" t="n"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>bgabriel@metalbellows.com</t>
+        </is>
+      </c>
       <c r="H194" s="2" t="n"/>
       <c r="I194" s="2" t="inlineStr">
         <is>
@@ -54960,7 +55284,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G197" s="2" t="n"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>tony@proven-process.com</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="n"/>
       <c r="I197" s="2" t="inlineStr">
         <is>
@@ -55019,7 +55347,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G198" s="2" t="n"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>dking@acumentrics.com</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="n"/>
       <c r="I198" s="2" t="inlineStr">
         <is>
@@ -55078,7 +55410,11 @@
           <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
-      <c r="G199" s="2" t="n"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>lonnie@clinicalsciencelab.com</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="n"/>
       <c r="I199" s="2" t="inlineStr">
         <is>

--- a/5PT-Master-Prospecting-Workbook.xlsx
+++ b/5PT-Master-Prospecting-Workbook.xlsx
@@ -907,7 +907,11 @@
           <t>(781) 982-9333</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>(617) 990-2352</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Gare Reid</t>
@@ -918,7 +922,11 @@
           <t>Manager, Systems Integration</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>gare.reid@thecateredaffair.com</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Holly Safford (Founder &amp; President)</t>
@@ -960,10 +968,14 @@
           <t>thecateredaffair.com</t>
         </is>
       </c>
-      <c r="W4" s="2" t="n"/>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Runs venues across Boston area from this HQ. Employee count includes event staff. [ZoomInfo ID 7012563]</t>
+          <t>Runs venues across Boston area from this HQ. Employee count includes event staff. [ZoomInfo ID 7012563]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1025,11 @@
           <t>(781) 261-9666</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>(781) 423-3053</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>Adam Houghton</t>
@@ -1024,7 +1040,11 @@
           <t>Director, System Planning</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>ahoughton@controlpointtech.com</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Jeffrey Flint (President)</t>
@@ -1066,10 +1086,14 @@
           <t>cpteng.com</t>
         </is>
       </c>
-      <c r="W5" s="2" t="n"/>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>Same building as Food Tech. Two stops, one parking lot. [ZoomInfo ID 9470939]</t>
+          <t>Same building as Food Tech. Two stops, one parking lot. [ZoomInfo ID 9470939]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -1938,198 +1962,210 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>K5 Corporation</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>9 Rockview Way, Ste B</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>(781) 982-9229</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>Ronald Beaudoin (Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>Utility and civil construction contractor</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Contractors are prime wire fraud targets. Lead with email security and payment fraud protection.</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>24829000</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>1982</t>
         </is>
       </c>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U14" s="4" t="n"/>
+      <c r="V14" s="4" t="inlineStr">
         <is>
           <t>k5corporation.com</t>
         </is>
       </c>
-      <c r="W14" s="2" t="n"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>Next door to Commonwealth Building Systems. [ZoomInfo ID 344267938]</t>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X14" s="5" t="inlineStr">
+        <is>
+          <t>Next door to Commonwealth Building Systems. [ZoomInfo ID 344267938]  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>George T. Wilkinson</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>405 VFW Dr, Ste 1</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>(781) 335-2622</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>gwilkinson@gtwilkinson.com</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>Geoffrey Wilkinson (Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>Commercial HVAC service and mechanical contractor</t>
         </is>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>Dispatch, service software and field devices. Lead with help desk and device management.</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr">
         <is>
           <t>15840000</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>1951</t>
         </is>
       </c>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U15" s="4" t="n"/>
+      <c r="V15" s="4" t="inlineStr">
         <is>
           <t>gtwilkinson.com</t>
         </is>
       </c>
-      <c r="W15" s="2" t="n"/>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 48400778]</t>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 48400778]  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -2228,100 +2264,104 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Bendon Gear &amp; Machine</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Rockland</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>100 Weymouth St, Ste A1</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>02370</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>(781) 878-8100</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>S. Belezos (Founder and Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>Precision gear and machine shop (defense work)</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Defense suppliers face CMMC requirements. Ask how they are handling CMMC and NIST 800-171.</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>6443000</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>1966</t>
         </is>
       </c>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U17" s="4" t="n"/>
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>bendongear.com</t>
         </is>
       </c>
-      <c r="W17" s="2" t="n"/>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>ITAR and CMMC pressure is a strong door opener for machine shops. [ZoomInfo ID 7965364]</t>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X17" s="5" t="inlineStr">
+        <is>
+          <t>ITAR and CMMC pressure is a strong door opener for machine shops. [ZoomInfo ID 7965364]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2411,11 @@
           <t>(800) 225-5404</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>(781) 871-4426</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>John Connelly</t>
@@ -2382,7 +2426,11 @@
           <t>IT Specialist</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>john@foodallergy.com</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Mark McDonough (Chief Executive Officer)</t>
@@ -2424,10 +2472,14 @@
           <t>foodallergy.com</t>
         </is>
       </c>
-      <c r="W18" s="2" t="n"/>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 4066062]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 4066062]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -3912,304 +3964,320 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>North River Home Care</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>275 Longwater Dr</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>(781) 352-0939</t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="2" t="n"/>
-      <c r="L33" s="2" t="n"/>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>heather@northriverhc.com</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
         <is>
           <t>Heather Kenney (Owner)</t>
         </is>
       </c>
-      <c r="O33" s="2" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>Private home care agency</t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>Caregiver scheduling and PHI on personal devices. Lead with HIPAA and mobile device management.</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="4" t="inlineStr">
         <is>
           <t>16932000</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="4" t="inlineStr">
         <is>
           <t>1975</t>
         </is>
       </c>
-      <c r="U33" s="2" t="n"/>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="U33" s="4" t="n"/>
+      <c r="V33" s="4" t="inlineStr">
         <is>
           <t>northriverhc.com</t>
         </is>
       </c>
-      <c r="W33" s="2" t="n"/>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 347309462]</t>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 347309462]  |  ZoomInfo: email confirmed, but both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Radio Solutions</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>55 Accord Park Dr</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>(781) 561-3000</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t>Matthew Dalton</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t>Lead System Engineer</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>Admir Surkovic (President, Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>Two way radio and wireless communications dealer</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>Tech adjacent but not an MSP. Lead with M365, security and back office systems.</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S34" s="4" t="inlineStr">
         <is>
           <t>12007000</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T34" s="4" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="U34" s="2" t="n"/>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="U34" s="4" t="n"/>
+      <c r="V34" s="4" t="inlineStr">
         <is>
           <t>radiosolutionsinc.com</t>
         </is>
       </c>
-      <c r="W34" s="2" t="n"/>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>Possible referral partner too. They see every public safety and facilities buyer locally. [ZoomInfo ID 354245370]</t>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X34" s="5" t="inlineStr">
+        <is>
+          <t>Possible referral partner too. They see every public safety and facilities buyer locally. [ZoomInfo ID 354245370]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>TryAngle Foods</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>N1</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>17 Accord Park Dr, Ste 202</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>(781) 871-6969</t>
         </is>
       </c>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>Doug Vonlderstein (Founder)</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>Food distribution and provisions</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>Orders, routing and invoicing systems. Lead with uptime and email fraud protection.</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>9752000</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="U35" s="2" t="n"/>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="U35" s="4" t="n"/>
+      <c r="V35" s="4" t="inlineStr">
         <is>
           <t>tryanglefoods.com</t>
         </is>
       </c>
-      <c r="W35" s="2" t="n"/>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 126845033]</t>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 126845033]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -4259,10 +4327,18 @@
           <t>(781) 531-8227</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>(781) 783-2414</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>cmurphy@bluebearplumbing.com</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>Christopher Murphy (Owner)</t>
@@ -4304,10 +4380,14 @@
           <t>bluebearplumbing.com</t>
         </is>
       </c>
-      <c r="W36" s="2" t="n"/>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>PE style growth playbook. Headcount likely higher than listed. [ZoomInfo ID 451726485]</t>
+          <t>PE style growth playbook. Headcount likely higher than listed. [ZoomInfo ID 451726485]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -4357,10 +4437,18 @@
           <t>(781) 681-6656</t>
         </is>
       </c>
-      <c r="J37" s="2" t="n"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>(781) 421-2496</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>sean@driscollagency.com</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>Sean Driscoll (Owner)</t>
@@ -4402,10 +4490,14 @@
           <t>driscollagency.com</t>
         </is>
       </c>
-      <c r="W37" s="2" t="n"/>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 41815502]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 41815502]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -4871,10 +4963,18 @@
           <t>(888) 735-3574</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>(617) 285-2863</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>abecker@jackconway.com</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>Al Becker (Real Estate President &amp; Chief Operating Officer &amp; Agent)</t>
@@ -4916,10 +5016,14 @@
           <t>jackconway.com</t>
         </is>
       </c>
-      <c r="W42" s="2" t="n"/>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>Employee figure includes agents. Corporate staff here is much smaller. [ZoomInfo ID 17287496]</t>
+          <t>Employee figure includes agents. Corporate staff here is much smaller. [ZoomInfo ID 17287496]  |  ZoomInfo: direct line is Do Not Call; mobile (617) 285-2863 is callable.</t>
         </is>
       </c>
     </row>
@@ -5018,300 +5122,316 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Proven Behavior Solutions</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>80 Washington St, Ste Q57</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>(781) 290-3886</t>
         </is>
       </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>Kyle Bray (President &amp; Chief Operating Officer)</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>ABA therapy centers</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>Growing multi site ABA group. Lead with HIPAA, MDM and opening new sites fast.</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
+      <c r="R44" s="4" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="S44" s="4" t="inlineStr">
         <is>
           <t>2726000</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr">
+      <c r="T44" s="4" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="U44" s="2" t="n"/>
-      <c r="V44" s="2" t="inlineStr">
+      <c r="U44" s="4" t="n"/>
+      <c r="V44" s="4" t="inlineStr">
         <is>
           <t>provenaba.com</t>
         </is>
       </c>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>Queen Anne's Corner plaza. Three targets share the 80 Washington St complex. [ZoomInfo ID 397758004]</t>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X44" s="5" t="inlineStr">
+        <is>
+          <t>Queen Anne's Corner plaza. Three targets share the 80 Washington St complex. [ZoomInfo ID 397758004]  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>South Shore Autism Center</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>45 Pond St</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>(781) 421-6182</t>
         </is>
       </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>emcloughlin@southshoreautismcenter.com</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>Erin McLoughlin (Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O45" s="2" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>ABA therapy centers</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>Two growing clinic sites. Lead with HIPAA, Wi-Fi reliability and new hire device turnaround.</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="R45" s="4" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>14297000</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="T45" s="4" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="U45" s="2" t="n"/>
-      <c r="V45" s="2" t="inlineStr">
+      <c r="U45" s="4" t="n"/>
+      <c r="V45" s="4" t="inlineStr">
         <is>
           <t>ssautismcenter.com</t>
         </is>
       </c>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 403845227]</t>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 403845227]  |  ZoomInfo: email confirmed, direct line is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>LMHS, P.C.</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="4" t="inlineStr">
         <is>
           <t>Norwell</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>80 Washington St, Bldg S</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>02061</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>(781) 878-9111</t>
         </is>
       </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Randy Toscano</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
         <is>
           <t>Director, System and Business Partner</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="M46" s="4" t="n"/>
+      <c r="N46" s="4" t="n"/>
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>CPA firm</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>FTC Safeguards requires CPA firms to maintain a written security plan. Ask who owns theirs.</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="S46" s="4" t="inlineStr">
         <is>
           <t>5895000</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr">
+      <c r="T46" s="4" t="inlineStr">
         <is>
           <t>1987</t>
         </is>
       </c>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="inlineStr">
+      <c r="U46" s="4" t="n"/>
+      <c r="V46" s="4" t="inlineStr">
         <is>
           <t>lmhspc.com</t>
         </is>
       </c>
-      <c r="W46" s="2" t="n"/>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t>Same plaza as Proven Behavior and Oral Surgery South. [ZoomInfo ID 348042852]</t>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X46" s="5" t="inlineStr">
+        <is>
+          <t>Same plaza as Proven Behavior and Oral Surgery South. [ZoomInfo ID 348042852]  |  ZoomInfo: no email; both numbers Do Not Call and are out-of-state (FL/AZ). Verify the contact still sits in MA.</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5481,11 @@
           <t>(781) 871-1677</t>
         </is>
       </c>
-      <c r="J47" s="2" t="n"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>(508) 746-1614</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
@@ -5406,10 +5530,14 @@
           <t>oralsurgerysouth.com</t>
         </is>
       </c>
-      <c r="W47" s="2" t="n"/>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>4 locations. Same plaza as LMHS and Proven Behavior.</t>
+          <t>4 locations. Same plaza as LMHS and Proven Behavior.  |  ZoomInfo confirmed direct dial, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -6026,292 +6154,312 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>First Resource Management</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>2001 Washington St</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>(781) 659-0025</t>
         </is>
       </c>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>Gordon Pulsifer (President)</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>Affordable housing property management</t>
         </is>
       </c>
-      <c r="P54" s="2" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>HUD compliance paperwork and resident data across sites. Lead with secure, supported systems.</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr">
+      <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R54" s="2" t="inlineStr">
+      <c r="R54" s="4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="S54" s="4" t="inlineStr">
         <is>
           <t>14197000</t>
         </is>
       </c>
-      <c r="T54" s="2" t="inlineStr">
+      <c r="T54" s="4" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="U54" s="2" t="n"/>
-      <c r="V54" s="2" t="inlineStr">
+      <c r="U54" s="4" t="n"/>
+      <c r="V54" s="4" t="inlineStr">
         <is>
           <t>firstresourcecompanies.com</t>
         </is>
       </c>
-      <c r="W54" s="2" t="n"/>
-      <c r="X54" s="3" t="inlineStr">
-        <is>
-          <t>Across the street from Jannell Ford. [ZoomInfo ID 359188055]</t>
+      <c r="W54" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X54" s="5" t="inlineStr">
+        <is>
+          <t>Across the street from Jannell Ford. [ZoomInfo ID 359188055]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Wozny/Barbar &amp; Associates</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>1076 Washington St</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>(781) 826-4144</t>
         </is>
       </c>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="2" t="n"/>
-      <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>zwozny@wbaengineers.com</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr">
         <is>
           <t>Zbigniew Wozny (President)</t>
         </is>
       </c>
-      <c r="O55" s="2" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>MEP engineering firm</t>
         </is>
       </c>
-      <c r="P55" s="2" t="inlineStr">
+      <c r="P55" s="4" t="inlineStr">
         <is>
           <t>Revit and CAD workstations. Lead with performance, backup and project deadlines.</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr">
+      <c r="Q55" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R55" s="2" t="inlineStr">
+      <c r="R55" s="4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="S55" s="2" t="inlineStr">
+      <c r="S55" s="4" t="inlineStr">
         <is>
           <t>6880000</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr">
+      <c r="T55" s="4" t="inlineStr">
         <is>
           <t>1988</t>
         </is>
       </c>
-      <c r="U55" s="2" t="n"/>
-      <c r="V55" s="2" t="inlineStr">
+      <c r="U55" s="4" t="n"/>
+      <c r="V55" s="4" t="inlineStr">
         <is>
           <t>wbaengineers.com</t>
         </is>
       </c>
-      <c r="W55" s="2" t="n"/>
-      <c r="X55" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 353985624]</t>
+      <c r="W55" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X55" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 353985624]  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Merrill Associates</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>427 Columbia Rd</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>(781) 826-9200</t>
         </is>
       </c>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="2" t="n"/>
-      <c r="L56" s="2" t="n"/>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>bmerrill@merrillinc.com</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>Robert Merrill (President)</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>Civil engineering and land surveying</t>
         </is>
       </c>
-      <c r="P56" s="2" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>Survey data and CAD files. Lead with backup and file access speed.</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr">
+      <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R56" s="2" t="inlineStr">
+      <c r="R56" s="4" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr">
         <is>
           <t>1517000</t>
         </is>
       </c>
-      <c r="T56" s="2" t="n"/>
-      <c r="U56" s="2" t="n"/>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="T56" s="4" t="n"/>
+      <c r="U56" s="4" t="n"/>
+      <c r="V56" s="4" t="inlineStr">
         <is>
           <t>merrillinc.com</t>
         </is>
       </c>
-      <c r="W56" s="2" t="n"/>
-      <c r="X56" s="3" t="inlineStr">
-        <is>
-          <t>Same building as Homestead Mortgage. Pair the stops. [ZoomInfo ID 343333439]</t>
+      <c r="W56" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X56" s="5" t="inlineStr">
+        <is>
+          <t>Same building as Homestead Mortgage. Pair the stops. [ZoomInfo ID 343333439]  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -7302,198 +7450,214 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>A. Murphy Inc</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>35 Hanover St</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>(781) 826-0222</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
-      <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>mpmurphy@amurphy.com</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
         <is>
           <t>Michael Murphy (Owner and Operator)</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr">
         <is>
           <t>Site work and utility contractor</t>
         </is>
       </c>
-      <c r="P66" s="2" t="inlineStr">
+      <c r="P66" s="4" t="inlineStr">
         <is>
           <t>Field crews and office estimating. Lead with email fraud protection and file backup.</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="inlineStr">
+      <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R66" s="2" t="inlineStr">
+      <c r="R66" s="4" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr">
+      <c r="S66" s="4" t="inlineStr">
         <is>
           <t>12799000</t>
         </is>
       </c>
-      <c r="T66" s="2" t="inlineStr">
+      <c r="T66" s="4" t="inlineStr">
         <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="U66" s="2" t="n"/>
-      <c r="V66" s="2" t="inlineStr">
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="inlineStr">
         <is>
           <t>amurphy.com</t>
         </is>
       </c>
-      <c r="W66" s="2" t="n"/>
-      <c r="X66" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 6295262]</t>
+      <c r="W66" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 6295262]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Eyesaver International</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>H2</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Hanover</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>348 Circuit St, Ste 2</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>02339</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>(781) 829-0808</t>
         </is>
       </c>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>sgeorge@eyesaverinternational.com</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>Stephen George (President)</t>
         </is>
       </c>
-      <c r="O67" s="2" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr">
         <is>
           <t>Safety eyewear manufacturer</t>
         </is>
       </c>
-      <c r="P67" s="2" t="inlineStr">
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>Product and order systems. Lead with M365 and endpoint management.</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="R67" s="4" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr">
+      <c r="S67" s="4" t="inlineStr">
         <is>
           <t>8590000</t>
         </is>
       </c>
-      <c r="T67" s="2" t="inlineStr">
+      <c r="T67" s="4" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="U67" s="4" t="n"/>
+      <c r="V67" s="4" t="inlineStr">
         <is>
           <t>eyesaverinternational.com</t>
         </is>
       </c>
-      <c r="W67" s="2" t="n"/>
-      <c r="X67" s="3" t="inlineStr">
-        <is>
-          <t>Same building as Sturtevant. Pair the stops. [ZoomInfo ID 43125676]</t>
+      <c r="W67" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X67" s="5" t="inlineStr">
+        <is>
+          <t>Same building as Sturtevant. Pair the stops. [ZoomInfo ID 43125676]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -7543,10 +7707,18 @@
           <t>(781) 829-6501</t>
         </is>
       </c>
-      <c r="J68" s="2" t="n"/>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>(781) 829-1455</t>
+        </is>
+      </c>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>senglish@sturtevantinc.com</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>Sturt English (President &amp; Chief Executive Officer)</t>
@@ -7588,10 +7760,14 @@
           <t>sturtevantinc.com</t>
         </is>
       </c>
-      <c r="W68" s="2" t="n"/>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>Same building as Eyesaver International. [ZoomInfo ID 92094650]</t>
+          <t>Same building as Eyesaver International. [ZoomInfo ID 92094650]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -8412,108 +8588,116 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>New England Village</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>664 School St</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>(781) 293-5461</t>
         </is>
       </c>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="inlineStr">
         <is>
           <t>Tim McKinney</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="L77" s="4" t="inlineStr">
         <is>
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>tmckinney@newenglandvillage.org</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
         <is>
           <t>Christine Chagnon (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O77" s="4" t="inlineStr">
         <is>
           <t>Nonprofit for adults with disabilities</t>
         </is>
       </c>
-      <c r="P77" s="2" t="inlineStr">
+      <c r="P77" s="4" t="inlineStr">
         <is>
           <t>Resident records and lean budgets. Lead with right sized managed IT and HIPAA.</t>
         </is>
       </c>
-      <c r="Q77" s="2" t="inlineStr">
+      <c r="Q77" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R77" s="2" t="inlineStr">
+      <c r="R77" s="4" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr">
+      <c r="S77" s="4" t="inlineStr">
         <is>
           <t>5359000</t>
         </is>
       </c>
-      <c r="T77" s="2" t="inlineStr">
+      <c r="T77" s="4" t="inlineStr">
         <is>
           <t>1972</t>
         </is>
       </c>
-      <c r="U77" s="2" t="n"/>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="U77" s="4" t="n"/>
+      <c r="V77" s="4" t="inlineStr">
         <is>
           <t>newenglandvillage.org</t>
         </is>
       </c>
-      <c r="W77" s="2" t="n"/>
-      <c r="X77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 27394913]</t>
+      <c r="W77" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 27394913]  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -8563,10 +8747,18 @@
           <t>(781) 293-1200</t>
         </is>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>(617) 448-2406</t>
+        </is>
+      </c>
       <c r="K78" s="2" t="n"/>
       <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>jen@preferredmechanicalservices.com</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>Jennifer Meade (Founder)</t>
@@ -8608,116 +8800,124 @@
           <t>preferredmechanicalservices.com</t>
         </is>
       </c>
-      <c r="W78" s="2" t="n"/>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 345994045]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 345994045]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Your Electrical Solution</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>345 Washington St</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>(781) 331-3500</t>
         </is>
       </c>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="J79" s="4" t="n"/>
+      <c r="K79" s="4" t="inlineStr">
         <is>
           <t>Peter Ockerbloom</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="L79" s="4" t="inlineStr">
         <is>
           <t>Telecom Systems Technician</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="M79" s="4" t="n"/>
+      <c r="N79" s="4" t="inlineStr">
         <is>
           <t>Bruce Sylvester (Owner)</t>
         </is>
       </c>
-      <c r="O79" s="2" t="inlineStr">
+      <c r="O79" s="4" t="inlineStr">
         <is>
           <t>Electrical contractor</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
+      <c r="P79" s="4" t="inlineStr">
         <is>
           <t>Growing contractor. Lead with email fraud protection and field device support.</t>
         </is>
       </c>
-      <c r="Q79" s="2" t="inlineStr">
+      <c r="Q79" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R79" s="2" t="inlineStr">
+      <c r="R79" s="4" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr">
+      <c r="S79" s="4" t="inlineStr">
         <is>
           <t>23819000</t>
         </is>
       </c>
-      <c r="T79" s="2" t="inlineStr">
+      <c r="T79" s="4" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="U79" s="2" t="n"/>
-      <c r="V79" s="2" t="inlineStr">
+      <c r="U79" s="4" t="n"/>
+      <c r="V79" s="4" t="inlineStr">
         <is>
           <t>yourelectricalsolutions.com</t>
         </is>
       </c>
-      <c r="W79" s="2" t="n"/>
-      <c r="X79" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 450765740]</t>
+      <c r="W79" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X79" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 450765740]  |  ZoomInfo: no email, mobile is Do Not Call. Use company main line.</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8967,11 @@
           <t>(781) 826-1546</t>
         </is>
       </c>
-      <c r="J80" s="2" t="n"/>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>(781) 422-8805</t>
+        </is>
+      </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
           <t>Jonathan Epstein</t>
@@ -8820,10 +9024,14 @@
           <t>rsidelivers.com</t>
         </is>
       </c>
-      <c r="W80" s="2" t="n"/>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>Same complex as Royal Health Group. Pair the stops. [ZoomInfo ID 122601758]</t>
+          <t>Same complex as Royal Health Group. Pair the stops. [ZoomInfo ID 122601758]  |  ZoomInfo confirmed direct dial, callable. No email on file. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -8873,10 +9081,18 @@
           <t>(781) 681-9240</t>
         </is>
       </c>
-      <c r="J81" s="2" t="n"/>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>(781) 421-0918</t>
+        </is>
+      </c>
       <c r="K81" s="2" t="n"/>
       <c r="L81" s="2" t="n"/>
-      <c r="M81" s="2" t="n"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>sschrader@acellaconstruction.com</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>Saul Schrader (President)</t>
@@ -8918,214 +9134,234 @@
           <t>acellaconstruction.com</t>
         </is>
       </c>
-      <c r="W81" s="2" t="n"/>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>Builds for healthcare and schools locally. Referral rich. [ZoomInfo ID 722847]</t>
+          <t>Builds for healthcare and schools locally. Referral rich. [ZoomInfo ID 722847]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Ritchie Navigation</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>243 Oak St</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>(781) 826-5131</t>
         </is>
       </c>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="2" t="n"/>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="2" t="n"/>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+      <c r="L82" s="4" t="n"/>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>jsherman@ritchienavigation.com</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
         <is>
           <t>Jonathan Sherman (President)</t>
         </is>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" s="4" t="inlineStr">
         <is>
           <t>Marine compass manufacturer since 1850</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
+      <c r="P82" s="4" t="inlineStr">
         <is>
           <t>Storied manufacturer. Lead with modern security wrapped around legacy systems.</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="inlineStr">
+      <c r="Q82" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R82" s="2" t="inlineStr">
+      <c r="R82" s="4" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr">
+      <c r="S82" s="4" t="inlineStr">
         <is>
           <t>8845000</t>
         </is>
       </c>
-      <c r="T82" s="2" t="inlineStr">
+      <c r="T82" s="4" t="inlineStr">
         <is>
           <t>1850</t>
         </is>
       </c>
-      <c r="U82" s="2" t="n"/>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="U82" s="4" t="n"/>
+      <c r="V82" s="4" t="inlineStr">
         <is>
           <t>ritchienavigation.com</t>
         </is>
       </c>
-      <c r="W82" s="2" t="n"/>
-      <c r="X82" s="3" t="inlineStr">
-        <is>
-          <t>America's oldest compass maker. Great conversation starter. [ZoomInfo ID 87149342]</t>
+      <c r="W82" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X82" s="5" t="inlineStr">
+        <is>
+          <t>America's oldest compass maker. Great conversation starter. [ZoomInfo ID 87149342]  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Protectowire FireSystems</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>Pembroke</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>60 Washington St</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>02359</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>(781) 826-3878</t>
         </is>
       </c>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="J83" s="4" t="n"/>
+      <c r="K83" s="4" t="inlineStr">
         <is>
           <t>Michael Hall</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="L83" s="4" t="inlineStr">
         <is>
           <t>System Engineer</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n"/>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="M83" s="4" t="inlineStr">
+        <is>
+          <t>mhall@protectowire.com</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
         <is>
           <t>Gerald Holmes (Founder)</t>
         </is>
       </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="O83" s="4" t="inlineStr">
         <is>
           <t>Linear heat detection manufacturer, HQ</t>
         </is>
       </c>
-      <c r="P83" s="2" t="inlineStr">
+      <c r="P83" s="4" t="inlineStr">
         <is>
           <t>Global OEM with engineering IP. Lead with security and dependable office IT.</t>
         </is>
       </c>
-      <c r="Q83" s="2" t="inlineStr">
+      <c r="Q83" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R83" s="2" t="inlineStr">
+      <c r="R83" s="4" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr">
+      <c r="S83" s="4" t="inlineStr">
         <is>
           <t>18925000</t>
         </is>
       </c>
-      <c r="T83" s="2" t="inlineStr">
+      <c r="T83" s="4" t="inlineStr">
         <is>
           <t>1938</t>
         </is>
       </c>
-      <c r="U83" s="2" t="n"/>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="U83" s="4" t="n"/>
+      <c r="V83" s="4" t="inlineStr">
         <is>
           <t>protectowire.com</t>
         </is>
       </c>
-      <c r="W83" s="2" t="n"/>
-      <c r="X83" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 64980067]</t>
+      <c r="W83" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X83" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 64980067]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10505,11 @@
           <t>(781) 293-9711</t>
         </is>
       </c>
-      <c r="J95" s="2" t="n"/>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>(203) 401-9792</t>
+        </is>
+      </c>
       <c r="K95" s="2" t="n"/>
       <c r="L95" s="2" t="n"/>
       <c r="M95" s="2" t="n"/>
@@ -10310,304 +10550,332 @@
           <t>sullivansusa.com</t>
         </is>
       </c>
-      <c r="W95" s="2" t="n"/>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X95" s="3" t="inlineStr">
         <is>
-          <t>Family owned since 1948 era roots. Verified via web. [ZoomInfo ID 371652590]</t>
+          <t>Family owned since 1948 era roots. Verified via web. [ZoomInfo ID 371652590]  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Seoane Landscape Design</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>Abington</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>551 Bedford St</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G96" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>02351</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>(781) 878-1306</t>
         </is>
       </c>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" s="2" t="n"/>
-      <c r="L96" s="2" t="n"/>
-      <c r="M96" s="2" t="n"/>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="J96" s="4" t="n"/>
+      <c r="K96" s="4" t="n"/>
+      <c r="L96" s="4" t="n"/>
+      <c r="M96" s="4" t="inlineStr">
+        <is>
+          <t>lou@seoanelandscape.com</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
         <is>
           <t>Louis Seoane (President, Operations &amp; Sales)</t>
         </is>
       </c>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" s="4" t="inlineStr">
         <is>
           <t>Commercial landscape design and construction</t>
         </is>
       </c>
-      <c r="P96" s="2" t="inlineStr">
+      <c r="P96" s="4" t="inlineStr">
         <is>
           <t>Crews, scheduling and billing. Lead with simple managed IT that keeps trucks rolling.</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="inlineStr">
+      <c r="Q96" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R96" s="2" t="inlineStr">
+      <c r="R96" s="4" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr">
+      <c r="S96" s="4" t="inlineStr">
         <is>
           <t>22537000</t>
         </is>
       </c>
-      <c r="T96" s="2" t="inlineStr">
+      <c r="T96" s="4" t="inlineStr">
         <is>
           <t>1972</t>
         </is>
       </c>
-      <c r="U96" s="2" t="n"/>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="U96" s="4" t="n"/>
+      <c r="V96" s="4" t="inlineStr">
         <is>
           <t>seoanelandscape.com</t>
         </is>
       </c>
-      <c r="W96" s="2" t="n"/>
-      <c r="X96" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 55133071]</t>
+      <c r="W96" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X96" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 55133071]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Whitman Company</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>Whitman</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>356 South Ave</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>02382</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>(781) 447-2422</t>
         </is>
       </c>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="n"/>
-      <c r="L97" s="2" t="n"/>
-      <c r="M97" s="2" t="n"/>
-      <c r="N97" s="2" t="inlineStr">
+      <c r="J97" s="4" t="n"/>
+      <c r="K97" s="4" t="n"/>
+      <c r="L97" s="4" t="n"/>
+      <c r="M97" s="4" t="inlineStr">
+        <is>
+          <t>will@whitmanllc.com</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
         <is>
           <t>William Whitman (President)</t>
         </is>
       </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="O97" s="4" t="inlineStr">
         <is>
           <t>Metal finishing and plating</t>
         </is>
       </c>
-      <c r="P97" s="2" t="inlineStr">
+      <c r="P97" s="4" t="inlineStr">
         <is>
           <t>Plating lines and quality certs. Lead with production uptime and simple secure IT.</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="inlineStr">
+      <c r="Q97" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R97" s="2" t="inlineStr">
+      <c r="R97" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr">
+      <c r="S97" s="4" t="inlineStr">
         <is>
           <t>17480000</t>
         </is>
       </c>
-      <c r="T97" s="2" t="inlineStr">
+      <c r="T97" s="4" t="inlineStr">
         <is>
           <t>1894</t>
         </is>
       </c>
-      <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="inlineStr">
+      <c r="U97" s="4" t="n"/>
+      <c r="V97" s="4" t="inlineStr">
         <is>
           <t>whitman-company.com</t>
         </is>
       </c>
-      <c r="W97" s="2" t="n"/>
-      <c r="X97" s="3" t="inlineStr">
-        <is>
-          <t>Address confirmed via web. ZoomInfo listing was incomplete. [ZoomInfo ID 128385304]</t>
+      <c r="W97" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X97" s="5" t="inlineStr">
+        <is>
+          <t>Address confirmed via web. ZoomInfo listing was incomplete. [ZoomInfo ID 128385304]  |  VERIFY: ZoomInfo returned title Attorney under a different company record. Confirm this is the right William Whitman before using.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Defense Investigators Group</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>Hanson</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>PO Box 119 (call ahead)</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G98" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>02341</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>(800) 233-0417</t>
         </is>
       </c>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="2" t="n"/>
-      <c r="L98" s="2" t="n"/>
-      <c r="M98" s="2" t="n"/>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="J98" s="4" t="n"/>
+      <c r="K98" s="4" t="n"/>
+      <c r="L98" s="4" t="n"/>
+      <c r="M98" s="4" t="inlineStr">
+        <is>
+          <t>don@d-i-g.com</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
         <is>
           <t>Don Anderson (Owner)</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="O98" s="4" t="inlineStr">
         <is>
           <t>Insurance defense investigations</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
+      <c r="P98" s="4" t="inlineStr">
         <is>
           <t>Sensitive case files and field investigators. Lead with security and secure remote access.</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr">
+      <c r="Q98" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R98" s="2" t="inlineStr">
+      <c r="R98" s="4" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="S98" s="2" t="inlineStr">
+      <c r="S98" s="4" t="inlineStr">
         <is>
           <t>16655000</t>
         </is>
       </c>
-      <c r="T98" s="2" t="inlineStr">
+      <c r="T98" s="4" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="U98" s="2" t="n"/>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="U98" s="4" t="n"/>
+      <c r="V98" s="4" t="inlineStr">
         <is>
           <t>defenseinvestigatorsgroup.com</t>
         </is>
       </c>
-      <c r="W98" s="2" t="n"/>
-      <c r="X98" s="3" t="inlineStr">
-        <is>
-          <t>Street address not published. Call before attempting a visit.</t>
+      <c r="W98" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X98" s="5" t="inlineStr">
+        <is>
+          <t>Street address not published. Call before attempting a visit.  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -10706,100 +10974,108 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>Webster Printing</t>
         </is>
       </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="D100" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="4" t="inlineStr">
         <is>
           <t>Hanson</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>1069 W Washington St</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>02341</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>(781) 447-5484</t>
         </is>
       </c>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="2" t="n"/>
-      <c r="L100" s="2" t="n"/>
-      <c r="M100" s="2" t="n"/>
-      <c r="N100" s="2" t="inlineStr">
+      <c r="J100" s="4" t="n"/>
+      <c r="K100" s="4" t="n"/>
+      <c r="L100" s="4" t="n"/>
+      <c r="M100" s="4" t="inlineStr">
+        <is>
+          <t>ernie@websterprinting.com</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
         <is>
           <t>Ernest Foster (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O100" s="2" t="inlineStr">
+      <c r="O100" s="4" t="inlineStr">
         <is>
           <t>Commercial printing</t>
         </is>
       </c>
-      <c r="P100" s="2" t="inlineStr">
+      <c r="P100" s="4" t="inlineStr">
         <is>
           <t>Prepress files and tight deadlines. Lead with backup and workstation reliability.</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="inlineStr">
+      <c r="Q100" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R100" s="2" t="inlineStr">
+      <c r="R100" s="4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S100" s="2" t="inlineStr">
+      <c r="S100" s="4" t="inlineStr">
         <is>
           <t>6726000</t>
         </is>
       </c>
-      <c r="T100" s="2" t="inlineStr">
+      <c r="T100" s="4" t="inlineStr">
         <is>
           <t>1956</t>
         </is>
       </c>
-      <c r="U100" s="2" t="n"/>
-      <c r="V100" s="2" t="inlineStr">
+      <c r="U100" s="4" t="n"/>
+      <c r="V100" s="4" t="inlineStr">
         <is>
           <t>websterprinting.com</t>
         </is>
       </c>
-      <c r="W100" s="2" t="n"/>
-      <c r="X100" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 353908367]</t>
+      <c r="W100" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X100" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 353908367]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -10849,10 +11125,18 @@
           <t>(781) 447-0421</t>
         </is>
       </c>
-      <c r="J101" s="2" t="n"/>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>(781) 350-5181</t>
+        </is>
+      </c>
       <c r="K101" s="2" t="n"/>
       <c r="L101" s="2" t="n"/>
-      <c r="M101" s="2" t="n"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>pawerthen@whitmantoolanddie.com</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>Peter Werthen (Buyer &amp; Owner)</t>
@@ -10894,108 +11178,120 @@
           <t>whitmantoolanddie.com</t>
         </is>
       </c>
-      <c r="W101" s="2" t="n"/>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X101" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 36425109]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 36425109]  |  ZoomInfo confirmed email and direct dial, callable.</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>President Titanium</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Hanson</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>243 Franklin St</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>02341</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>(781) 294-0000</t>
         </is>
       </c>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" s="2" t="n"/>
-      <c r="L102" s="2" t="n"/>
-      <c r="M102" s="2" t="n"/>
-      <c r="N102" s="2" t="inlineStr">
+      <c r="J102" s="4" t="n"/>
+      <c r="K102" s="4" t="n"/>
+      <c r="L102" s="4" t="n"/>
+      <c r="M102" s="4" t="inlineStr">
+        <is>
+          <t>shawn@presidenttitanium.com</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
         <is>
           <t>Shawn MacLeod (President)</t>
         </is>
       </c>
-      <c r="O102" s="2" t="inlineStr">
+      <c r="O102" s="4" t="inlineStr">
         <is>
           <t>Titanium bar and alloy stock distributor</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr">
+      <c r="P102" s="4" t="inlineStr">
         <is>
           <t>Aerospace customers mean traceability. Ask about CMMC and quality system uptime.</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="inlineStr">
+      <c r="Q102" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R102" s="2" t="inlineStr">
+      <c r="R102" s="4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr">
+      <c r="S102" s="4" t="inlineStr">
         <is>
           <t>4509000</t>
         </is>
       </c>
-      <c r="T102" s="2" t="inlineStr">
+      <c r="T102" s="4" t="inlineStr">
         <is>
           <t>1973</t>
         </is>
       </c>
-      <c r="U102" s="2" t="n"/>
-      <c r="V102" s="2" t="inlineStr">
+      <c r="U102" s="4" t="n"/>
+      <c r="V102" s="4" t="inlineStr">
         <is>
           <t>presidenttitanium.com</t>
         </is>
       </c>
-      <c r="W102" s="2" t="n"/>
-      <c r="X102" s="3" t="inlineStr">
-        <is>
-          <t>Near Sullivan's on Franklin St. Pair the stops. [ZoomInfo ID 85656175]</t>
+      <c r="W102" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X102" s="5" t="inlineStr">
+        <is>
+          <t>Near Sullivan's on Franklin St. Pair the stops. [ZoomInfo ID 85656175]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12645,11 @@
           <t>(781) 340-1400</t>
         </is>
       </c>
-      <c r="J115" s="2" t="n"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>(781) 974-5923</t>
+        </is>
+      </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
           <t>Bryce Bailey</t>
@@ -12360,7 +12660,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M115" s="2" t="n"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>bbailey@egsawyer.com</t>
+        </is>
+      </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
           <t>Tyrone Sandefur (General Manager)</t>
@@ -12402,312 +12706,336 @@
           <t>egsawyer.com</t>
         </is>
       </c>
-      <c r="W115" s="2" t="n"/>
+      <c r="W115" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X115" s="3" t="inlineStr">
         <is>
-          <t>Libbey Industrial Pkwy anchor stop. [ZoomInfo ID 31693971]</t>
+          <t>Libbey Industrial Pkwy anchor stop. [ZoomInfo ID 31693971]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>Harold Brothers Mechanical</t>
         </is>
       </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="D116" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Weymouth</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F116" s="4" t="inlineStr">
         <is>
           <t>44 Woodrock Rd Ste 1</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>02189</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="I116" s="4" t="inlineStr">
         <is>
           <t>(781) 871-2111</t>
         </is>
       </c>
-      <c r="J116" s="2" t="n"/>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="J116" s="4" t="n"/>
+      <c r="K116" s="4" t="inlineStr">
         <is>
           <t>Briyanna Arklein</t>
         </is>
       </c>
-      <c r="L116" s="2" t="inlineStr">
+      <c r="L116" s="4" t="inlineStr">
         <is>
           <t>IT Specialist</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
-      <c r="N116" s="2" t="inlineStr">
+      <c r="M116" s="4" t="n"/>
+      <c r="N116" s="4" t="inlineStr">
         <is>
           <t>John Harold (President)</t>
         </is>
       </c>
-      <c r="O116" s="2" t="inlineStr">
+      <c r="O116" s="4" t="inlineStr">
         <is>
           <t>Mechanical contractor</t>
         </is>
       </c>
-      <c r="P116" s="2" t="inlineStr">
+      <c r="P116" s="4" t="inlineStr">
         <is>
           <t>Contractors are prime wire fraud targets. Lead with email security and estimating uptime.</t>
         </is>
       </c>
-      <c r="Q116" s="2" t="inlineStr">
+      <c r="Q116" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R116" s="2" t="inlineStr">
+      <c r="R116" s="4" t="inlineStr">
         <is>
           <t>219</t>
         </is>
       </c>
-      <c r="S116" s="2" t="inlineStr">
+      <c r="S116" s="4" t="inlineStr">
         <is>
           <t>123485000</t>
         </is>
       </c>
-      <c r="T116" s="2" t="inlineStr">
+      <c r="T116" s="4" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U116" s="2" t="n"/>
-      <c r="V116" s="2" t="inlineStr">
+      <c r="U116" s="4" t="n"/>
+      <c r="V116" s="4" t="inlineStr">
         <is>
           <t>haroldbros.com</t>
         </is>
       </c>
-      <c r="W116" s="2" t="n"/>
-      <c r="X116" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 347288554]</t>
+      <c r="W116" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X116" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 347288554]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Harbor Clinical</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F117" s="4" t="inlineStr">
         <is>
           <t>94 Otis St</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>(781) 775-0342</t>
         </is>
       </c>
-      <c r="J117" s="2" t="n"/>
-      <c r="K117" s="2" t="n"/>
-      <c r="L117" s="2" t="n"/>
-      <c r="M117" s="2" t="n"/>
-      <c r="N117" s="2" t="inlineStr">
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="4" t="n"/>
+      <c r="L117" s="4" t="n"/>
+      <c r="M117" s="4" t="inlineStr">
+        <is>
+          <t>ann.conner@harborclinical.com</t>
+        </is>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
         <is>
           <t>Ann Conner (President)</t>
         </is>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O117" s="4" t="inlineStr">
         <is>
           <t>Clinical trial services (CRO)</t>
         </is>
       </c>
-      <c r="P117" s="2" t="inlineStr">
+      <c r="P117" s="4" t="inlineStr">
         <is>
           <t>PHI and EHR uptime on a lean team. Lead with a HIPAA security risk assessment.</t>
         </is>
       </c>
-      <c r="Q117" s="2" t="inlineStr">
+      <c r="Q117" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R117" s="2" t="inlineStr">
+      <c r="R117" s="4" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr">
+      <c r="S117" s="4" t="inlineStr">
         <is>
           <t>29361000</t>
         </is>
       </c>
-      <c r="T117" s="2" t="inlineStr">
+      <c r="T117" s="4" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="U117" s="2" t="n"/>
-      <c r="V117" s="2" t="inlineStr">
+      <c r="U117" s="4" t="n"/>
+      <c r="V117" s="4" t="inlineStr">
         <is>
           <t>harborclinical.com</t>
         </is>
       </c>
-      <c r="W117" s="2" t="n"/>
-      <c r="X117" s="3" t="inlineStr">
-        <is>
-          <t>Life sciences services. Compliance heavy, lean IT. [ZoomInfo ID 435710361]</t>
+      <c r="W117" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X117" s="5" t="inlineStr">
+        <is>
+          <t>Life sciences services. Compliance heavy, lean IT. [ZoomInfo ID 435710361]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Wellness Workdays</t>
         </is>
       </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F118" s="4" t="inlineStr">
         <is>
           <t>21 Fottler Rd</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>(781) 741-5483</t>
         </is>
       </c>
-      <c r="J118" s="2" t="n"/>
-      <c r="K118" s="2" t="n"/>
-      <c r="L118" s="2" t="n"/>
-      <c r="M118" s="2" t="n"/>
-      <c r="N118" s="2" t="inlineStr">
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n"/>
+      <c r="L118" s="4" t="n"/>
+      <c r="M118" s="4" t="inlineStr">
+        <is>
+          <t>debra@wellnessworkdays.com</t>
+        </is>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
         <is>
           <t>Debra Wein (Chief Executive Officer &amp; Founder)</t>
         </is>
       </c>
-      <c r="O118" s="2" t="inlineStr">
+      <c r="O118" s="4" t="inlineStr">
         <is>
           <t>Corporate wellness programs</t>
         </is>
       </c>
-      <c r="P118" s="2" t="inlineStr">
+      <c r="P118" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q118" s="2" t="inlineStr">
+      <c r="Q118" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R118" s="2" t="inlineStr">
+      <c r="R118" s="4" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="S118" s="2" t="inlineStr">
+      <c r="S118" s="4" t="inlineStr">
         <is>
           <t>7368000</t>
         </is>
       </c>
-      <c r="T118" s="2" t="inlineStr">
+      <c r="T118" s="4" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="U118" s="2" t="n"/>
-      <c r="V118" s="2" t="inlineStr">
+      <c r="U118" s="4" t="n"/>
+      <c r="V118" s="4" t="inlineStr">
         <is>
           <t>wellnessworkdays.com</t>
         </is>
       </c>
-      <c r="W118" s="2" t="n"/>
-      <c r="X118" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 352540974]</t>
+      <c r="W118" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 352540974]  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -12757,7 +13085,11 @@
           <t>(781) 902-0304</t>
         </is>
       </c>
-      <c r="J119" s="2" t="n"/>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>(218) 543-7523</t>
+        </is>
+      </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
           <t>Tait Hoglund</t>
@@ -12768,7 +13100,11 @@
           <t>Senior Infrastructure Engineer</t>
         </is>
       </c>
-      <c r="M119" s="2" t="n"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>tait.hoglund@o2x.com</t>
+        </is>
+      </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
           <t>Paul McCullough (President &amp; Co-Founder)</t>
@@ -12810,10 +13146,14 @@
           <t>o2x.com</t>
         </is>
       </c>
-      <c r="W119" s="2" t="n"/>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X119" s="3" t="inlineStr">
         <is>
-          <t>Scituate Harbor office. Veteran founded. [ZoomInfo ID 363727526]</t>
+          <t>Scituate Harbor office. Veteran founded. [ZoomInfo ID 363727526]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -12912,198 +13252,214 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>McDonald Electric</t>
         </is>
       </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="D121" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F121" s="4" t="inlineStr">
         <is>
           <t>72 Sharp St Ste C8</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H121" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>(781) 340-0008</t>
         </is>
       </c>
-      <c r="J121" s="2" t="n"/>
-      <c r="K121" s="2" t="n"/>
-      <c r="L121" s="2" t="n"/>
-      <c r="M121" s="2" t="n"/>
-      <c r="N121" s="2" t="inlineStr">
+      <c r="J121" s="4" t="n"/>
+      <c r="K121" s="4" t="n"/>
+      <c r="L121" s="4" t="n"/>
+      <c r="M121" s="4" t="inlineStr">
+        <is>
+          <t>sbuccigross@mcdonaldcorp.com</t>
+        </is>
+      </c>
+      <c r="N121" s="4" t="inlineStr">
         <is>
           <t>Steven Buccigross (Chief Operating Officer)</t>
         </is>
       </c>
-      <c r="O121" s="2" t="inlineStr">
+      <c r="O121" s="4" t="inlineStr">
         <is>
           <t>Electrical contractor</t>
         </is>
       </c>
-      <c r="P121" s="2" t="inlineStr">
+      <c r="P121" s="4" t="inlineStr">
         <is>
           <t>Contractors are prime wire fraud targets. Lead with email security and estimating uptime.</t>
         </is>
       </c>
-      <c r="Q121" s="2" t="inlineStr">
+      <c r="Q121" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R121" s="2" t="inlineStr">
+      <c r="R121" s="4" t="inlineStr">
         <is>
           <t>96</t>
         </is>
       </c>
-      <c r="S121" s="2" t="inlineStr">
+      <c r="S121" s="4" t="inlineStr">
         <is>
           <t>18414000</t>
         </is>
       </c>
-      <c r="T121" s="2" t="inlineStr">
+      <c r="T121" s="4" t="inlineStr">
         <is>
           <t>1990</t>
         </is>
       </c>
-      <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="inlineStr">
+      <c r="U121" s="4" t="n"/>
+      <c r="V121" s="4" t="inlineStr">
         <is>
           <t>mcdonaldcorp.com</t>
         </is>
       </c>
-      <c r="W121" s="2" t="n"/>
-      <c r="X121" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 363797900]</t>
+      <c r="W121" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X121" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 363797900]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>New England Hospice</t>
         </is>
       </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>Hingham</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F122" s="4" t="inlineStr">
         <is>
           <t>190 Old Derby St Ste 304</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H122" s="4" t="inlineStr">
         <is>
           <t>02043</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="I122" s="4" t="inlineStr">
         <is>
           <t>(781) 749-2900</t>
         </is>
       </c>
-      <c r="J122" s="2" t="n"/>
-      <c r="K122" s="2" t="n"/>
-      <c r="L122" s="2" t="n"/>
-      <c r="M122" s="2" t="n"/>
-      <c r="N122" s="2" t="inlineStr">
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="4" t="n"/>
+      <c r="L122" s="4" t="n"/>
+      <c r="M122" s="4" t="inlineStr">
+        <is>
+          <t>gregg_estey@newenglandhospice.com</t>
+        </is>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
         <is>
           <t>Gregg Estey (Owner and Administrator)</t>
         </is>
       </c>
-      <c r="O122" s="2" t="inlineStr">
+      <c r="O122" s="4" t="inlineStr">
         <is>
           <t>Hospice care</t>
         </is>
       </c>
-      <c r="P122" s="2" t="inlineStr">
+      <c r="P122" s="4" t="inlineStr">
         <is>
           <t>PHI and EHR uptime on a lean team. Lead with a HIPAA security risk assessment.</t>
         </is>
       </c>
-      <c r="Q122" s="2" t="inlineStr">
+      <c r="Q122" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R122" s="2" t="inlineStr">
+      <c r="R122" s="4" t="inlineStr">
         <is>
           <t>87</t>
         </is>
       </c>
-      <c r="S122" s="2" t="inlineStr">
+      <c r="S122" s="4" t="inlineStr">
         <is>
           <t>12715000</t>
         </is>
       </c>
-      <c r="T122" s="2" t="inlineStr">
+      <c r="T122" s="4" t="inlineStr">
         <is>
           <t>2002</t>
         </is>
       </c>
-      <c r="U122" s="2" t="n"/>
-      <c r="V122" s="2" t="inlineStr">
+      <c r="U122" s="4" t="n"/>
+      <c r="V122" s="4" t="inlineStr">
         <is>
           <t>newenglandhospice.com</t>
         </is>
       </c>
-      <c r="W122" s="2" t="n"/>
-      <c r="X122" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 345317503]</t>
+      <c r="W122" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X122" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 345317503]  |  ZoomInfo: email confirmed, direct line is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13607,11 @@
           <t>(800) 445-6607</t>
         </is>
       </c>
-      <c r="J124" s="2" t="n"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>(917) 834-1910</t>
+        </is>
+      </c>
       <c r="K124" s="2" t="n"/>
       <c r="L124" s="2" t="n"/>
       <c r="M124" s="2" t="n"/>
@@ -13296,104 +13656,112 @@
           <t>hartsupply.com</t>
         </is>
       </c>
-      <c r="W124" s="2" t="n"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X124" s="3" t="inlineStr">
         <is>
-          <t>Same street as South Shore Orthopedics. [ZoomInfo ID 53858535]</t>
+          <t>Same street as South Shore Orthopedics. [ZoomInfo ID 53858535]  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>Boxerbrand</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>S1</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>Weymouth</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>293 Libbey Industrial Pkwy Ste 500</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>02189</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>(617) 269-8244</t>
         </is>
       </c>
-      <c r="J125" s="2" t="n"/>
-      <c r="K125" s="2" t="n"/>
-      <c r="L125" s="2" t="n"/>
-      <c r="M125" s="2" t="n"/>
-      <c r="N125" s="2" t="inlineStr">
+      <c r="J125" s="4" t="n"/>
+      <c r="K125" s="4" t="n"/>
+      <c r="L125" s="4" t="n"/>
+      <c r="M125" s="4" t="n"/>
+      <c r="N125" s="4" t="inlineStr">
         <is>
           <t>Luis Paniagua (Plant Manager)</t>
         </is>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O125" s="4" t="inlineStr">
         <is>
           <t>Menu cover and hospitality products manufacturer</t>
         </is>
       </c>
-      <c r="P125" s="2" t="inlineStr">
+      <c r="P125" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q125" s="2" t="inlineStr">
+      <c r="Q125" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R125" s="2" t="inlineStr">
+      <c r="R125" s="4" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="S125" s="2" t="inlineStr">
+      <c r="S125" s="4" t="inlineStr">
         <is>
           <t>19485000</t>
         </is>
       </c>
-      <c r="T125" s="2" t="n"/>
-      <c r="U125" s="2" t="n"/>
-      <c r="V125" s="2" t="inlineStr">
+      <c r="T125" s="4" t="n"/>
+      <c r="U125" s="4" t="n"/>
+      <c r="V125" s="4" t="inlineStr">
         <is>
           <t>boxerbrand.com</t>
         </is>
       </c>
-      <c r="W125" s="2" t="n"/>
-      <c r="X125" s="3" t="inlineStr">
-        <is>
-          <t>Same parkway as EG Sawyer. [ZoomInfo ID 12667248]</t>
+      <c r="W125" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X125" s="5" t="inlineStr">
+        <is>
+          <t>Same parkway as EG Sawyer. [ZoomInfo ID 12667248]  |  ZoomInfo: no email; both direct and mobile are Do Not Call. Use company main line.</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14389,11 @@
           <t>(800) 227-1464</t>
         </is>
       </c>
-      <c r="J131" s="2" t="n"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>(412) 228-5127</t>
+        </is>
+      </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
           <t>Louis Pappa</t>
@@ -14032,7 +14404,11 @@
           <t>Information Security Officer</t>
         </is>
       </c>
-      <c r="M131" s="2" t="n"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>louis.pappa@mcmcllc.com</t>
+        </is>
+      </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
           <t>Mario Corbiciero (President)</t>
@@ -14074,10 +14450,14 @@
           <t>mcmcllc.com</t>
         </is>
       </c>
-      <c r="W131" s="2" t="n"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X131" s="3" t="inlineStr">
         <is>
-          <t>Crown Colony office park cluster. [ZoomInfo ID 36242667]</t>
+          <t>Crown Colony office park cluster. [ZoomInfo ID 36242667]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14507,11 @@
           <t>(617) 472-6500</t>
         </is>
       </c>
-      <c r="J132" s="2" t="n"/>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>(617) 221-1551</t>
+        </is>
+      </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
           <t>Lawrence Levesque</t>
@@ -14138,7 +14522,11 @@
           <t>Senior Business Systems Analyst</t>
         </is>
       </c>
-      <c r="M132" s="2" t="n"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>larry.levesque@granitecityelectric.com</t>
+        </is>
+      </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
           <t>Phyllis Godwin (Chairman &amp; Chief Executive Officer)</t>
@@ -14180,10 +14568,14 @@
           <t>granitecityelectric.com</t>
         </is>
       </c>
-      <c r="W132" s="2" t="n"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X132" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 45878157]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 45878157]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14625,11 @@
           <t>(617) 825-6930</t>
         </is>
       </c>
-      <c r="J133" s="2" t="n"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>(617) 825-6930 ext. 156</t>
+        </is>
+      </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
           <t>Mahmoud Yassine</t>
@@ -14244,7 +14640,11 @@
           <t>Director, Management Information Systems</t>
         </is>
       </c>
-      <c r="M133" s="2" t="n"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>myassine@leekennedy.com</t>
+        </is>
+      </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
           <t>Bob O'Leary (President)</t>
@@ -14286,10 +14686,14 @@
           <t>leekennedy.com</t>
         </is>
       </c>
-      <c r="W133" s="2" t="n"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X133" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 62097206]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 62097206]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -14339,10 +14743,18 @@
           <t>(617) 471-8400</t>
         </is>
       </c>
-      <c r="J134" s="2" t="n"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>(617) 471-8400 ext. 114</t>
+        </is>
+      </c>
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="2" t="n"/>
-      <c r="M134" s="2" t="n"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>dcox@baystatecs.org</t>
+        </is>
+      </c>
       <c r="N134" s="2" t="inlineStr">
         <is>
           <t>Daurice Cox (President &amp; Chief Executive Officer)</t>
@@ -14384,10 +14796,14 @@
           <t>baystatecs.org</t>
         </is>
       </c>
-      <c r="W134" s="2" t="n"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X134" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 8587981]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 8587981]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -14437,10 +14853,18 @@
           <t>(617) 773-5800</t>
         </is>
       </c>
-      <c r="J135" s="2" t="n"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>(858) 753-8027</t>
+        </is>
+      </c>
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="2" t="n"/>
-      <c r="M135" s="2" t="n"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>tyla@bestofcare.com</t>
+        </is>
+      </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
           <t>Tyla DiMaria (Owner and President)</t>
@@ -14482,206 +14906,226 @@
           <t>bestofcareinc.com</t>
         </is>
       </c>
-      <c r="W135" s="2" t="n"/>
+      <c r="W135" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X135" s="3" t="inlineStr">
         <is>
-          <t>1250 Hancock holds Magellan Jets too. [ZoomInfo ID 357382839]</t>
+          <t>1250 Hancock holds Magellan Jets too. [ZoomInfo ID 357382839]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>Housing Management Resources</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>500 Victory Rd Ste 5</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>02171</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>(617) 471-0300</t>
         </is>
       </c>
-      <c r="J136" s="2" t="n"/>
-      <c r="K136" s="2" t="n"/>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="inlineStr">
+      <c r="J136" s="4" t="n"/>
+      <c r="K136" s="4" t="n"/>
+      <c r="L136" s="4" t="n"/>
+      <c r="M136" s="4" t="inlineStr">
+        <is>
+          <t>richard@hmrproperties.com</t>
+        </is>
+      </c>
+      <c r="N136" s="4" t="inlineStr">
         <is>
           <t>Richard Pierce (Founder and President Emeritus)</t>
         </is>
       </c>
-      <c r="O136" s="2" t="inlineStr">
+      <c r="O136" s="4" t="inlineStr">
         <is>
           <t>Affordable housing property management</t>
         </is>
       </c>
-      <c r="P136" s="2" t="inlineStr">
+      <c r="P136" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q136" s="2" t="inlineStr">
+      <c r="Q136" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R136" s="2" t="inlineStr">
+      <c r="R136" s="4" t="inlineStr">
         <is>
           <t>317</t>
         </is>
       </c>
-      <c r="S136" s="2" t="inlineStr">
+      <c r="S136" s="4" t="inlineStr">
         <is>
           <t>331994000</t>
         </is>
       </c>
-      <c r="T136" s="2" t="inlineStr">
+      <c r="T136" s="4" t="inlineStr">
         <is>
           <t>2001</t>
         </is>
       </c>
-      <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="inlineStr">
+      <c r="U136" s="4" t="n"/>
+      <c r="V136" s="4" t="inlineStr">
         <is>
           <t>hmrproperties.com</t>
         </is>
       </c>
-      <c r="W136" s="2" t="n"/>
-      <c r="X136" s="3" t="inlineStr">
-        <is>
-          <t>Same building as Stran. [ZoomInfo ID 57150904]</t>
+      <c r="W136" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X136" s="5" t="inlineStr">
+        <is>
+          <t>Same building as Stran. [ZoomInfo ID 57150904]  |  ZoomInfo: title is now Founder and President Emeritus, so he may have stepped back from day to day. Mobile is Do Not Call. Consider asking for the current operations lead.</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>South Cove Manor</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>288 Washington St</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>02169</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>(617) 237-3618</t>
         </is>
       </c>
-      <c r="J137" s="2" t="n"/>
-      <c r="K137" s="2" t="n"/>
-      <c r="L137" s="2" t="n"/>
-      <c r="M137" s="2" t="n"/>
-      <c r="N137" s="2" t="inlineStr">
+      <c r="J137" s="4" t="n"/>
+      <c r="K137" s="4" t="n"/>
+      <c r="L137" s="4" t="n"/>
+      <c r="M137" s="4" t="inlineStr">
+        <is>
+          <t>bill.graves@southcovemanor.org</t>
+        </is>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
         <is>
           <t>Bill Graves (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O137" s="2" t="inlineStr">
+      <c r="O137" s="4" t="inlineStr">
         <is>
           <t>Skilled nursing and rehab</t>
         </is>
       </c>
-      <c r="P137" s="2" t="inlineStr">
+      <c r="P137" s="4" t="inlineStr">
         <is>
           <t>PHI and EHR uptime on a lean team. Lead with a HIPAA security risk assessment.</t>
         </is>
       </c>
-      <c r="Q137" s="2" t="inlineStr">
+      <c r="Q137" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R137" s="2" t="inlineStr">
+      <c r="R137" s="4" t="inlineStr">
         <is>
           <t>266</t>
         </is>
       </c>
-      <c r="S137" s="2" t="inlineStr">
+      <c r="S137" s="4" t="inlineStr">
         <is>
           <t>15421000</t>
         </is>
       </c>
-      <c r="T137" s="2" t="inlineStr">
+      <c r="T137" s="4" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="inlineStr">
+      <c r="U137" s="4" t="n"/>
+      <c r="V137" s="4" t="inlineStr">
         <is>
           <t>southcovemanor.org</t>
         </is>
       </c>
-      <c r="W137" s="2" t="n"/>
-      <c r="X137" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 35718236]</t>
+      <c r="W137" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X137" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 35718236]  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -14731,7 +15175,11 @@
           <t>(781) 380-1675</t>
         </is>
       </c>
-      <c r="J138" s="2" t="n"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>(781) 312-2554</t>
+        </is>
+      </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
           <t>Corren Collura</t>
@@ -14742,7 +15190,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M138" s="2" t="n"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>ccollura@dellbrookjks.com</t>
+        </is>
+      </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
           <t>Jim Tracey (Co-President)</t>
@@ -14784,210 +15236,230 @@
           <t>dellbrookjks.com</t>
         </is>
       </c>
-      <c r="W138" s="2" t="n"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X138" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 61228486]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 61228486]  |  ZoomInfo: direct line is Do Not Call; mobile (781) 312-2554 is callable.</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>Stran &amp; Company</t>
         </is>
       </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E139" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F139" s="4" t="inlineStr">
         <is>
           <t>500 Victory Rd Ste 301</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H139" s="4" t="inlineStr">
         <is>
           <t>02171</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I139" s="4" t="inlineStr">
         <is>
           <t>(800) 833-3309</t>
         </is>
       </c>
-      <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="J139" s="4" t="n"/>
+      <c r="K139" s="4" t="inlineStr">
         <is>
           <t>Ian Wall</t>
         </is>
       </c>
-      <c r="L139" s="2" t="inlineStr">
+      <c r="L139" s="4" t="inlineStr">
         <is>
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M139" s="2" t="n"/>
-      <c r="N139" s="2" t="n"/>
-      <c r="O139" s="2" t="inlineStr">
+      <c r="M139" s="4" t="inlineStr">
+        <is>
+          <t>iwall@stran.com</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="n"/>
+      <c r="O139" s="4" t="inlineStr">
         <is>
           <t>Promotional products, public company HQ</t>
         </is>
       </c>
-      <c r="P139" s="2" t="inlineStr">
+      <c r="P139" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q139" s="2" t="inlineStr">
+      <c r="Q139" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R139" s="2" t="inlineStr">
+      <c r="R139" s="4" t="inlineStr">
         <is>
           <t>154</t>
         </is>
       </c>
-      <c r="S139" s="2" t="inlineStr">
+      <c r="S139" s="4" t="inlineStr">
         <is>
           <t>118746000</t>
         </is>
       </c>
-      <c r="T139" s="2" t="inlineStr">
+      <c r="T139" s="4" t="inlineStr">
         <is>
           <t>1994</t>
         </is>
       </c>
-      <c r="U139" s="2" t="n"/>
-      <c r="V139" s="2" t="inlineStr">
+      <c r="U139" s="4" t="n"/>
+      <c r="V139" s="4" t="inlineStr">
         <is>
           <t>stran.com</t>
         </is>
       </c>
-      <c r="W139" s="2" t="n"/>
-      <c r="X139" s="3" t="inlineStr">
-        <is>
-          <t>Public company with a named CIO. Marina Bay office. [ZoomInfo ID 48595506]</t>
+      <c r="W139" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X139" s="5" t="inlineStr">
+        <is>
+          <t>Public company with a named CIO. Marina Bay office. [ZoomInfo ID 48595506]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>J. Calnan &amp; Associates</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F140" s="4" t="inlineStr">
         <is>
           <t>3 Batterymarch Park Fl 5</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>02169</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>(617) 801-0200</t>
         </is>
       </c>
-      <c r="J140" s="2" t="n"/>
-      <c r="K140" s="2" t="n"/>
-      <c r="L140" s="2" t="n"/>
-      <c r="M140" s="2" t="n"/>
-      <c r="N140" s="2" t="inlineStr">
+      <c r="J140" s="4" t="n"/>
+      <c r="K140" s="4" t="n"/>
+      <c r="L140" s="4" t="n"/>
+      <c r="M140" s="4" t="inlineStr">
+        <is>
+          <t>jcalnan@jcalnan.com</t>
+        </is>
+      </c>
+      <c r="N140" s="4" t="inlineStr">
         <is>
           <t>Jay Calnan (Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
+      <c r="O140" s="4" t="inlineStr">
         <is>
           <t>Commercial construction manager</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr">
+      <c r="P140" s="4" t="inlineStr">
         <is>
           <t>Contractors are prime wire fraud targets. Lead with email security and estimating uptime.</t>
         </is>
       </c>
-      <c r="Q140" s="2" t="inlineStr">
+      <c r="Q140" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
+      <c r="R140" s="4" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="S140" s="2" t="inlineStr">
+      <c r="S140" s="4" t="inlineStr">
         <is>
           <t>32565000</t>
         </is>
       </c>
-      <c r="T140" s="2" t="inlineStr">
+      <c r="T140" s="4" t="inlineStr">
         <is>
           <t>1996</t>
         </is>
       </c>
-      <c r="U140" s="2" t="n"/>
-      <c r="V140" s="2" t="inlineStr">
+      <c r="U140" s="4" t="n"/>
+      <c r="V140" s="4" t="inlineStr">
         <is>
           <t>jcalnan.com</t>
         </is>
       </c>
-      <c r="W140" s="2" t="n"/>
-      <c r="X140" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 57001788]</t>
+      <c r="W140" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 57001788]  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15509,11 @@
           <t>(617) 507-6589</t>
         </is>
       </c>
-      <c r="J141" s="2" t="n"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>(401) 692-2115</t>
+        </is>
+      </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
           <t>Michael Vinacco</t>
@@ -15048,7 +15524,11 @@
           <t>IT Systems Administrator</t>
         </is>
       </c>
-      <c r="M141" s="2" t="n"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>mikev@magellanjets.com</t>
+        </is>
+      </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
           <t>Anthony Tivnan (President)</t>
@@ -15090,108 +15570,116 @@
           <t>magellanjets.com</t>
         </is>
       </c>
-      <c r="W141" s="2" t="n"/>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X141" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 345603103]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 345603103]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>Environmental Partners Group</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
         <is>
           <t>Quincy</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F142" s="4" t="inlineStr">
         <is>
           <t>1900 Crown Colony Dr Ste 402</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>02169</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>(617) 657-0200</t>
         </is>
       </c>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="n"/>
-      <c r="N142" s="2" t="inlineStr">
+      <c r="J142" s="4" t="n"/>
+      <c r="K142" s="4" t="n"/>
+      <c r="L142" s="4" t="n"/>
+      <c r="M142" s="4" t="n"/>
+      <c r="N142" s="4" t="inlineStr">
         <is>
           <t>Robert W Custard (Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O142" s="2" t="inlineStr">
+      <c r="O142" s="4" t="inlineStr">
         <is>
           <t>Civil and environmental engineering</t>
         </is>
       </c>
-      <c r="P142" s="2" t="inlineStr">
+      <c r="P142" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q142" s="2" t="inlineStr">
+      <c r="Q142" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R142" s="2" t="inlineStr">
+      <c r="R142" s="4" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="S142" s="2" t="inlineStr">
+      <c r="S142" s="4" t="inlineStr">
         <is>
           <t>17076000</t>
         </is>
       </c>
-      <c r="T142" s="2" t="inlineStr">
+      <c r="T142" s="4" t="inlineStr">
         <is>
           <t>1997</t>
         </is>
       </c>
-      <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="inlineStr">
+      <c r="U142" s="4" t="n"/>
+      <c r="V142" s="4" t="inlineStr">
         <is>
           <t>envpartners.com</t>
         </is>
       </c>
-      <c r="W142" s="2" t="n"/>
-      <c r="X142" s="3" t="inlineStr">
-        <is>
-          <t>Crown Colony cluster with MCMC and Arbella. [ZoomInfo ID 36457934]</t>
+      <c r="W142" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X142" s="5" t="inlineStr">
+        <is>
+          <t>Crown Colony cluster with MCMC and Arbella. [ZoomInfo ID 36457934]  |  VERIFY: ZoomInfo returned an email on the wv.gov domain, which is a West Virginia government address and clearly the wrong person. No usable contact data.</t>
         </is>
       </c>
     </row>
@@ -16183,7 +16671,11 @@
           <t>(877) 732-9101</t>
         </is>
       </c>
-      <c r="J152" s="2" t="n"/>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>(508) 503-1895</t>
+        </is>
+      </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
           <t>Jon Pinault</t>
@@ -16194,7 +16686,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M152" s="2" t="n"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>jonathan.pinault@learnwell.com</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
           <t>Kathleen Egger (Chief Executive Officer)</t>
@@ -16236,222 +16732,238 @@
           <t>learnwell.com</t>
         </is>
       </c>
-      <c r="W152" s="2" t="n"/>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X152" s="3" t="inlineStr">
         <is>
-          <t>Downtown Plymouth. Walking distance from 5PT. [ZoomInfo ID 451065368]</t>
+          <t>Downtown Plymouth. Walking distance from 5PT. [ZoomInfo ID 451065368]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>VERC Enterprises</t>
         </is>
       </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
         <is>
           <t>Duxbury</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F153" s="4" t="inlineStr">
         <is>
           <t>10 Washington St</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G153" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H153" s="4" t="inlineStr">
         <is>
           <t>02332</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>(781) 934-5166</t>
         </is>
       </c>
-      <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="inlineStr">
+      <c r="J153" s="4" t="n"/>
+      <c r="K153" s="4" t="inlineStr">
         <is>
           <t>Hossainnuzzaman Shekhon</t>
         </is>
       </c>
-      <c r="L153" s="2" t="inlineStr">
+      <c r="L153" s="4" t="inlineStr">
         <is>
           <t>Management Information Systems Officer</t>
         </is>
       </c>
-      <c r="M153" s="2" t="n"/>
-      <c r="N153" s="2" t="inlineStr">
+      <c r="M153" s="4" t="inlineStr">
+        <is>
+          <t>hosshekhon@vercenterprises.com</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
         <is>
           <t>Louis Gottlieb (President)</t>
         </is>
       </c>
-      <c r="O153" s="2" t="inlineStr">
+      <c r="O153" s="4" t="inlineStr">
         <is>
           <t>Convenience store group, HQ</t>
         </is>
       </c>
-      <c r="P153" s="2" t="inlineStr">
+      <c r="P153" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q153" s="2" t="inlineStr">
+      <c r="Q153" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R153" s="2" t="inlineStr">
+      <c r="R153" s="4" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="S153" s="2" t="inlineStr">
+      <c r="S153" s="4" t="inlineStr">
         <is>
           <t>29010000</t>
         </is>
       </c>
-      <c r="T153" s="2" t="inlineStr">
+      <c r="T153" s="4" t="inlineStr">
         <is>
           <t>1977</t>
         </is>
       </c>
-      <c r="U153" s="2" t="n"/>
-      <c r="V153" s="2" t="inlineStr">
+      <c r="U153" s="4" t="n"/>
+      <c r="V153" s="4" t="inlineStr">
         <is>
           <t>vercenterprises.com</t>
         </is>
       </c>
-      <c r="W153" s="2" t="n"/>
-      <c r="X153" s="3" t="inlineStr">
-        <is>
-          <t>President and MIS officer on file. [ZoomInfo ID 119881895]</t>
+      <c r="W153" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X153" s="5" t="inlineStr">
+        <is>
+          <t>President and MIS officer on file. [ZoomInfo ID 119881895]  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>Keville Enterprises</t>
         </is>
       </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E154" s="4" t="inlineStr">
         <is>
           <t>Marshfield</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>475 School St Ste 11</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H154" s="4" t="inlineStr">
         <is>
           <t>02050</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>(781) 837-3884</t>
         </is>
       </c>
-      <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="J154" s="4" t="n"/>
+      <c r="K154" s="4" t="inlineStr">
         <is>
           <t>Matthew Wilson</t>
         </is>
       </c>
-      <c r="L154" s="2" t="inlineStr">
+      <c r="L154" s="4" t="inlineStr">
         <is>
           <t>Systems Consultant</t>
         </is>
       </c>
-      <c r="M154" s="2" t="n"/>
-      <c r="N154" s="2" t="inlineStr">
+      <c r="M154" s="4" t="n"/>
+      <c r="N154" s="4" t="inlineStr">
         <is>
           <t>Christine Keville (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O154" s="2" t="inlineStr">
+      <c r="O154" s="4" t="inlineStr">
         <is>
           <t>Construction management and inspection</t>
         </is>
       </c>
-      <c r="P154" s="2" t="inlineStr">
+      <c r="P154" s="4" t="inlineStr">
         <is>
           <t>Contractors are prime wire fraud targets. Lead with email security and estimating uptime.</t>
         </is>
       </c>
-      <c r="Q154" s="2" t="inlineStr">
+      <c r="Q154" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R154" s="2" t="inlineStr">
+      <c r="R154" s="4" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="S154" s="2" t="inlineStr">
+      <c r="S154" s="4" t="inlineStr">
         <is>
           <t>76326000</t>
         </is>
       </c>
-      <c r="T154" s="2" t="inlineStr">
+      <c r="T154" s="4" t="inlineStr">
         <is>
           <t>1991</t>
         </is>
       </c>
-      <c r="U154" s="2" t="n"/>
-      <c r="V154" s="2" t="inlineStr">
+      <c r="U154" s="4" t="n"/>
+      <c r="V154" s="4" t="inlineStr">
         <is>
           <t>keville.com</t>
         </is>
       </c>
-      <c r="W154" s="2" t="n"/>
-      <c r="X154" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 21381606]</t>
+      <c r="W154" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X154" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 21381606]  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -16501,7 +17013,11 @@
           <t>(781) 834-1300</t>
         </is>
       </c>
-      <c r="J155" s="2" t="n"/>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>(781) 536-3223</t>
+        </is>
+      </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
           <t>Jing Wan</t>
@@ -16512,7 +17028,11 @@
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M155" s="2" t="n"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>jingwan@roadtoresponsibility.org</t>
+        </is>
+      </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
           <t>Christopher White (President &amp; Chief Executive Officer)</t>
@@ -16554,10 +17074,14 @@
           <t>roadtoresponsibility.org</t>
         </is>
       </c>
-      <c r="W155" s="2" t="n"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X155" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 32686648]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 32686648]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -16701,10 +17225,18 @@
           <t>(781) 740-2440</t>
         </is>
       </c>
-      <c r="J157" s="2" t="n"/>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>(647) 928-4223</t>
+        </is>
+      </c>
       <c r="K157" s="2" t="n"/>
       <c r="L157" s="2" t="n"/>
-      <c r="M157" s="2" t="n"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>sherry@unitedelevatorltd.com</t>
+        </is>
+      </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
           <t>Sherry Haskell (President)</t>
@@ -16746,10 +17278,14 @@
           <t>unitedelevatorcorp.com</t>
         </is>
       </c>
-      <c r="W157" s="2" t="n"/>
+      <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X157" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 58998985]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 58998985]  |  VERIFY: numbers returned are Ontario, Canada (905/647). This may be a different United Elevator. Confirm before calling.</t>
         </is>
       </c>
     </row>
@@ -16799,10 +17335,18 @@
           <t>(508) 830-3440</t>
         </is>
       </c>
-      <c r="J158" s="2" t="n"/>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>(508) 556-7952</t>
+        </is>
+      </c>
       <c r="K158" s="2" t="n"/>
       <c r="L158" s="2" t="n"/>
-      <c r="M158" s="2" t="n"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>choyt@coolgearinc.com</t>
+        </is>
+      </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
           <t>Chris Hoyt (Senior Vice President - General Manager)</t>
@@ -16844,8 +17388,16 @@
           <t>coolgearinc.com</t>
         </is>
       </c>
-      <c r="W158" s="2" t="n"/>
-      <c r="X158" s="3" t="n"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
+      <c r="X158" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -16893,7 +17445,11 @@
           <t>(781) 319-1000</t>
         </is>
       </c>
-      <c r="J159" s="2" t="n"/>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>(781) 319-1147</t>
+        </is>
+      </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
           <t>Ed Monahan</t>
@@ -16904,7 +17460,11 @@
           <t>Infrastructure Manager</t>
         </is>
       </c>
-      <c r="M159" s="2" t="n"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>ed.monahan@induscom.com</t>
+        </is>
+      </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
           <t>Frank Dirico (President)</t>
@@ -16946,10 +17506,14 @@
           <t>induscom.com</t>
         </is>
       </c>
-      <c r="W159" s="2" t="n"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X159" s="3" t="inlineStr">
         <is>
-          <t>Tech adjacent, referral partner potential too. [ZoomInfo ID 58461035]</t>
+          <t>Tech adjacent, referral partner potential too. [ZoomInfo ID 58461035]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18671,11 @@
           <t>(508) 588-3300</t>
         </is>
       </c>
-      <c r="J170" s="2" t="n"/>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>(617) 353-4153</t>
+        </is>
+      </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
           <t>George Wyner</t>
@@ -18156,116 +18724,128 @@
           <t>shawmutcorporation.com</t>
         </is>
       </c>
-      <c r="W170" s="2" t="n"/>
+      <c r="W170" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X170" s="3" t="inlineStr">
         <is>
-          <t>CIO George Wyner on file. Century old family firm. [ZoomInfo ID 45891624]</t>
+          <t>CIO George Wyner on file. Century old family firm. [ZoomInfo ID 45891624]  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
         <is>
           <t>Jones &amp; Vining</t>
         </is>
       </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="D171" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E171" s="4" t="inlineStr">
         <is>
           <t>Brockton</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F171" s="4" t="inlineStr">
         <is>
           <t>1115 W Chestnut St Ste 9</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H171" s="4" t="inlineStr">
         <is>
           <t>02301</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="I171" s="4" t="inlineStr">
         <is>
           <t>(508) 232-7470</t>
         </is>
       </c>
-      <c r="J171" s="2" t="n"/>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="J171" s="4" t="n"/>
+      <c r="K171" s="4" t="inlineStr">
         <is>
           <t>Jason Savery</t>
         </is>
       </c>
-      <c r="L171" s="2" t="inlineStr">
+      <c r="L171" s="4" t="inlineStr">
         <is>
           <t>Global Director, Information Technology</t>
         </is>
       </c>
-      <c r="M171" s="2" t="n"/>
-      <c r="N171" s="2" t="inlineStr">
+      <c r="M171" s="4" t="inlineStr">
+        <is>
+          <t>jsavery@jonesandvining.com</t>
+        </is>
+      </c>
+      <c r="N171" s="4" t="inlineStr">
         <is>
           <t>James Salzano (President &amp; Chief Executive Officer)</t>
         </is>
       </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="O171" s="4" t="inlineStr">
         <is>
           <t>Footwear components manufacturer</t>
         </is>
       </c>
-      <c r="P171" s="2" t="inlineStr">
+      <c r="P171" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q171" s="2" t="inlineStr">
+      <c r="Q171" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R171" s="2" t="inlineStr">
+      <c r="R171" s="4" t="inlineStr">
         <is>
           <t>437</t>
         </is>
       </c>
-      <c r="S171" s="2" t="inlineStr">
+      <c r="S171" s="4" t="inlineStr">
         <is>
           <t>63716000</t>
         </is>
       </c>
-      <c r="T171" s="2" t="inlineStr">
+      <c r="T171" s="4" t="inlineStr">
         <is>
           <t>1930</t>
         </is>
       </c>
-      <c r="U171" s="2" t="n"/>
-      <c r="V171" s="2" t="inlineStr">
+      <c r="U171" s="4" t="n"/>
+      <c r="V171" s="4" t="inlineStr">
         <is>
           <t>jonesandvining.com</t>
         </is>
       </c>
-      <c r="W171" s="2" t="n"/>
-      <c r="X171" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 63801356]</t>
+      <c r="W171" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 63801356]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -18315,7 +18895,11 @@
           <t>(508) 559-6699</t>
         </is>
       </c>
-      <c r="J172" s="2" t="n"/>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>(508) 894-3511</t>
+        </is>
+      </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
           <t>David Anderson</t>
@@ -18326,7 +18910,11 @@
           <t>Chief Information Officer</t>
         </is>
       </c>
-      <c r="M172" s="2" t="n"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>andersond@bnhc.org</t>
+        </is>
+      </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
           <t>Maria Celli (Chief Executive Officer)</t>
@@ -18368,10 +18956,14 @@
           <t>bnhc.org</t>
         </is>
       </c>
-      <c r="W172" s="2" t="n"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X172" s="3" t="inlineStr">
         <is>
-          <t>HIPAA and grants. Sysadmin on file. [ZoomInfo ID 16994242]</t>
+          <t>HIPAA and grants. Sysadmin on file. [ZoomInfo ID 16994242]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -18507,10 +19099,18 @@
           <t>(508) 927-7800</t>
         </is>
       </c>
-      <c r="J174" s="2" t="n"/>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>(508) 927-7819</t>
+        </is>
+      </c>
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="2" t="n"/>
-      <c r="M174" s="2" t="n"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>jward@cheerpack.com</t>
+        </is>
+      </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
           <t>Jeffrey Ward (Chief Executive Officer)</t>
@@ -18552,116 +19152,128 @@
           <t>cheerpack.com</t>
         </is>
       </c>
-      <c r="W174" s="2" t="n"/>
+      <c r="W174" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X174" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 355741114]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 355741114]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
         <is>
           <t>Burke Distributing</t>
         </is>
       </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="D175" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E175" s="4" t="inlineStr">
         <is>
           <t>Randolph</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F175" s="4" t="inlineStr">
         <is>
           <t>89 Teed Dr</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H175" s="4" t="inlineStr">
         <is>
           <t>02368</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="I175" s="4" t="inlineStr">
         <is>
           <t>(781) 986-6300</t>
         </is>
       </c>
-      <c r="J175" s="2" t="n"/>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="J175" s="4" t="n"/>
+      <c r="K175" s="4" t="inlineStr">
         <is>
           <t>Jeff Ryan</t>
         </is>
       </c>
-      <c r="L175" s="2" t="inlineStr">
+      <c r="L175" s="4" t="inlineStr">
         <is>
           <t>Director, Information Technology &amp; Analytics</t>
         </is>
       </c>
-      <c r="M175" s="2" t="n"/>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="M175" s="4" t="inlineStr">
+        <is>
+          <t>jryan@burkedist.com</t>
+        </is>
+      </c>
+      <c r="N175" s="4" t="inlineStr">
         <is>
           <t>William Burke (President)</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O175" s="4" t="inlineStr">
         <is>
           <t>Beer distributor</t>
         </is>
       </c>
-      <c r="P175" s="2" t="inlineStr">
+      <c r="P175" s="4" t="inlineStr">
         <is>
           <t>Branch and warehouse ops on one ERP. Lead with uptime and ransomware defense.</t>
         </is>
       </c>
-      <c r="Q175" s="2" t="inlineStr">
+      <c r="Q175" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R175" s="2" t="inlineStr">
+      <c r="R175" s="4" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="S175" s="2" t="inlineStr">
+      <c r="S175" s="4" t="inlineStr">
         <is>
           <t>133192000</t>
         </is>
       </c>
-      <c r="T175" s="2" t="inlineStr">
+      <c r="T175" s="4" t="inlineStr">
         <is>
           <t>1935</t>
         </is>
       </c>
-      <c r="U175" s="2" t="n"/>
-      <c r="V175" s="2" t="inlineStr">
+      <c r="U175" s="4" t="n"/>
+      <c r="V175" s="4" t="inlineStr">
         <is>
           <t>burkedist.com</t>
         </is>
       </c>
-      <c r="W175" s="2" t="n"/>
-      <c r="X175" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 353985141]</t>
+      <c r="W175" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X175" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 353985141]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -18711,10 +19323,18 @@
           <t>(508) 588-4400</t>
         </is>
       </c>
-      <c r="J176" s="2" t="n"/>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>(412) 805-5868</t>
+        </is>
+      </c>
       <c r="K176" s="2" t="n"/>
       <c r="L176" s="2" t="n"/>
-      <c r="M176" s="2" t="n"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>emily.r@cervos.com</t>
+        </is>
+      </c>
       <c r="N176" s="2" t="inlineStr">
         <is>
           <t>Emily Rager (Chief Commercial Officer)</t>
@@ -18752,10 +19372,14 @@
           <t>cervos.com</t>
         </is>
       </c>
-      <c r="W176" s="2" t="n"/>
+      <c r="W176" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X176" s="3" t="inlineStr">
         <is>
-          <t>Avon Industrial Park. [ZoomInfo ID 556202114]</t>
+          <t>Avon Industrial Park. [ZoomInfo ID 556202114]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -18805,10 +19429,18 @@
           <t>(508) 588-3240</t>
         </is>
       </c>
-      <c r="J177" s="2" t="n"/>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>(508) 682-8529</t>
+        </is>
+      </c>
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="2" t="n"/>
-      <c r="M177" s="2" t="n"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>bklaila@gtrmfg.com</t>
+        </is>
+      </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
           <t>William Klaila (Owner)</t>
@@ -18850,10 +19482,14 @@
           <t>gtrmfg.com</t>
         </is>
       </c>
-      <c r="W177" s="2" t="n"/>
+      <c r="W177" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X177" s="3" t="inlineStr">
         <is>
-          <t>Ask about defense work and CMMC. [ZoomInfo ID 343685898]</t>
+          <t>Ask about defense work and CMMC. [ZoomInfo ID 343685898]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -18903,10 +19539,18 @@
           <t>(781) 963-6440</t>
         </is>
       </c>
-      <c r="J178" s="2" t="n"/>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>(781) 473-2323</t>
+        </is>
+      </c>
       <c r="K178" s="2" t="n"/>
       <c r="L178" s="2" t="n"/>
-      <c r="M178" s="2" t="n"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>marke@frounds.com</t>
+        </is>
+      </c>
       <c r="N178" s="2" t="inlineStr">
         <is>
           <t>Mark Ehrenzeller (President)</t>
@@ -18948,10 +19592,14 @@
           <t>frankirounds.com</t>
         </is>
       </c>
-      <c r="W178" s="2" t="n"/>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 45993486]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 45993486]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19833,11 @@
           <t>(508) 588-7007</t>
         </is>
       </c>
-      <c r="J181" s="2" t="n"/>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>(508) 728-4890</t>
+        </is>
+      </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
           <t>Matthew Acord</t>
@@ -19196,7 +19848,11 @@
           <t>Manager, Information Technology</t>
         </is>
       </c>
-      <c r="M181" s="2" t="n"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>matthewacord@rubywines.com</t>
+        </is>
+      </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
           <t>Robert Rubin (President &amp; Chief Executive Officer)</t>
@@ -19238,10 +19894,14 @@
           <t>rubywines.com</t>
         </is>
       </c>
-      <c r="W181" s="2" t="n"/>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X181" s="3" t="inlineStr">
         <is>
-          <t>Family owned since 1933. CEO on file. [ZoomInfo ID 33375094]</t>
+          <t>Family owned since 1933. CEO on file. [ZoomInfo ID 33375094]  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -19291,7 +19951,11 @@
           <t>(508) 583-8300</t>
         </is>
       </c>
-      <c r="J182" s="2" t="n"/>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>(310) 800-6935</t>
+        </is>
+      </c>
       <c r="K182" s="2" t="n"/>
       <c r="L182" s="2" t="n"/>
       <c r="M182" s="2" t="n"/>
@@ -19336,10 +20000,14 @@
           <t>weiss-sheetmetal.com</t>
         </is>
       </c>
-      <c r="W182" s="2" t="n"/>
+      <c r="W182" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X182" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 343453890]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 343453890]  |  ZoomInfo confirmed mobile, callable (out-of-state area code on file). No email.</t>
         </is>
       </c>
     </row>
@@ -19389,10 +20057,18 @@
           <t>(508) 238-6985</t>
         </is>
       </c>
-      <c r="J183" s="2" t="n"/>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>(508) 238-6985 ext. 224</t>
+        </is>
+      </c>
       <c r="K183" s="2" t="n"/>
       <c r="L183" s="2" t="n"/>
-      <c r="M183" s="2" t="n"/>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>wmcpherson@centralceilings.com</t>
+        </is>
+      </c>
       <c r="N183" s="2" t="inlineStr">
         <is>
           <t>William McPherson (President)</t>
@@ -19434,10 +20110,14 @@
           <t>centralceilings.com</t>
         </is>
       </c>
-      <c r="W183" s="2" t="n"/>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X183" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 7275226]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 7275226]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -19487,7 +20167,11 @@
           <t>(508) 587-5401</t>
         </is>
       </c>
-      <c r="J184" s="2" t="n"/>
+      <c r="J184" s="2" t="inlineStr">
+        <is>
+          <t>(508) 587-5400 ext. 228</t>
+        </is>
+      </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
           <t>Wayne McKinnon</t>
@@ -19498,7 +20182,11 @@
           <t>Desktop Support Technician</t>
         </is>
       </c>
-      <c r="M184" s="2" t="n"/>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>wmckinnon@aqualeisure.com</t>
+        </is>
+      </c>
       <c r="N184" s="2" t="inlineStr">
         <is>
           <t>Barry Fireman (President)</t>
@@ -19540,116 +20228,128 @@
           <t>aqualeisure.com</t>
         </is>
       </c>
-      <c r="W184" s="2" t="n"/>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X184" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 6359706]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 6359706]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>Equal Exchange</t>
         </is>
       </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>K1</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E185" s="4" t="inlineStr">
         <is>
           <t>West Bridgewater</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F185" s="4" t="inlineStr">
         <is>
           <t>50 United Dr</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H185" s="4" t="inlineStr">
         <is>
           <t>02379</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="I185" s="4" t="inlineStr">
         <is>
           <t>(774) 776-7366</t>
         </is>
       </c>
-      <c r="J185" s="2" t="n"/>
-      <c r="K185" s="2" t="inlineStr">
+      <c r="J185" s="4" t="n"/>
+      <c r="K185" s="4" t="inlineStr">
         <is>
           <t>Wayne Kritzman</t>
         </is>
       </c>
-      <c r="L185" s="2" t="inlineStr">
+      <c r="L185" s="4" t="inlineStr">
         <is>
           <t>Computer Help Desk</t>
         </is>
       </c>
-      <c r="M185" s="2" t="n"/>
-      <c r="N185" s="2" t="inlineStr">
+      <c r="M185" s="4" t="inlineStr">
+        <is>
+          <t>wayne.kritzman@equalexchange.com</t>
+        </is>
+      </c>
+      <c r="N185" s="4" t="inlineStr">
         <is>
           <t>Nicole Vitello (President)</t>
         </is>
       </c>
-      <c r="O185" s="2" t="inlineStr">
+      <c r="O185" s="4" t="inlineStr">
         <is>
           <t>Fair trade coffee co-op, HQ</t>
         </is>
       </c>
-      <c r="P185" s="2" t="inlineStr">
+      <c r="P185" s="4" t="inlineStr">
         <is>
           <t>Real office and operations inside the drive zone. Lead with dependable IT and security basics.</t>
         </is>
       </c>
-      <c r="Q185" s="2" t="inlineStr">
+      <c r="Q185" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R185" s="2" t="inlineStr">
+      <c r="R185" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S185" s="2" t="inlineStr">
+      <c r="S185" s="4" t="inlineStr">
         <is>
           <t>42187000</t>
         </is>
       </c>
-      <c r="T185" s="2" t="inlineStr">
+      <c r="T185" s="4" t="inlineStr">
         <is>
           <t>1986</t>
         </is>
       </c>
-      <c r="U185" s="2" t="n"/>
-      <c r="V185" s="2" t="inlineStr">
+      <c r="U185" s="4" t="n"/>
+      <c r="V185" s="4" t="inlineStr">
         <is>
           <t>equalexchange.coop</t>
         </is>
       </c>
-      <c r="W185" s="2" t="n"/>
-      <c r="X185" s="3" t="inlineStr">
-        <is>
-          <t>Mission driven brand. Same street as Cheer Pack. [ZoomInfo ID 33361784]</t>
+      <c r="W185" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X185" s="5" t="inlineStr">
+        <is>
+          <t>Mission driven brand. Same street as Cheer Pack. [ZoomInfo ID 33361784]  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -20254,100 +20954,108 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>BETA Group</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="E192" s="2" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>Norwood</t>
         </is>
       </c>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>315 Norwood Park S, Fl 2</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="H192" s="4" t="inlineStr">
         <is>
           <t>02062</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="I192" s="4" t="inlineStr">
         <is>
           <t>(781) 255-1982</t>
         </is>
       </c>
-      <c r="J192" s="2" t="n"/>
-      <c r="K192" s="2" t="inlineStr">
+      <c r="J192" s="4" t="n"/>
+      <c r="K192" s="4" t="inlineStr">
         <is>
           <t>Greg Snow</t>
         </is>
       </c>
-      <c r="L192" s="2" t="inlineStr">
+      <c r="L192" s="4" t="inlineStr">
         <is>
           <t>IT Director, sits in Lincoln RI office</t>
         </is>
       </c>
-      <c r="M192" s="2" t="n"/>
-      <c r="N192" s="2" t="inlineStr">
+      <c r="M192" s="4" t="inlineStr">
+        <is>
+          <t>gsnow@beta-inc.com</t>
+        </is>
+      </c>
+      <c r="N192" s="4" t="inlineStr">
         <is>
           <t>Mark Gershman (President &amp; CEO)</t>
         </is>
       </c>
-      <c r="O192" s="2" t="inlineStr">
+      <c r="O192" s="4" t="inlineStr">
         <is>
           <t>Civil engineering firm</t>
         </is>
       </c>
-      <c r="P192" s="2" t="inlineStr">
+      <c r="P192" s="4" t="inlineStr">
         <is>
           <t>Multi office engineering firm. Lead with CAD performance, backup and office to office access.</t>
         </is>
       </c>
-      <c r="Q192" s="2" t="inlineStr">
+      <c r="Q192" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R192" s="2" t="inlineStr">
+      <c r="R192" s="4" t="inlineStr">
         <is>
           <t>173</t>
         </is>
       </c>
-      <c r="S192" s="2" t="n"/>
-      <c r="T192" s="2" t="n"/>
-      <c r="U192" s="2" t="n"/>
-      <c r="V192" s="2" t="inlineStr">
+      <c r="S192" s="4" t="n"/>
+      <c r="T192" s="4" t="n"/>
+      <c r="U192" s="4" t="n"/>
+      <c r="V192" s="4" t="inlineStr">
         <is>
           <t>beta-inc.com</t>
         </is>
       </c>
-      <c r="W192" s="2" t="n"/>
-      <c r="X192" s="3" t="inlineStr">
-        <is>
-          <t>From postcard list. Emails on file: mgershman@beta-inc.com, gsnow@beta-inc.com.</t>
+      <c r="W192" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X192" s="5" t="inlineStr">
+        <is>
+          <t>From postcard list. Emails on file: mgershman@beta-inc.com, gsnow@beta-inc.com.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -21461,7 +22169,11 @@
           <t>(800) 762-1552</t>
         </is>
       </c>
-      <c r="J203" s="2" t="n"/>
+      <c r="J203" s="2" t="inlineStr">
+        <is>
+          <t>(774) 268-0783</t>
+        </is>
+      </c>
       <c r="K203" s="2" t="inlineStr">
         <is>
           <t>Octavio Bizarro</t>
@@ -21514,10 +22226,14 @@
           <t>newenglandicecream.com</t>
         </is>
       </c>
-      <c r="W203" s="2" t="n"/>
+      <c r="W203" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X203" s="3" t="inlineStr">
         <is>
-          <t>Big distribution ops, lean office IT. [ZoomInfo ID 85230209]</t>
+          <t>Big distribution ops, lean office IT. [ZoomInfo ID 85230209]  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -21755,10 +22471,18 @@
           <t>(978) 674-8464</t>
         </is>
       </c>
-      <c r="J206" s="2" t="n"/>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>(978) 674-7231</t>
+        </is>
+      </c>
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="2" t="n"/>
-      <c r="M206" s="2" t="n"/>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>dlanci@nexdine.com</t>
+        </is>
+      </c>
       <c r="N206" s="2" t="inlineStr">
         <is>
           <t>David Lanci (Co-Founder &amp; Chief Executive Officer)</t>
@@ -21800,10 +22524,14 @@
           <t>nexdine.com</t>
         </is>
       </c>
-      <c r="W206" s="2" t="n"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X206" s="3" t="inlineStr">
         <is>
-          <t>Many client sites, one HQ office. [ZoomInfo ID 347367421]</t>
+          <t>Many client sites, one HQ office. [ZoomInfo ID 347367421]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -21853,10 +22581,18 @@
           <t>(800) 777-4752</t>
         </is>
       </c>
-      <c r="J207" s="2" t="n"/>
+      <c r="J207" s="2" t="inlineStr">
+        <is>
+          <t>(508) 660-1176</t>
+        </is>
+      </c>
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="2" t="n"/>
-      <c r="M207" s="2" t="n"/>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>mherbert@islandoasis.com</t>
+        </is>
+      </c>
       <c r="N207" s="2" t="inlineStr">
         <is>
           <t>Michael Herbert (President)</t>
@@ -21902,10 +22638,14 @@
           <t>islandoasis.com</t>
         </is>
       </c>
-      <c r="W207" s="2" t="n"/>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X207" s="3" t="inlineStr">
         <is>
-          <t>Kerry owned plant, local ops team. [ZoomInfo ID 56035430]</t>
+          <t>Kerry owned plant, local ops team. [ZoomInfo ID 56035430]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -21955,7 +22695,11 @@
           <t>(508) 337-2727</t>
         </is>
       </c>
-      <c r="J208" s="2" t="n"/>
+      <c r="J208" s="2" t="inlineStr">
+        <is>
+          <t>(508) 337-2700</t>
+        </is>
+      </c>
       <c r="K208" s="2" t="inlineStr">
         <is>
           <t>Ed Murphy</t>
@@ -21966,7 +22710,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M208" s="2" t="n"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>ed.murphy@belknapwhite.com</t>
+        </is>
+      </c>
       <c r="N208" s="2" t="n"/>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -22004,10 +22752,14 @@
           <t>belknapwhite.com</t>
         </is>
       </c>
-      <c r="W208" s="2" t="n"/>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X208" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [ZoomInfo ID 13539125]</t>
+          <t xml:space="preserve"> [ZoomInfo ID 13539125]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -22057,7 +22809,11 @@
           <t>(781) 793-5300</t>
         </is>
       </c>
-      <c r="J209" s="2" t="n"/>
+      <c r="J209" s="2" t="inlineStr">
+        <is>
+          <t>(781) 793-5346</t>
+        </is>
+      </c>
       <c r="K209" s="2" t="inlineStr">
         <is>
           <t>Renato Paiva</t>
@@ -22068,7 +22824,11 @@
           <t>Director, Information Technology</t>
         </is>
       </c>
-      <c r="M209" s="2" t="n"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>rpaiva@charlesriverapparel.com</t>
+        </is>
+      </c>
       <c r="N209" s="2" t="inlineStr">
         <is>
           <t>Jason Lipsett (President &amp; Chief Executive Officer)</t>
@@ -22110,108 +22870,120 @@
           <t>charlesriverapparel.com</t>
         </is>
       </c>
-      <c r="W209" s="2" t="n"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X209" s="3" t="inlineStr">
         <is>
-          <t>Same highway as Senior Metal Bellows. [ZoomInfo ID 7635805]</t>
+          <t>Same highway as Senior Metal Bellows. [ZoomInfo ID 7635805]  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="A210" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B210" s="2" t="inlineStr">
+      <c r="B210" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="4" t="inlineStr">
         <is>
           <t>Accutech Packaging</t>
         </is>
       </c>
-      <c r="D210" s="2" t="inlineStr">
+      <c r="D210" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="E210" s="4" t="inlineStr">
         <is>
           <t>Foxborough</t>
         </is>
       </c>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="F210" s="4" t="inlineStr">
         <is>
           <t>157 Green St</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="H210" s="4" t="inlineStr">
         <is>
           <t>02035</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="I210" s="4" t="inlineStr">
         <is>
           <t>(508) 543-3800</t>
         </is>
       </c>
-      <c r="J210" s="2" t="n"/>
-      <c r="K210" s="2" t="n"/>
-      <c r="L210" s="2" t="n"/>
-      <c r="M210" s="2" t="n"/>
-      <c r="N210" s="2" t="inlineStr">
+      <c r="J210" s="4" t="n"/>
+      <c r="K210" s="4" t="n"/>
+      <c r="L210" s="4" t="n"/>
+      <c r="M210" s="4" t="inlineStr">
+        <is>
+          <t>rmadigan@accutechpkg.com</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="inlineStr">
         <is>
           <t>Richard Madigan (Owner)</t>
         </is>
       </c>
-      <c r="O210" s="2" t="inlineStr">
+      <c r="O210" s="4" t="inlineStr">
         <is>
           <t>Packaging manufacturer</t>
         </is>
       </c>
-      <c r="P210" s="2" t="inlineStr">
+      <c r="P210" s="4" t="inlineStr">
         <is>
           <t>Production uptime and ransomware risk with a small office team. Lead with co-managed IT.</t>
         </is>
       </c>
-      <c r="Q210" s="2" t="inlineStr">
+      <c r="Q210" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R210" s="2" t="inlineStr">
+      <c r="R210" s="4" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="S210" s="2" t="inlineStr">
+      <c r="S210" s="4" t="inlineStr">
         <is>
           <t>28998000</t>
         </is>
       </c>
-      <c r="T210" s="2" t="inlineStr">
+      <c r="T210" s="4" t="inlineStr">
         <is>
           <t>1986</t>
         </is>
       </c>
-      <c r="U210" s="2" t="n"/>
-      <c r="V210" s="2" t="inlineStr">
+      <c r="U210" s="4" t="n"/>
+      <c r="V210" s="4" t="inlineStr">
         <is>
           <t>accutechpkg.com</t>
         </is>
       </c>
-      <c r="W210" s="2" t="n"/>
-      <c r="X210" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 840895]</t>
+      <c r="W210" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X210" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 840895]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -22355,10 +23127,18 @@
           <t>(774) 225-6300</t>
         </is>
       </c>
-      <c r="J212" s="2" t="n"/>
+      <c r="J212" s="2" t="inlineStr">
+        <is>
+          <t>(774) 225-6327</t>
+        </is>
+      </c>
       <c r="K212" s="2" t="n"/>
       <c r="L212" s="2" t="n"/>
-      <c r="M212" s="2" t="n"/>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>pmarceau@southshoremillwork.com</t>
+        </is>
+      </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
           <t>Peter Marceau (General Manager)</t>
@@ -22400,108 +23180,120 @@
           <t>southshoremillwork.com</t>
         </is>
       </c>
-      <c r="W212" s="2" t="n"/>
+      <c r="W212" s="2" t="inlineStr">
+        <is>
+          <t>Verified callable</t>
+        </is>
+      </c>
       <c r="X212" s="3" t="inlineStr">
         <is>
-          <t>GM Peter Marceau on file. [ZoomInfo ID 109167378]</t>
+          <t>GM Peter Marceau on file. [ZoomInfo ID 109167378]  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="A213" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B213" s="2" t="inlineStr">
+      <c r="B213" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C213" s="4" t="inlineStr">
         <is>
           <t>Chex Finer Foods</t>
         </is>
       </c>
-      <c r="D213" s="2" t="inlineStr">
+      <c r="D213" s="4" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="E213" s="2" t="inlineStr">
+      <c r="E213" s="4" t="inlineStr">
         <is>
           <t>Mansfield</t>
         </is>
       </c>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="F213" s="4" t="inlineStr">
         <is>
           <t>71 Hampden Rd Ste 100</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="H213" s="4" t="inlineStr">
         <is>
           <t>02048</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="I213" s="4" t="inlineStr">
         <is>
           <t>(508) 226-0660</t>
         </is>
       </c>
-      <c r="J213" s="2" t="n"/>
-      <c r="K213" s="2" t="n"/>
-      <c r="L213" s="2" t="n"/>
-      <c r="M213" s="2" t="n"/>
-      <c r="N213" s="2" t="inlineStr">
+      <c r="J213" s="4" t="n"/>
+      <c r="K213" s="4" t="n"/>
+      <c r="L213" s="4" t="n"/>
+      <c r="M213" s="4" t="inlineStr">
+        <is>
+          <t>dcisenberg@chexfoods.com</t>
+        </is>
+      </c>
+      <c r="N213" s="4" t="inlineStr">
         <is>
           <t>David Isenberg (Founder)</t>
         </is>
       </c>
-      <c r="O213" s="2" t="inlineStr">
+      <c r="O213" s="4" t="inlineStr">
         <is>
           <t>Specialty food distributor</t>
         </is>
       </c>
-      <c r="P213" s="2" t="inlineStr">
+      <c r="P213" s="4" t="inlineStr">
         <is>
           <t>Branch and warehouse ops on one ERP. Lead with uptime and ransomware defense.</t>
         </is>
       </c>
-      <c r="Q213" s="2" t="inlineStr">
+      <c r="Q213" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R213" s="2" t="inlineStr">
+      <c r="R213" s="4" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S213" s="2" t="inlineStr">
+      <c r="S213" s="4" t="inlineStr">
         <is>
           <t>21112000</t>
         </is>
       </c>
-      <c r="T213" s="2" t="inlineStr">
+      <c r="T213" s="4" t="inlineStr">
         <is>
           <t>1965</t>
         </is>
       </c>
-      <c r="U213" s="2" t="n"/>
-      <c r="V213" s="2" t="inlineStr">
+      <c r="U213" s="4" t="n"/>
+      <c r="V213" s="4" t="inlineStr">
         <is>
           <t>chexfoods.com</t>
         </is>
       </c>
-      <c r="W213" s="2" t="n"/>
-      <c r="X213" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> [ZoomInfo ID 15272254]</t>
+      <c r="W213" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X213" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [ZoomInfo ID 15272254]  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -22902,108 +23694,112 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>Cold Target</t>
         </is>
       </c>
-      <c r="B218" s="2" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C218" s="2" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>Bay State Physical Therapy</t>
         </is>
       </c>
-      <c r="D218" s="2" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>X1</t>
         </is>
       </c>
-      <c r="E218" s="2" t="inlineStr">
+      <c r="E218" s="4" t="inlineStr">
         <is>
           <t>Braintree</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F218" s="4" t="inlineStr">
         <is>
           <t>703 Granite St, Ste 300</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="H218" s="4" t="inlineStr">
         <is>
           <t>02184</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="I218" s="4" t="inlineStr">
         <is>
           <t>(781) 878-5550</t>
         </is>
       </c>
-      <c r="J218" s="2" t="n"/>
-      <c r="K218" s="2" t="inlineStr">
+      <c r="J218" s="4" t="n"/>
+      <c r="K218" s="4" t="inlineStr">
         <is>
           <t>Jon Dibiasio</t>
         </is>
       </c>
-      <c r="L218" s="2" t="inlineStr">
+      <c r="L218" s="4" t="inlineStr">
         <is>
           <t>Vice President, Information Technology</t>
         </is>
       </c>
-      <c r="M218" s="2" t="n"/>
-      <c r="N218" s="2" t="inlineStr">
+      <c r="M218" s="4" t="n"/>
+      <c r="N218" s="4" t="inlineStr">
         <is>
           <t>Vladimir Shursky (Owner)</t>
         </is>
       </c>
-      <c r="O218" s="2" t="inlineStr">
+      <c r="O218" s="4" t="inlineStr">
         <is>
           <t>Physical therapy group, 60+ clinics, HQ</t>
         </is>
       </c>
-      <c r="P218" s="2" t="inlineStr">
+      <c r="P218" s="4" t="inlineStr">
         <is>
           <t>Dozens of clinics on shared EHR. Lead with multi site support, HIPAA and clinic openings.</t>
         </is>
       </c>
-      <c r="Q218" s="2" t="inlineStr">
+      <c r="Q218" s="4" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="R218" s="2" t="inlineStr">
+      <c r="R218" s="4" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="S218" s="2" t="inlineStr">
+      <c r="S218" s="4" t="inlineStr">
         <is>
           <t>32775000</t>
         </is>
       </c>
-      <c r="T218" s="2" t="inlineStr">
+      <c r="T218" s="4" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="U218" s="2" t="n"/>
-      <c r="V218" s="2" t="inlineStr">
+      <c r="U218" s="4" t="n"/>
+      <c r="V218" s="4" t="inlineStr">
         <is>
           <t>baystatept.com</t>
         </is>
       </c>
-      <c r="W218" s="2" t="n"/>
-      <c r="X218" s="3" t="inlineStr">
-        <is>
-          <t>HQ moved to Braintree. ZoomInfo still lists 360 Brockton Ave, Abington. 15 min from Rockland. [ZoomInfo ID 26038289]</t>
+      <c r="W218" s="4" t="inlineStr">
+        <is>
+          <t>Unverified / Do Not Call (see notes)</t>
+        </is>
+      </c>
+      <c r="X218" s="5" t="inlineStr">
+        <is>
+          <t>HQ moved to Braintree. ZoomInfo still lists 360 Brockton Ave, Abington. 15 min from Rockland. [ZoomInfo ID 26038289]  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
@@ -44079,7 +44875,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>(781) 982-9333</t>
+          <t>(617) 990-2352</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -44094,10 +44890,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>gare.reid@thecateredaffair.com</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -44121,7 +44921,7 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Runs venues across Boston area from this HQ. Employee count includes event staff.</t>
+          <t>Runs venues across Boston area from this HQ. Employee count includes event staff.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -44138,7 +44938,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>(781) 261-9666</t>
+          <t>(781) 423-3053</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -44153,10 +44953,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ahoughton@controlpointtech.com</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -44180,7 +44984,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Same building as Food Tech. Two stops, one parking lot.</t>
+          <t>Same building as Food Tech. Two stops, one parking lot.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -44715,7 +45519,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Next door to Commonwealth Building Systems.</t>
+          <t>Next door to Commonwealth Building Systems.  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
@@ -44750,7 +45554,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>gwilkinson@gtwilkinson.com</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
@@ -44772,7 +45580,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M15" s="3" t="n"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email. No phone on file; use company main line.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -44884,7 +45696,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>ITAR and CMMC pressure is a strong door opener for machine shops.</t>
+          <t>ITAR and CMMC pressure is a strong door opener for machine shops.  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -44901,7 +45713,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>(800) 225-5404</t>
+          <t>(781) 871-4426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -44916,10 +45728,14 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>john@foodallergy.com</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
@@ -44941,7 +45757,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M18" s="3" t="n"/>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -45800,7 +46620,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G33" s="2" t="n"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>heather@northriverhc.com</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
@@ -45822,7 +46646,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M33" s="3" t="n"/>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, but both direct and mobile are Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -45879,7 +46707,7 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Possible referral partner too. They see every public safety and facilities buyer locally.</t>
+          <t>Possible referral partner too. They see every public safety and facilities buyer locally.  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -45936,7 +46764,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M35" s="3" t="n"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo matched the contact but returned no email or phone.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -45951,7 +46783,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>(781) 531-8227</t>
+          <t>(781) 783-2414</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -45966,10 +46798,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>cmurphy@bluebearplumbing.com</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
@@ -45993,7 +46829,7 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>PE style growth playbook. Headcount likely higher than listed.</t>
+          <t>PE style growth playbook. Headcount likely higher than listed.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -46010,7 +46846,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>(781) 681-6656</t>
+          <t>(781) 421-2496</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -46025,10 +46861,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>sean@driscollagency.com</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -46050,7 +46890,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M37" s="3" t="n"/>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -46297,7 +47141,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>(888) 735-3574</t>
+          <t>(617) 285-2863</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -46312,10 +47156,14 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>abecker@jackconway.com</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
@@ -46339,7 +47187,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Employee figure includes agents. Corporate staff here is much smaller.</t>
+          <t>Employee figure includes agents. Corporate staff here is much smaller.  |  ZoomInfo: direct line is Do Not Call; mobile (617) 285-2863 is callable.</t>
         </is>
       </c>
     </row>
@@ -46453,7 +47301,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Queen Anne's Corner plaza. Three targets share the 80 Washington St complex.</t>
+          <t>Queen Anne's Corner plaza. Three targets share the 80 Washington St complex.  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
@@ -46488,7 +47336,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G45" s="2" t="n"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>emcloughlin@southshoreautismcenter.com</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -46510,7 +47362,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M45" s="3" t="n"/>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, direct line is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -46567,7 +47423,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Same plaza as Proven Behavior and Oral Surgery South.</t>
+          <t>Same plaza as Proven Behavior and Oral Surgery South.  |  ZoomInfo: no email; both numbers Do Not Call and are out-of-state (FL/AZ). Verify the contact still sits in MA.</t>
         </is>
       </c>
     </row>
@@ -46584,7 +47440,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>(781) 871-1677</t>
+          <t>(508) 746-1614</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -46599,7 +47455,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G47" s="2" t="n"/>
@@ -46626,7 +47482,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>4 locations. Same plaza as LMHS and Proven Behavior.</t>
+          <t>4 locations. Same plaza as LMHS and Proven Behavior.  |  ZoomInfo confirmed direct dial, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -47027,7 +47883,7 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>Across the street from Jannell Ford.</t>
+          <t>Across the street from Jannell Ford.  |  ZoomInfo matched the contact but returned no email or phone.</t>
         </is>
       </c>
     </row>
@@ -47062,7 +47918,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G55" s="2" t="n"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>zwozny@wbaengineers.com</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
@@ -47084,7 +47944,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M55" s="3" t="n"/>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -47117,7 +47981,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G56" s="2" t="n"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>bmerrill@merrillinc.com</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
@@ -47141,7 +48009,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Same building as Homestead Mortgage. Pair the stops.</t>
+          <t>Same building as Homestead Mortgage. Pair the stops.  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -47723,7 +48591,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G66" s="2" t="n"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>mpmurphy@amurphy.com</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
@@ -47745,7 +48617,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M66" s="3" t="n"/>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -47778,7 +48654,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G67" s="2" t="n"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>sgeorge@eyesaverinternational.com</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
@@ -47802,7 +48682,7 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>Same building as Sturtevant. Pair the stops.</t>
+          <t>Same building as Sturtevant. Pair the stops.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -47819,7 +48699,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>(781) 829-6501</t>
+          <t>(781) 829-1455</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -47834,10 +48714,14 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>senglish@sturtevantinc.com</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
@@ -47861,7 +48745,7 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>Same building as Eyesaver International.</t>
+          <t>Same building as Eyesaver International.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -48348,7 +49232,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G77" s="2" t="n"/>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>tmckinney@newenglandvillage.org</t>
+        </is>
+      </c>
       <c r="H77" s="2" t="n"/>
       <c r="I77" s="2" t="inlineStr">
         <is>
@@ -48370,7 +49258,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M77" s="3" t="n"/>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email. No phone on file; use company main line.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -48385,7 +49277,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>(781) 293-1200</t>
+          <t>(617) 448-2406</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -48400,10 +49292,14 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>jen@preferredmechanicalservices.com</t>
+        </is>
+      </c>
       <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
@@ -48425,7 +49321,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M78" s="3" t="n"/>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -48480,7 +49380,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M79" s="3" t="n"/>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: no email, mobile is Do Not Call. Use company main line.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -48495,7 +49399,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>(781) 826-1546</t>
+          <t>(781) 422-8805</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -48510,7 +49414,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G80" s="2" t="n"/>
@@ -48537,7 +49441,7 @@
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>Same complex as Royal Health Group. Pair the stops.</t>
+          <t>Same complex as Royal Health Group. Pair the stops.  |  ZoomInfo confirmed direct dial, callable. No email on file. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -48554,7 +49458,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>(781) 681-9240</t>
+          <t>(781) 421-0918</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -48569,10 +49473,14 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>sschrader@acellaconstruction.com</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="n"/>
       <c r="I81" s="2" t="inlineStr">
         <is>
@@ -48596,7 +49504,7 @@
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>Builds for healthcare and schools locally. Referral rich.</t>
+          <t>Builds for healthcare and schools locally. Referral rich.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -48631,7 +49539,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G82" s="2" t="n"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>jsherman@ritchienavigation.com</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="n"/>
       <c r="I82" s="2" t="inlineStr">
         <is>
@@ -48655,7 +49567,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>America's oldest compass maker. Great conversation starter.</t>
+          <t>America's oldest compass maker. Great conversation starter.  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -48690,7 +49602,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G83" s="2" t="n"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>mhall@protectowire.com</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="n"/>
       <c r="I83" s="2" t="inlineStr">
         <is>
@@ -48712,7 +49628,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M83" s="3" t="n"/>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -49348,7 +50268,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>(781) 293-9711</t>
+          <t>(203) 401-9792</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -49363,7 +50283,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G95" s="2" t="n"/>
@@ -49390,7 +50310,7 @@
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
-          <t>Family owned since 1948 era roots. Verified via web.</t>
+          <t>Family owned since 1948 era roots. Verified via web.  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -49425,7 +50345,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G96" s="2" t="n"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>lou@seoanelandscape.com</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="n"/>
       <c r="I96" s="2" t="inlineStr">
         <is>
@@ -49447,7 +50371,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M96" s="3" t="n"/>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -49480,7 +50408,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G97" s="2" t="n"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>will@whitmanllc.com</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="n"/>
       <c r="I97" s="2" t="inlineStr">
         <is>
@@ -49504,7 +50436,7 @@
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
-          <t>Address confirmed via web. ZoomInfo listing was incomplete.</t>
+          <t>Address confirmed via web. ZoomInfo listing was incomplete.  |  VERIFY: ZoomInfo returned title Attorney under a different company record. Confirm this is the right William Whitman before using.</t>
         </is>
       </c>
     </row>
@@ -49539,7 +50471,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G98" s="2" t="n"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>don@d-i-g.com</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="n"/>
       <c r="I98" s="2" t="inlineStr">
         <is>
@@ -49563,7 +50499,7 @@
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
-          <t>Street address not published. Call before attempting a visit.</t>
+          <t>Street address not published. Call before attempting a visit.  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -49649,7 +50585,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G100" s="2" t="n"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>ernie@websterprinting.com</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="n"/>
       <c r="I100" s="2" t="inlineStr">
         <is>
@@ -49671,7 +50611,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M100" s="3" t="n"/>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -49686,7 +50630,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>(781) 447-0421</t>
+          <t>(781) 350-5181</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -49701,10 +50645,14 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>pawerthen@whitmantoolanddie.com</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="n"/>
       <c r="I101" s="2" t="inlineStr">
         <is>
@@ -49726,7 +50674,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M101" s="3" t="n"/>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -49759,7 +50711,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G102" s="2" t="n"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>shawn@presidenttitanium.com</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="n"/>
       <c r="I102" s="2" t="inlineStr">
         <is>
@@ -49783,7 +50739,7 @@
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
-          <t>Near Sullivan's on Franklin St. Pair the stops.</t>
+          <t>Near Sullivan's on Franklin St. Pair the stops.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -50524,7 +51480,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>(781) 340-1400</t>
+          <t>(781) 974-5923</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -50539,10 +51495,14 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>bbailey@egsawyer.com</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="n"/>
       <c r="I115" s="2" t="inlineStr">
         <is>
@@ -50566,7 +51526,7 @@
       </c>
       <c r="M115" s="3" t="inlineStr">
         <is>
-          <t>Libbey Industrial Pkwy anchor stop.</t>
+          <t>Libbey Industrial Pkwy anchor stop.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -50623,7 +51583,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M116" s="3" t="n"/>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo matched the contact but returned no email or phone.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -50656,7 +51620,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G117" s="2" t="n"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>ann.conner@harborclinical.com</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="n"/>
       <c r="I117" s="2" t="inlineStr">
         <is>
@@ -50680,7 +51648,7 @@
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
-          <t>Life sciences services. Compliance heavy, lean IT.</t>
+          <t>Life sciences services. Compliance heavy, lean IT.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -50715,7 +51683,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G118" s="2" t="n"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>debra@wellnessworkdays.com</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="n"/>
       <c r="I118" s="2" t="inlineStr">
         <is>
@@ -50737,7 +51709,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M118" s="3" t="n"/>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -50752,7 +51728,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>(781) 902-0304</t>
+          <t>(218) 543-7523</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -50767,10 +51743,14 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>tait.hoglund@o2x.com</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="n"/>
       <c r="I119" s="2" t="inlineStr">
         <is>
@@ -50794,7 +51774,7 @@
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
-          <t>Scituate Harbor office. Veteran founded.</t>
+          <t>Scituate Harbor office. Veteran founded.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -50880,7 +51860,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G121" s="2" t="n"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>sbuccigross@mcdonaldcorp.com</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="n"/>
       <c r="I121" s="2" t="inlineStr">
         <is>
@@ -50902,7 +51886,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M121" s="3" t="n"/>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -50935,7 +51923,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G122" s="2" t="n"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>gregg_estey@newenglandhospice.com</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="n"/>
       <c r="I122" s="2" t="inlineStr">
         <is>
@@ -50957,7 +51949,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M122" s="3" t="n"/>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, direct line is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -51027,7 +52023,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>(800) 445-6607</t>
+          <t>(917) 834-1910</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -51042,7 +52038,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G124" s="2" t="n"/>
@@ -51069,7 +52065,7 @@
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
-          <t>Same street as South Shore Orthopedics.</t>
+          <t>Same street as South Shore Orthopedics.  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -51128,7 +52124,7 @@
       </c>
       <c r="M125" s="3" t="inlineStr">
         <is>
-          <t>Same parkway as EG Sawyer.</t>
+          <t>Same parkway as EG Sawyer.  |  ZoomInfo: no email; both direct and mobile are Do Not Call. Use company main line.</t>
         </is>
       </c>
     </row>
@@ -51452,7 +52448,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>(800) 227-1464</t>
+          <t>(412) 228-5127</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -51467,10 +52463,14 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>louis.pappa@mcmcllc.com</t>
+        </is>
+      </c>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="inlineStr">
         <is>
@@ -51494,7 +52494,7 @@
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
-          <t>Crown Colony office park cluster.</t>
+          <t>Crown Colony office park cluster.  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -51511,7 +52511,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>(617) 472-6500</t>
+          <t>(617) 221-1551</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -51526,10 +52526,14 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>larry.levesque@granitecityelectric.com</t>
+        </is>
+      </c>
       <c r="H132" s="2" t="n"/>
       <c r="I132" s="2" t="inlineStr">
         <is>
@@ -51551,7 +52555,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M132" s="3" t="n"/>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -51566,7 +52574,7 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>(617) 825-6930</t>
+          <t>(617) 825-6930 ext. 156</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -51581,10 +52589,14 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>myassine@leekennedy.com</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="n"/>
       <c r="I133" s="2" t="inlineStr">
         <is>
@@ -51606,7 +52618,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M133" s="3" t="n"/>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -51621,7 +52637,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>(617) 471-8400</t>
+          <t>(617) 471-8400 ext. 114</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -51636,10 +52652,14 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>dcox@baystatecs.org</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="n"/>
       <c r="I134" s="2" t="inlineStr">
         <is>
@@ -51661,7 +52681,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M134" s="3" t="n"/>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -51676,7 +52700,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>(617) 773-5800</t>
+          <t>(858) 753-8027</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -51691,10 +52715,14 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>tyla@bestofcare.com</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="n"/>
       <c r="I135" s="2" t="inlineStr">
         <is>
@@ -51718,7 +52746,7 @@
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
-          <t>1250 Hancock holds Magellan Jets too.</t>
+          <t>1250 Hancock holds Magellan Jets too.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -51753,7 +52781,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G136" s="2" t="n"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>richard@hmrproperties.com</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="n"/>
       <c r="I136" s="2" t="inlineStr">
         <is>
@@ -51777,7 +52809,7 @@
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
-          <t>Same building as Stran.</t>
+          <t>Same building as Stran.  |  ZoomInfo: title is now Founder and President Emeritus, so he may have stepped back from day to day. Mobile is Do Not Call. Consider asking for the current operations lead.</t>
         </is>
       </c>
     </row>
@@ -51812,7 +52844,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G137" s="2" t="n"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>bill.graves@southcovemanor.org</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="n"/>
       <c r="I137" s="2" t="inlineStr">
         <is>
@@ -51834,7 +52870,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M137" s="3" t="n"/>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -51849,7 +52889,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>(781) 380-1675</t>
+          <t>(781) 312-2554</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -51864,10 +52904,14 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>ccollura@dellbrookjks.com</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="n"/>
       <c r="I138" s="2" t="inlineStr">
         <is>
@@ -51889,7 +52933,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M138" s="3" t="n"/>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: direct line is Do Not Call; mobile (781) 312-2554 is callable.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -51922,7 +52970,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G139" s="2" t="n"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>iwall@stran.com</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="inlineStr">
         <is>
@@ -51946,7 +52998,7 @@
       </c>
       <c r="M139" s="3" t="inlineStr">
         <is>
-          <t>Public company with a named CIO. Marina Bay office.</t>
+          <t>Public company with a named CIO. Marina Bay office.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -51981,7 +53033,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G140" s="2" t="n"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>jcalnan@jcalnan.com</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="n"/>
       <c r="I140" s="2" t="inlineStr">
         <is>
@@ -52003,7 +53059,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M140" s="3" t="n"/>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email. No phone on file; use company main line.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -52018,7 +53078,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>(617) 507-6589</t>
+          <t>(401) 692-2115</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -52033,10 +53093,14 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>mikev@magellanjets.com</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="n"/>
       <c r="I141" s="2" t="inlineStr">
         <is>
@@ -52058,7 +53122,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M141" s="3" t="n"/>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and mobile, callable.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -52115,7 +53183,7 @@
       </c>
       <c r="M142" s="3" t="inlineStr">
         <is>
-          <t>Crown Colony cluster with MCMC and Arbella.</t>
+          <t>Crown Colony cluster with MCMC and Arbella.  |  VERIFY: ZoomInfo returned an email on the wv.gov domain, which is a West Virginia government address and clearly the wrong person. No usable contact data.</t>
         </is>
       </c>
     </row>
@@ -52663,7 +53731,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>(877) 732-9101</t>
+          <t>(508) 503-1895</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -52678,10 +53746,14 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>jonathan.pinault@learnwell.com</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="n"/>
       <c r="I152" s="2" t="inlineStr">
         <is>
@@ -52705,7 +53777,7 @@
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
-          <t>Downtown Plymouth. Walking distance from 5PT.</t>
+          <t>Downtown Plymouth. Walking distance from 5PT.  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -52740,7 +53812,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G153" s="2" t="n"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>hosshekhon@vercenterprises.com</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="n"/>
       <c r="I153" s="2" t="inlineStr">
         <is>
@@ -52764,7 +53840,7 @@
       </c>
       <c r="M153" s="3" t="inlineStr">
         <is>
-          <t>President and MIS officer on file.</t>
+          <t>President and MIS officer on file.  |  ZoomInfo confirmed email. No phone on file; use company main line.</t>
         </is>
       </c>
     </row>
@@ -52821,7 +53897,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M154" s="3" t="n"/>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo matched the contact but returned no email or phone.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -52836,7 +53916,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>(781) 834-1300</t>
+          <t>(781) 536-3223</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -52851,10 +53931,14 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G155" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>jingwan@roadtoresponsibility.org</t>
+        </is>
+      </c>
       <c r="H155" s="2" t="n"/>
       <c r="I155" s="2" t="inlineStr">
         <is>
@@ -52876,7 +53960,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M155" s="3" t="n"/>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -52942,7 +54030,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>(781) 740-2440</t>
+          <t>(647) 928-4223</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -52957,10 +54045,14 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G157" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>sherry@unitedelevatorltd.com</t>
+        </is>
+      </c>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="inlineStr">
         <is>
@@ -52982,7 +54074,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M157" s="3" t="n"/>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>VERIFY: numbers returned are Ontario, Canada (905/647). This may be a different United Elevator. Confirm before calling.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -52997,7 +54093,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>(508) 830-3440</t>
+          <t>(508) 556-7952</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -53012,10 +54108,14 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>choyt@coolgearinc.com</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="n"/>
       <c r="I158" s="2" t="inlineStr">
         <is>
@@ -53037,7 +54137,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M158" s="3" t="n"/>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -53052,7 +54156,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>(781) 319-1000</t>
+          <t>(781) 319-1147</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -53067,10 +54171,14 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>ed.monahan@induscom.com</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="n"/>
       <c r="I159" s="2" t="inlineStr">
         <is>
@@ -53094,7 +54202,7 @@
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
-          <t>Tech adjacent, referral partner potential too.</t>
+          <t>Tech adjacent, referral partner potential too.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -53717,7 +54825,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>(508) 588-3300</t>
+          <t>(617) 353-4153</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -53732,7 +54840,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G170" s="2" t="n"/>
@@ -53759,7 +54867,7 @@
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
-          <t>CIO George Wyner on file. Century old family firm.</t>
+          <t>CIO George Wyner on file. Century old family firm.  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -53794,7 +54902,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G171" s="2" t="n"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>jsavery@jonesandvining.com</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="n"/>
       <c r="I171" s="2" t="inlineStr">
         <is>
@@ -53816,7 +54928,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M171" s="3" t="n"/>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -53831,7 +54947,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>(508) 559-6699</t>
+          <t>(508) 894-3511</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -53846,10 +54962,14 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G172" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>andersond@bnhc.org</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="n"/>
       <c r="I172" s="2" t="inlineStr">
         <is>
@@ -53873,7 +54993,7 @@
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
-          <t>HIPAA and grants. Sysadmin on file.</t>
+          <t>HIPAA and grants. Sysadmin on file.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -53890,7 +55010,7 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>(508) 927-7800</t>
+          <t>(508) 927-7819</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
@@ -53905,10 +55025,14 @@
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>jward@cheerpack.com</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="n"/>
       <c r="I173" s="2" t="inlineStr">
         <is>
@@ -53930,7 +55054,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M173" s="3" t="n"/>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -53963,7 +55091,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G174" s="2" t="n"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>jryan@burkedist.com</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="n"/>
       <c r="I174" s="2" t="inlineStr">
         <is>
@@ -53985,7 +55117,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M174" s="3" t="n"/>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -54000,7 +55136,7 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>(508) 588-4400</t>
+          <t>(412) 805-5868</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
@@ -54015,10 +55151,14 @@
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>emily.r@cervos.com</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="n"/>
       <c r="I175" s="2" t="inlineStr">
         <is>
@@ -54042,7 +55182,7 @@
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>Avon Industrial Park.</t>
+          <t>Avon Industrial Park.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -54059,7 +55199,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>(508) 588-3240</t>
+          <t>(508) 682-8529</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -54074,10 +55214,14 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G176" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>bklaila@gtrmfg.com</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="n"/>
       <c r="I176" s="2" t="inlineStr">
         <is>
@@ -54101,7 +55245,7 @@
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
-          <t>Ask about defense work and CMMC.</t>
+          <t>Ask about defense work and CMMC.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -54118,7 +55262,7 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>(781) 963-6440</t>
+          <t>(781) 473-2323</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
@@ -54133,10 +55277,14 @@
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>marke@frounds.com</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="n"/>
       <c r="I177" s="2" t="inlineStr">
         <is>
@@ -54158,7 +55306,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M177" s="3" t="n"/>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -54275,7 +55427,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>(508) 588-7007</t>
+          <t>(508) 728-4890</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -54290,10 +55442,14 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>matthewacord@rubywines.com</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="n"/>
       <c r="I180" s="2" t="inlineStr">
         <is>
@@ -54317,7 +55473,7 @@
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
-          <t>Family owned since 1933. CEO on file.</t>
+          <t>Family owned since 1933. CEO on file.  |  ZoomInfo confirmed email and mobile, callable.</t>
         </is>
       </c>
     </row>
@@ -54334,7 +55490,7 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>(508) 583-8300</t>
+          <t>(310) 800-6935</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
@@ -54349,7 +55505,7 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G181" s="2" t="n"/>
@@ -54374,7 +55530,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M181" s="3" t="n"/>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed mobile, callable (out-of-state area code on file). No email.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -54389,7 +55549,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>(508) 238-6985</t>
+          <t>(508) 238-6985 ext. 224</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -54404,10 +55564,14 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G182" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>wmcpherson@centralceilings.com</t>
+        </is>
+      </c>
       <c r="H182" s="2" t="n"/>
       <c r="I182" s="2" t="inlineStr">
         <is>
@@ -54429,7 +55593,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M182" s="3" t="n"/>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -54444,7 +55612,7 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>(508) 587-5401</t>
+          <t>(508) 587-5400 ext. 228</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
@@ -54459,10 +55627,14 @@
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G183" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>wmckinnon@aqualeisure.com</t>
+        </is>
+      </c>
       <c r="H183" s="2" t="n"/>
       <c r="I183" s="2" t="inlineStr">
         <is>
@@ -54484,7 +55656,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M183" s="3" t="n"/>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -54517,7 +55693,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G184" s="2" t="n"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>wayne.kritzman@equalexchange.com</t>
+        </is>
+      </c>
       <c r="H184" s="2" t="n"/>
       <c r="I184" s="2" t="inlineStr">
         <is>
@@ -54541,7 +55721,7 @@
       </c>
       <c r="M184" s="3" t="inlineStr">
         <is>
-          <t>Mission driven brand. Same street as Cheer Pack.</t>
+          <t>Mission driven brand. Same street as Cheer Pack.  |  ZoomInfo: email confirmed, both direct and mobile are Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -54812,7 +55992,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G189" s="2" t="n"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>gsnow@beta-inc.com</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="n"/>
       <c r="I189" s="2" t="inlineStr">
         <is>
@@ -54836,7 +56020,7 @@
       </c>
       <c r="M189" s="3" t="inlineStr">
         <is>
-          <t>From postcard list. Emails on file: mgershman@beta-inc.com, gsnow@beta-inc.com.</t>
+          <t>From postcard list. Emails on file: mgershman@beta-inc.com, gsnow@beta-inc.com.  |  ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
         </is>
       </c>
     </row>
@@ -55455,7 +56639,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>(800) 762-1552</t>
+          <t>(774) 268-0783</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -55470,7 +56654,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
+          <t>ZoomInfo verified personal direct/mobile</t>
         </is>
       </c>
       <c r="G200" s="2" t="n"/>
@@ -55497,7 +56681,7 @@
       </c>
       <c r="M200" s="3" t="inlineStr">
         <is>
-          <t>Big distribution ops, lean office IT.</t>
+          <t>Big distribution ops, lean office IT.  |  ZoomInfo confirmed mobile, callable. No email on file.</t>
         </is>
       </c>
     </row>
@@ -55616,7 +56800,7 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>(978) 674-8464</t>
+          <t>(978) 674-7231</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
@@ -55631,10 +56815,14 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G203" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>dlanci@nexdine.com</t>
+        </is>
+      </c>
       <c r="H203" s="2" t="n"/>
       <c r="I203" s="2" t="inlineStr">
         <is>
@@ -55658,7 +56846,7 @@
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
-          <t>Many client sites, one HQ office.</t>
+          <t>Many client sites, one HQ office.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -55675,7 +56863,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>(800) 777-4752</t>
+          <t>(508) 660-1176</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -55690,10 +56878,14 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>mherbert@islandoasis.com</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="n"/>
       <c r="I204" s="2" t="inlineStr">
         <is>
@@ -55717,7 +56909,7 @@
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
-          <t>Kerry owned plant, local ops team.</t>
+          <t>Kerry owned plant, local ops team.  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -55734,7 +56926,7 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>(508) 337-2727</t>
+          <t>(508) 337-2700</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
@@ -55749,10 +56941,14 @@
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>ed.murphy@belknapwhite.com</t>
+        </is>
+      </c>
       <c r="H205" s="2" t="n"/>
       <c r="I205" s="2" t="inlineStr">
         <is>
@@ -55774,7 +56970,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M205" s="3" t="n"/>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -55789,7 +56989,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>(781) 793-5300</t>
+          <t>(781) 793-5346</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -55804,10 +57004,14 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>rpaiva@charlesriverapparel.com</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="n"/>
       <c r="I206" s="2" t="inlineStr">
         <is>
@@ -55831,7 +57035,7 @@
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
-          <t>Same highway as Senior Metal Bellows.</t>
+          <t>Same highway as Senior Metal Bellows.  |  ZoomInfo confirmed email and direct dial, callable. Mobile is Do Not Call.</t>
         </is>
       </c>
     </row>
@@ -55866,7 +57070,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G207" s="2" t="n"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>rmadigan@accutechpkg.com</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="n"/>
       <c r="I207" s="2" t="inlineStr">
         <is>
@@ -55888,7 +57096,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M207" s="3" t="n"/>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -55954,7 +57166,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>(774) 225-6300</t>
+          <t>(774) 225-6327</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
@@ -55969,10 +57181,14 @@
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>Company main line -- reliably sourced</t>
-        </is>
-      </c>
-      <c r="G209" s="2" t="n"/>
+          <t>ZoomInfo verified personal direct/mobile</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>pmarceau@southshoremillwork.com</t>
+        </is>
+      </c>
       <c r="H209" s="2" t="n"/>
       <c r="I209" s="2" t="inlineStr">
         <is>
@@ -55996,7 +57212,7 @@
       </c>
       <c r="M209" s="3" t="inlineStr">
         <is>
-          <t>GM Peter Marceau on file.</t>
+          <t>GM Peter Marceau on file.  |  ZoomInfo confirmed email, direct dial and mobile, all callable.</t>
         </is>
       </c>
     </row>
@@ -56031,7 +57247,11 @@
           <t>Company main line -- reliably sourced</t>
         </is>
       </c>
-      <c r="G210" s="2" t="n"/>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>dcisenberg@chexfoods.com</t>
+        </is>
+      </c>
       <c r="H210" s="2" t="n"/>
       <c r="I210" s="2" t="inlineStr">
         <is>
@@ -56053,7 +57273,11 @@
           <t>Prospect</t>
         </is>
       </c>
-      <c r="M210" s="3" t="n"/>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>ZoomInfo: email confirmed, mobile is Do Not Call. Email or main line only.</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -56334,7 +57558,7 @@
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>HQ moved to Braintree. ZoomInfo still lists 360 Brockton Ave, Abington. 15 min from Rockland.</t>
+          <t>HQ moved to Braintree. ZoomInfo still lists 360 Brockton Ave, Abington. 15 min from Rockland.  |  ZoomInfo weak match (company only). No email or phone confirmed.</t>
         </is>
       </c>
     </row>
